--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -1759,7 +1759,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AQ9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AR9" s="9" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AQ11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AR11" s="9" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -1779,7 +1779,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Story Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Story Tracker'!$A$3:$AS$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Story Tracker'!$A$3:$AS$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS22"/>
+  <dimension ref="A1:AS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1310,43 +1310,43 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>floating-through-the-pillars-of-creation</t>
+          <t>aristotle-the-greatest-philosopher</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr"/>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>staging</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>free</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Floating Through the Pillars of Creation</t>
+          <t>Aristotle, the Greatest Philosopher</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Cold columns of dust and gas, six thousand light years out, quietly making stars</t>
+          <t>A quiet journey through reason, virtue, and the good life</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr"/>
@@ -1362,57 +1362,55 @@
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-09T00:00:00Z</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>1A1026</t>
+          <t>26384A</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>C98A6B</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
+          <t>B89A6A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>2640</v>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>Nothing out there is waiting for anything. The columns simply stand in the light, giving themselves up to it slowly, and they will go on standing long after tonight.</t>
+          <t>One calm mind, examined slowly — reason, virtue, and the good life, laid out like a quiet evening walk. Nothing here needs to be solved tonight.</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>Feeling small and safe</t>
+          <t>Curious, wandering minds</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>Slow and drifting</t>
+          <t>Slow and steady</t>
         </is>
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>Cold, dusty, lit from above</t>
+          <t>Marble, lamplight, reason</t>
         </is>
       </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
-          <t>You rise from your own roof and travel outward, past every planet, until the stars themselves begin to thicken into a glowing cloud. Three dark columns stand in the middle of it, each one taller than the gap between our sun and its nearest neighbour. You learn what they are made of, how starlight is quietly carving them, why they are pillars at all, and what is forming in the pockets of shadow inside. Then the light goes on arriving, as it has for six thousand years, and you let all of it go.</t>
+          <t>You settle in beside one of history’s calmest minds. This is a slow exploration of Aristotle’s life and ideas — how he watched the natural world, what he taught about knowledge, character, and friendship, and why his patient way of thinking still shapes how we understand ourselves. The questions are old, the pace is gentle, and nothing needs deciding tonight.</t>
         </is>
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-aristotle-en-v1-aac96</t>
         </is>
       </c>
       <c r="W6" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X6" s="7" t="inlineStr">
@@ -1427,7 +1425,7 @@
       </c>
       <c r="Z6" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>staging</t>
         </is>
       </c>
       <c r="AA6" s="9" t="inlineStr">
@@ -1462,7 +1460,7 @@
       </c>
       <c r="AG6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH6" s="9" t="inlineStr">
@@ -1472,22 +1470,22 @@
       </c>
       <c r="AI6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM6" s="9" t="inlineStr">
@@ -1502,7 +1500,7 @@
       </c>
       <c r="AO6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP6" s="9" t="inlineStr">
@@ -1517,25 +1515,25 @@
       </c>
       <c r="AR6" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AS6" s="9" t="inlineStr">
         <is>
-          <t>Stories/floating-through-the-pillars-of-creation/story.yaml</t>
+          <t>Stories/aristotle-the-greatest-philosopher/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>mapping-the-cosmic-web</t>
+          <t>dinosaurs-from-rule-to-ruin</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr"/>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>staging</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1545,27 +1543,27 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Mapping the Cosmic Web</t>
+          <t>The Dinosaurs: From Rule to Ruin</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Decades of cold nights on mountains, one galaxy at a time, until a shape appeared</t>
+          <t>A 44-minute journey through deep time</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Sleep Stories by AVP</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr"/>
@@ -1581,57 +1579,55 @@
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-11T02:11:43Z</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>10131F</t>
+          <t>26384A</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>8E9FD0</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
+          <t>B89A6A</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>2690</v>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>The largest arrangement there is, and it does nothing in any hurry. It was found by people writing down one number a night, and none of it needs your attention tonight.</t>
+          <t>Deep time moves slowly here. Every age in this story settled into stillness long ago, and nothing in it asks anything of you tonight.</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Ending a long day</t>
+          <t>Drifting through time</t>
         </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>Slow, wide, still</t>
+          <t>Slow and steady</t>
         </is>
       </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>Vast, dark, quiet, patient</t>
+          <t>Ancient, vast, hushed</t>
         </is>
       </c>
       <c r="U7" s="7" t="inlineStr">
         <is>
-          <t>Sit in a cold dome in Arizona in the 1980s, while somebody points a telescope at one faint smudge after another and writes down a number. Do that for years, plot the results, and a shape appears that nobody expected — galaxies strung along threads, gathered at knots, wrapped around enormous quiet rooms with almost nothing inside. Along the way, the mule driver who became one of the great observers, a sound from the early universe frozen into the sky as a ruler, and five thousand small robots that rearrange themselves in the dark.</t>
+          <t>Drift through the rise, reign, and quiet fading of the dinosaurs in a calm story of deep time. You move slowly across changing continents and warm shallow seas, through long ages when giants grazed in the light of an older sun, and follow the traces they left behind in stone — a world that never fully ended, still with us in every morning’s birdsong.</t>
         </is>
       </c>
       <c r="V7" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-dinosaurs-en-v1-aac96</t>
         </is>
       </c>
       <c r="W7" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X7" s="7" t="inlineStr">
@@ -1646,7 +1642,7 @@
       </c>
       <c r="Z7" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>staging</t>
         </is>
       </c>
       <c r="AA7" s="9" t="inlineStr">
@@ -1681,7 +1677,7 @@
       </c>
       <c r="AG7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH7" s="9" t="inlineStr">
@@ -1691,22 +1687,22 @@
       </c>
       <c r="AI7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM7" s="9" t="inlineStr">
@@ -1721,7 +1717,7 @@
       </c>
       <c r="AO7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP7" s="9" t="inlineStr">
@@ -1736,19 +1732,19 @@
       </c>
       <c r="AR7" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AS7" s="9" t="inlineStr">
         <is>
-          <t>Stories/mapping-the-cosmic-web/story.yaml</t>
+          <t>Stories/dinosaurs-from-rule-to-ruin/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>the-bakery-before-dawn</t>
+          <t>floating-through-the-pillars-of-creation</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr"/>
@@ -1759,7 +1755,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1769,12 +1765,12 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>The Bakery Before Dawn</t>
+          <t>Floating Through the Pillars of Creation</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Warm flour, a slow rising, and the long quiet hours before a town wakes</t>
+          <t>Cold columns of dust and gas, six thousand light years out, quietly making stars</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1784,7 +1780,7 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>cozy-tales</t>
+          <t>cosmic-journeys</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr"/>
@@ -1805,12 +1801,12 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>2E1F14</t>
+          <t>1A1026</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>E3B778</t>
+          <t>C98A6B</t>
         </is>
       </c>
       <c r="P8" s="8" t="inlineStr">
@@ -1820,27 +1816,27 @@
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>Someone else is already awake, working gently in the warm, at something that cannot be hurried. There is nothing here you need to do.</t>
+          <t>Nothing out there is waiting for anything. The columns simply stand in the light, giving themselves up to it slowly, and they will go on standing long after tonight.</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Feeling safe and warm</t>
+          <t>Feeling small and safe</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>Slow and steady</t>
+          <t>Slow and drifting</t>
         </is>
       </c>
       <c r="T8" s="7" t="inlineStr">
         <is>
-          <t>Warm, floury, hushed</t>
+          <t>Cold, dusty, lit from above</t>
         </is>
       </c>
       <c r="U8" s="7" t="inlineStr">
         <is>
-          <t>You cross a frozen street at two in the morning toward the one lit window on the corner, and step into a small tiled room that smells of warm flour. A baker works alone at a wooden bench, unhurried, feeding a glass jar that is older than she is. You learn what is living inside it, why the dough rests before it is touched, what the salt is quietly doing, and how a loaf lifts and sets and turns gold in the last half hour. Then the light goes off, and she walks home to sleep.</t>
+          <t>You rise from your own roof and travel outward, past every planet, until the stars themselves begin to thicken into a glowing cloud. Three dark columns stand in the middle of it, each one taller than the gap between our sun and its nearest neighbour. You learn what they are made of, how starlight is quietly carving them, why they are pillars at all, and what is forming in the pockets of shadow inside. Then the light goes on arriving, as it has for six thousand years, and you let all of it go.</t>
         </is>
       </c>
       <c r="V8" s="7" t="inlineStr">
@@ -1960,14 +1956,14 @@
       </c>
       <c r="AS8" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-bakery-before-dawn/story.yaml</t>
+          <t>Stories/floating-through-the-pillars-of-creation/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>the-bay-that-glows-at-night</t>
+          <t>mapping-the-cosmic-web</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr"/>
@@ -1988,12 +1984,12 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>The Bay That Glows at Night</t>
+          <t>Mapping the Cosmic Web</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Adrift on a moonless Caribbean bay where every touch of the water answers in blue</t>
+          <t>Decades of cold nights on mountains, one galaxy at a time, until a shape appeared</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -2003,7 +1999,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>cosmic-journeys</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr"/>
@@ -2024,12 +2020,12 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>0A1622</t>
+          <t>10131F</t>
         </is>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>63D9F2</t>
+          <t>8E9FD0</t>
         </is>
       </c>
       <c r="P9" s="8" t="inlineStr">
@@ -2039,27 +2035,27 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>No moon tonight, and that is the point. The paddle rests, the water glows wherever the fish go, and a whole island keeps its darkness like a garden.</t>
+          <t>The largest arrangement there is, and it does nothing in any hurry. It was found by people writing down one number a night, and none of it needs your attention tonight.</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>Dimming a busy mind</t>
+          <t>Ending a long day</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>Adrift and moonless</t>
+          <t>Slow, wide, still</t>
         </is>
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>Warm dark, blue sparks</t>
+          <t>Vast, dark, quiet, patient</t>
         </is>
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
-          <t>Glide out through a tunnel of mangroves onto the brightest glowing bay in the world, on a night with no moon. Learn how a single living cell, one of seven hundred thousand in every gallon, keeps a tiny pantry of light and opens it at a touch. Watch fish write comet trails, hold a handful of blue stars, and float between two skies while warm rain sets the whole surface flickering. With Darwin at the ship's rail, the rare milky seas that glow from horizon to horizon, and an island community that tends its darkness the way other towns tend their gardens.</t>
+          <t>Sit in a cold dome in Arizona in the 1980s, while somebody points a telescope at one faint smudge after another and writes down a number. Do that for years, plot the results, and a shape appears that nobody expected — galaxies strung along threads, gathered at knots, wrapped around enormous quiet rooms with almost nothing inside. Along the way, the mule driver who became one of the great observers, a sound from the early universe frozen into the sky as a ruler, and five thousand small robots that rearrange themselves in the dark.</t>
         </is>
       </c>
       <c r="V9" s="7" t="inlineStr">
@@ -2179,40 +2175,40 @@
       </c>
       <c r="AS9" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-bay-that-glows-at-night/story.yaml</t>
+          <t>Stories/mapping-the-cosmic-web/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>the-building-of-a-cathedral</t>
+          <t>the-bakery-before-dawn</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr"/>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>staging</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>free</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>The Building of a Cathedral</t>
+          <t>The Bakery Before Dawn</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>An evening among people entirely at peace with never finishing</t>
+          <t>Warm flour, a slow rising, and the long quiet hours before a town wakes</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -2222,7 +2218,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>ancient-worlds</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr"/>
@@ -2238,57 +2234,55 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-16T15:26:08Z</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>26222B</t>
+          <t>2E1F14</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>C9A2C8</t>
-        </is>
-      </c>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
+          <t>E3B778</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>2174</v>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>Sixty years done, eighty to go, and every person on the site content with that arithmetic. Nothing in your life needs finishing by morning either.</t>
+          <t>Someone else is already awake, working gently in the warm, at something that cannot be hurried. There is nothing here you need to do.</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>Setting worries down</t>
+          <t>Feeling safe and warm</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>Generational and calm</t>
+          <t>Slow and steady</t>
         </is>
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>Stone, dusk, gold, chant</t>
+          <t>Warm, floury, hushed</t>
         </is>
       </c>
       <c r="U10" s="7" t="inlineStr">
         <is>
-          <t>Walk into a thirteenth-century city at dusk, where the largest unfinished thing in the world has been rising for sixty years and will not be done for eighty more. Visit the lodge where stone dust turns gold in the doorway light, and the plaster tracing floor where three generations of masters have scratched their thinking at full size. Learn why the pointed arch lets stone float, how a timber centering is struck and a vault suddenly holds itself, and why lime mortar sets the pace of the whole century. Then watch the site put itself to bed, wrapped in straw against the frost, still quietly turning back into stone in the dark.</t>
+          <t>You cross a frozen street at two in the morning toward the one lit window on the corner, and step into a small tiled room that smells of warm flour. A baker works alone at a wooden bench, unhurried, feeding a glass jar that is older than she is. You learn what is living inside it, why the dough rests before it is touched, what the salt is quietly doing, and how a loaf lifts and sets and turns gold in the last half hour. Then the light goes off, and she walks home to sleep.</t>
         </is>
       </c>
       <c r="V10" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-bakery-before-dawn-en-v1-aac96</t>
         </is>
       </c>
       <c r="W10" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ElevenLabs_the-bakery-before-dawn.wav</t>
         </is>
       </c>
       <c r="X10" s="7" t="inlineStr">
@@ -2303,7 +2297,7 @@
       </c>
       <c r="Z10" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>staging</t>
         </is>
       </c>
       <c r="AA10" s="9" t="inlineStr">
@@ -2338,7 +2332,7 @@
       </c>
       <c r="AG10" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH10" s="9" t="inlineStr">
@@ -2348,22 +2342,22 @@
       </c>
       <c r="AI10" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ10" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK10" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL10" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM10" s="9" t="inlineStr">
@@ -2378,7 +2372,7 @@
       </c>
       <c r="AO10" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP10" s="9" t="inlineStr">
@@ -2398,14 +2392,14 @@
       </c>
       <c r="AS10" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-building-of-a-cathedral/story.yaml</t>
+          <t>Stories/the-bakery-before-dawn/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>the-clockmaker-s-workshop</t>
+          <t>the-bay-that-glows-at-night</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr"/>
@@ -2426,12 +2420,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>The Clockmaker's Workshop</t>
+          <t>The Bay That Glows at Night</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>An evening among a hundred gentle clocks, none of them quite in agreement</t>
+          <t>Adrift on a moonless Caribbean bay where every touch of the water answers in blue</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -2441,7 +2435,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>cozy-tales</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr"/>
@@ -2462,12 +2456,12 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>1C140E</t>
+          <t>0A1622</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>C98F3D</t>
+          <t>63D9F2</t>
         </is>
       </c>
       <c r="P11" s="8" t="inlineStr">
@@ -2477,27 +2471,27 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>The shop is locked, the lamp is out, and every pendulum keeps its small agreement in the dark. Nobody has to keep time while they sleep. It is being handled.</t>
+          <t>No moon tonight, and that is the point. The paddle rests, the water glows wherever the fish go, and a whole island keeps its darkness like a garden.</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>Ticking down to rest</t>
+          <t>Dimming a busy mind</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>Once a second, forever</t>
+          <t>Adrift and moonless</t>
         </is>
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>Brass, oil, a hundred ticks</t>
+          <t>Warm dark, blue sparks</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
         <is>
-          <t>Step through a door with a brass bell into a small-town shop where a hundred clocks tick softly out of step, like rain on a roof. At the bench, an unhurried craftsman tends a movement of polished wheels with tools that have not changed in two centuries. Learn what a clock really is, a falling weight let down slowly over a week, and why two clocks on the same wall drift into perfect step with each other, a mystery first noticed from a sickbed in 1665. With painted moon dials, a drawer of orphaned keys that all fit something somewhere, winding day, house calls taken over tea, and the repairers' names penciled inside case doors, a century apart.</t>
+          <t>Glide out through a tunnel of mangroves onto the brightest glowing bay in the world, on a night with no moon. Learn how a single living cell, one of seven hundred thousand in every gallon, keeps a tiny pantry of light and opens it at a touch. Watch fish write comet trails, hold a handful of blue stars, and float between two skies while warm rain sets the whole surface flickering. With Darwin at the ship's rail, the rare milky seas that glow from horizon to horizon, and an island community that tends its darkness the way other towns tend their gardens.</t>
         </is>
       </c>
       <c r="V11" s="7" t="inlineStr">
@@ -2617,14 +2611,14 @@
       </c>
       <c r="AS11" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-clockmaker-s-workshop/story.yaml</t>
+          <t>Stories/the-bay-that-glows-at-night/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>the-deep-ocean-trenches</t>
+          <t>the-building-of-a-cathedral</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr"/>
@@ -2645,22 +2639,22 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>The Deep Ocean Trenches</t>
+          <t>The Building of a Cathedral</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>A slow descent past the last of the light, into the stillest water on earth</t>
+          <t>An evening among people entirely at peace with never finishing</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr"/>
@@ -2681,12 +2675,12 @@
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>0B1F33</t>
+          <t>26222B</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>5FA8C4</t>
+          <t>C9A2C8</t>
         </is>
       </c>
       <c r="P12" s="8" t="inlineStr">
@@ -2696,27 +2690,27 @@
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>One slow direction, downward, and nothing waiting at the end of it. An easy thing to follow, and an easier thing to let go of.</t>
+          <t>Sixty years done, eighty to go, and every person on the site content with that arithmetic. Nothing in your life needs finishing by morning either.</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>Letting the day end</t>
+          <t>Setting worries down</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>Slow and sinking</t>
+          <t>Generational and calm</t>
         </is>
       </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
-          <t>Dark, cool, weightless</t>
+          <t>Stone, dusk, gold, chant</t>
         </is>
       </c>
       <c r="U12" s="7" t="inlineStr">
         <is>
-          <t>You slip beneath a starlit sea and sink, without effort, through the sunlit water and the long blue twilight into a darkness the sun has never reached. Small living lights blink on and drift away. Marine snow falls, soft and endless, all the way down to a floor of pale sediment older than memory. Further down still lie the trenches, where the pressure feels only like stillness and there is nowhere deeper to go.</t>
+          <t>Walk into a thirteenth-century city at dusk, where the largest unfinished thing in the world has been rising for sixty years and will not be done for eighty more. Visit the lodge where stone dust turns gold in the doorway light, and the plaster tracing floor where three generations of masters have scratched their thinking at full size. Learn why the pointed arch lets stone float, how a timber centering is struck and a vault suddenly holds itself, and why lime mortar sets the pace of the whole century. Then watch the site put itself to bed, wrapped in straw against the frost, still quietly turning back into stone in the dark.</t>
         </is>
       </c>
       <c r="V12" s="7" t="inlineStr">
@@ -2836,14 +2830,14 @@
       </c>
       <c r="AS12" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-deep-ocean-trenches/story.yaml</t>
+          <t>Stories/the-building-of-a-cathedral/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>the-great-library-of-alexandria</t>
+          <t>the-clockmaker-s-workshop</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr"/>
@@ -2864,22 +2858,22 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>The Great Library of Alexandria</t>
+          <t>The Clockmaker's Workshop</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Lamplight, papyrus and patient work beside a warm and quiet sea</t>
+          <t>An evening among a hundred gentle clocks, none of them quite in agreement</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>ancient-worlds</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr"/>
@@ -2900,12 +2894,12 @@
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>3A2A18</t>
+          <t>1C140E</t>
         </is>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>D9A55C</t>
+          <t>C98F3D</t>
         </is>
       </c>
       <c r="P13" s="8" t="inlineStr">
@@ -2915,27 +2909,27 @@
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>Nothing here is urgent and nothing needs remembering. Only scribes at their tables, copying one careful line at a time.</t>
+          <t>The shop is locked, the lamp is out, and every pendulum keeps its small agreement in the dark. Nobody has to keep time while they sleep. It is being handled.</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>Slowing a busy day</t>
+          <t>Ticking down to rest</t>
         </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>Slow, unhurried</t>
+          <t>Once a second, forever</t>
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>Warm, dusty, lamplit</t>
+          <t>Brass, oil, a hundred ticks</t>
         </is>
       </c>
       <c r="U13" s="7" t="inlineStr">
         <is>
-          <t>You arrive at a harbour in the evening, when the light is going gold and the sea wind is moving up through the streets. Inside the cool halls, thousands of scrolls lie in their niches, and scribes copy them by hand, one careful line at a time. You learn how papyrus was pressed from river reeds, how ink was made from soot, how the first catalogue was written, and how a man measured the whole earth from the length of a shadow. Then the lamps are lit, and the work is set down.</t>
+          <t>Step through a door with a brass bell into a small-town shop where a hundred clocks tick softly out of step, like rain on a roof. At the bench, an unhurried craftsman tends a movement of polished wheels with tools that have not changed in two centuries. Learn what a clock really is, a falling weight let down slowly over a week, and why two clocks on the same wall drift into perfect step with each other, a mystery first noticed from a sickbed in 1665. With painted moon dials, a drawer of orphaned keys that all fit something somewhere, winding day, house calls taken over tea, and the repairers' names penciled inside case doors, a century apart.</t>
         </is>
       </c>
       <c r="V13" s="7" t="inlineStr">
@@ -3055,14 +3049,14 @@
       </c>
       <c r="AS13" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-great-library-of-alexandria/story.yaml</t>
+          <t>Stories/the-clockmaker-s-workshop/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>the-joinery-of-japan-s-wooden-temples</t>
+          <t>the-deep-ocean-trenches</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
@@ -3083,22 +3077,22 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>The Joinery of Japan's Wooden Temples</t>
+          <t>The Deep Ocean Trenches</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Thirteen centuries of buildings held together by shape alone, and not one nail</t>
+          <t>A slow descent past the last of the light, into the stillest water on earth</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>ancient-worlds</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr"/>
@@ -3119,12 +3113,12 @@
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>1E241C</t>
+          <t>0B1F33</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>C4B49A</t>
+          <t>5FA8C4</t>
         </is>
       </c>
       <c r="P14" s="8" t="inlineStr">
@@ -3134,27 +3128,27 @@
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>Nothing here was ever nailed, so nothing is ever finished. It has been taken apart and put back together for thirteen hundred years, and none of it needs watching tonight.</t>
+          <t>One slow direction, downward, and nothing waiting at the end of it. An easy thing to follow, and an easier thing to let go of.</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>Putting the day down</t>
+          <t>Letting the day end</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>Careful and unhurried</t>
+          <t>Slow and sinking</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
-          <t>Wooden, misty, still, warm</t>
+          <t>Dark, cool, weightless</t>
         </is>
       </c>
       <c r="U14" s="7" t="inlineStr">
         <is>
-          <t>Stand in a raked gravel courtyard at dawn and look up at a building with no nails in it. No screws, no brackets, nothing but wood cut to hold wood. Along the way, the joint that grips harder the more you load it, the carpenter who said to buy the mountain rather than the timber, a central pillar that holds up nothing and rests loose on a stone, and roof bark peeled from living trees that grow it back in ten years. And at Ise, a shrine rebuilt from new wood every twenty years for thirteen centuries, because twenty years is the length of human memory.</t>
+          <t>You slip beneath a starlit sea and sink, without effort, through the sunlit water and the long blue twilight into a darkness the sun has never reached. Small living lights blink on and drift away. Marine snow falls, soft and endless, all the way down to a floor of pale sediment older than memory. Further down still lie the trenches, where the pressure feels only like stillness and there is nowhere deeper to go.</t>
         </is>
       </c>
       <c r="V14" s="7" t="inlineStr">
@@ -3274,14 +3268,14 @@
       </c>
       <c r="AS14" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-joinery-of-japan-s-wooden-temples/story.yaml</t>
+          <t>Stories/the-deep-ocean-trenches/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>the-journey-of-a-glacial-river</t>
+          <t>the-great-library-of-alexandria</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr"/>
@@ -3302,22 +3296,22 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>The Journey of a Glacial River</t>
+          <t>The Great Library of Alexandria</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>One snowflake's two-hundred-year trip from a silent snowfield to the sea</t>
+          <t>Lamplight, papyrus and patient work beside a warm and quiet sea</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr"/>
@@ -3338,12 +3332,12 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>0F2230</t>
+          <t>3A2A18</t>
         </is>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>7FD0C9</t>
+          <t>D9A55C</t>
         </is>
       </c>
       <c r="P15" s="8" t="inlineStr">
@@ -3353,27 +3347,27 @@
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>Water never has to choose. It goes the one way it can go, at whatever pace it is given, and tonight you can go with it, downhill the whole way.</t>
+          <t>Nothing here is urgent and nothing needs remembering. Only scribes at their tables, copying one careful line at a time.</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>Drifting downstream</t>
+          <t>Slowing a busy day</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>Downhill, all the way</t>
+          <t>Slow, unhurried</t>
         </is>
       </c>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>Blue ice, cold water, calm</t>
+          <t>Warm, dusty, lamplit</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
-          <t>Follow a single snowflake from a windless high snowfield down to the salt water, a journey of two centuries in one direction only. Be buried into blue glacier ice with a breath of old sky sealed inside, ride the slowest river there is, and emerge at the ice cave where the young river is born, milky with the flour of ground mountains. Then down through the braided gravel plains, into a turquoise lake that sorts the sunlight, through pine forests where a small brown bird walks underwater, and out at last across the mudflats to the sea, where the sun is already lifting the water to begin again.</t>
+          <t>You arrive at a harbour in the evening, when the light is going gold and the sea wind is moving up through the streets. Inside the cool halls, thousands of scrolls lie in their niches, and scribes copy them by hand, one careful line at a time. You learn how papyrus was pressed from river reeds, how ink was made from soot, how the first catalogue was written, and how a man measured the whole earth from the length of a shadow. Then the lamps are lit, and the work is set down.</t>
         </is>
       </c>
       <c r="V15" s="7" t="inlineStr">
@@ -3493,14 +3487,14 @@
       </c>
       <c r="AS15" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-journey-of-a-glacial-river/story.yaml</t>
+          <t>Stories/the-great-library-of-alexandria/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>the-life-cycle-of-a-red-dwarf-star</t>
+          <t>the-joinery-of-japan-s-wooden-temples</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr"/>
@@ -3521,12 +3515,12 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>The Life Cycle of a Red Dwarf Star</t>
+          <t>The Joinery of Japan's Wooden Temples</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>The commonest star in the galaxy, burning so slowly that none has ever finished</t>
+          <t>Thirteen centuries of buildings held together by shape alone, and not one nail</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -3536,7 +3530,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr"/>
@@ -3557,12 +3551,12 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>1C1013</t>
+          <t>1E241C</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>D97A55</t>
+          <t>C4B49A</t>
         </is>
       </c>
       <c r="P16" s="8" t="inlineStr">
@@ -3572,27 +3566,27 @@
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>Not one red dwarf has ever run down. The universe is far too young. Every single one ever made is still quietly burning, and none of it needs watching tonight.</t>
+          <t>Nothing here was ever nailed, so nothing is ever finished. It has been taken apart and put back together for thirteen hundred years, and none of it needs watching tonight.</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>Unwinding without hurry</t>
+          <t>Putting the day down</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>Low, warm, unchanging</t>
+          <t>Careful and unhurried</t>
         </is>
       </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
-          <t>Dim, orange, warm, endless</t>
+          <t>Wooden, misty, still, warm</t>
         </is>
       </c>
       <c r="U16" s="7" t="inlineStr">
         <is>
-          <t>Travel four light years to Proxima Centauri, a small orange star so dim you could look straight at it, and so ordinary that three quarters of the galaxy is made of stars like it. Inside, the whole body slowly turns itself over, which is why it will still be burning in ten trillion years. Along the way, why nature makes far more small stars than large ones, the women at Harvard who sorted the spectra by hand, the titanium chemistry that survives in a star's atmosphere, and the quiet fact that not one red dwarf anywhere has ever finished.</t>
+          <t>Stand in a raked gravel courtyard at dawn and look up at a building with no nails in it. No screws, no brackets, nothing but wood cut to hold wood. Along the way, the joint that grips harder the more you load it, the carpenter who said to buy the mountain rather than the timber, a central pillar that holds up nothing and rests loose on a stone, and roof bark peeled from living trees that grow it back in ten years. And at Ise, a shrine rebuilt from new wood every twenty years for thirteen centuries, because twenty years is the length of human memory.</t>
         </is>
       </c>
       <c r="V16" s="7" t="inlineStr">
@@ -3712,14 +3706,14 @@
       </c>
       <c r="AS16" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-life-cycle-of-a-red-dwarf-star/story.yaml</t>
+          <t>Stories/the-joinery-of-japan-s-wooden-temples/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>the-midnight-sleeper-train-across-the-alps</t>
+          <t>the-journey-of-a-glacial-river</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr"/>
@@ -3740,12 +3734,12 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>The Midnight Sleeper Train Across the Alps</t>
+          <t>The Journey of a Glacial River</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>A warm berth, a folder of sleeping passports, and mountains passing in the dark</t>
+          <t>One snowflake's two-hundred-year trip from a silent snowfield to the sea</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -3755,7 +3749,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>cozy-tales</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr"/>
@@ -3776,12 +3770,12 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>151A2E</t>
+          <t>0F2230</t>
         </is>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>D9B36C</t>
+          <t>7FD0C9</t>
         </is>
       </c>
       <c r="P17" s="8" t="inlineStr">
@@ -3791,27 +3785,27 @@
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>The signals are turning green all the way to the lake, and the attendant is awake so you need not be. The train knows the rest, and none of it is your business tonight.</t>
+          <t>Water never has to choose. It goes the one way it can go, at whatever pace it is given, and tonight you can go with it, downhill the whole way.</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>Being gently carried</t>
+          <t>Drifting downstream</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>Rocking and westward</t>
+          <t>Downhill, all the way</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>Warm, amber, moonlit, moving</t>
+          <t>Blue ice, cold water, calm</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
-          <t>Board the midnight-blue sleeper in Vienna, hand your passport to the attendant, and let the train do the rest. Cross the Alps in a rocking berth while borders pass over you like weather, carriages are quietly sorted toward separate mornings, and a freight train washes past in the dark. Along the way, why the clickety-clack disappeared when the rails were welded into seamless miles, the 1884 tunnel bored from both ends to meet like a handshake, and the whole quiet profession of people who stay awake so that everyone else can sleep at seventy miles an hour.</t>
+          <t>Follow a single snowflake from a windless high snowfield down to the salt water, a journey of two centuries in one direction only. Be buried into blue glacier ice with a breath of old sky sealed inside, ride the slowest river there is, and emerge at the ice cave where the young river is born, milky with the flour of ground mountains. Then down through the braided gravel plains, into a turquoise lake that sorts the sunlight, through pine forests where a small brown bird walks underwater, and out at last across the mudflats to the sea, where the sun is already lifting the water to begin again.</t>
         </is>
       </c>
       <c r="V17" s="7" t="inlineStr">
@@ -3931,14 +3925,14 @@
       </c>
       <c r="AS17" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-midnight-sleeper-train-across-the-alps/story.yaml</t>
+          <t>Stories/the-journey-of-a-glacial-river/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>the-moons-of-jupiter-europa-s-ice-and-ocean</t>
+          <t>the-life-cycle-of-a-red-dwarf-star</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr"/>
@@ -3959,12 +3953,12 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>The Moons of Jupiter: Europa's Ice and Ocean</t>
+          <t>The Life Cycle of a Red Dwarf Star</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>A small cracked moon of ice, and the dark ocean turning over beneath it</t>
+          <t>The commonest star in the galaxy, burning so slowly that none has ever finished</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -3995,12 +3989,12 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>0E1A2B</t>
+          <t>1C1013</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>9FC8DA</t>
+          <t>D97A55</t>
         </is>
       </c>
       <c r="P18" s="8" t="inlineStr">
@@ -4010,27 +4004,27 @@
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>There is no light down there and there never has been. The water simply turns over in the dark, as it has for a very long time, and none of it needs watching tonight.</t>
+          <t>Not one red dwarf has ever run down. The universe is far too young. Every single one ever made is still quietly burning, and none of it needs watching tonight.</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>Sinking into sleep</t>
+          <t>Unwinding without hurry</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>Quiet and downward</t>
+          <t>Low, warm, unchanging</t>
         </is>
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>Cold, white, deep, quiet</t>
+          <t>Dim, orange, warm, endless</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
         <is>
-          <t>You travel out past Mars to a banded planet eleven times the width of the Earth, and find four small worlds standing beside it in a line. The second one is white, smooth as a billiard ball, and cracked all over like a glazed bowl. You learn why it has almost no craters, how a tiny wobble in its orbit keeps an ocean liquid where nothing should be, and how that ocean was found from the outside without anyone touching it. Then you sink through the ice into water that has never once seen light.</t>
+          <t>Travel four light years to Proxima Centauri, a small orange star so dim you could look straight at it, and so ordinary that three quarters of the galaxy is made of stars like it. Inside, the whole body slowly turns itself over, which is why it will still be burning in ten trillion years. Along the way, why nature makes far more small stars than large ones, the women at Harvard who sorted the spectra by hand, the titanium chemistry that survives in a star's atmosphere, and the quiet fact that not one red dwarf anywhere has ever finished.</t>
         </is>
       </c>
       <c r="V18" s="7" t="inlineStr">
@@ -4150,14 +4144,14 @@
       </c>
       <c r="AS18" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-moons-of-jupiter-europa-s-ice-and-ocean/story.yaml</t>
+          <t>Stories/the-life-cycle-of-a-red-dwarf-star/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>the-observatory-on-ben-nevis</t>
+          <t>the-midnight-sleeper-train-across-the-alps</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr"/>
@@ -4178,17 +4172,17 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>The Observatory on Ben Nevis</t>
+          <t>The Midnight Sleeper Train Across the Alps</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Twenty-one years of hourly weather readings, taken by lamplight inside a cloud</t>
+          <t>A warm berth, a folder of sleeping passports, and mountains passing in the dark</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -4214,12 +4208,12 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>1F2A2E</t>
+          <t>151A2E</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>B9C9CE</t>
+          <t>D9B36C</t>
         </is>
       </c>
       <c r="P19" s="8" t="inlineStr">
@@ -4229,27 +4223,27 @@
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>Somebody is awake on a mountain, taking a reading on the hour, whether or not you are. The next one is not yours, and it will be taken anyway.</t>
+          <t>The signals are turning green all the way to the lake, and the attendant is awake so you need not be. The train knows the rest, and none of it is your business tonight.</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>Letting go of the day</t>
+          <t>Being gently carried</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>Hourly and unhurried</t>
+          <t>Rocking and westward</t>
         </is>
       </c>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>Cold, lamplit, patient</t>
+          <t>Warm, amber, moonlit, moving</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
         <is>
-          <t>You climb into the cloud that sits on the highest ground in Britain, and step through a low stone door into lamplight, a warm stove, and a kettle that is always on. For twenty-one years, somebody here walked out into the weather every hour of every night and wrote down what it was doing. You learn how a wet sleeve of muslin measures the dryness of the air, why the thermometer boxes had to be lifted as the snow came up to meet them, and how ice grows sideways into the wind. Then the lamp is turned low, a wet coat goes on the hook, and the mountain carries on without you.</t>
+          <t>Board the midnight-blue sleeper in Vienna, hand your passport to the attendant, and let the train do the rest. Cross the Alps in a rocking berth while borders pass over you like weather, carriages are quietly sorted toward separate mornings, and a freight train washes past in the dark. Along the way, why the clickety-clack disappeared when the rails were welded into seamless miles, the 1884 tunnel bored from both ends to meet like a handshake, and the whole quiet profession of people who stay awake so that everyone else can sleep at seventy miles an hour.</t>
         </is>
       </c>
       <c r="V19" s="7" t="inlineStr">
@@ -4369,40 +4363,40 @@
       </c>
       <c r="AS19" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-observatory-on-ben-nevis/story.yaml</t>
+          <t>Stories/the-midnight-sleeper-train-across-the-alps/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>the-rings-of-saturn</t>
+          <t>the-moons-of-jupiter-europa-s-ice-and-ocean</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr"/>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>The Rings of Saturn</t>
+          <t>The Moons of Jupiter: Europa's Ice and Ocean</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Ten metres of ice, two hundred thousand kilometres wide, turning in silence</t>
+          <t>A small cracked moon of ice, and the dark ocean turning over beneath it</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -4423,60 +4417,62 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14T17:53:16Z</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>1B2436</t>
+          <t>0E1A2B</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>E8C89A</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="n">
-        <v>2125.557</v>
+          <t>9FC8DA</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>A long way from anything that has ever asked something of you. Nothing out here is in a hurry, and none of it needs watching.</t>
+          <t>There is no light down there and there never has been. The water simply turns over in the dark, as it has for a very long time, and none of it needs watching tonight.</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>Drifting off slowly</t>
+          <t>Sinking into sleep</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>Slow and weightless</t>
+          <t>Quiet and downward</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Cold, vast, silent</t>
+          <t>Cold, white, deep, quiet</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
         <is>
-          <t>You rise gently from your own roof and travel outward, past the Moon and Jupiter, until a tilted gold shape appears in the dark. Up close the rings resolve into thousands of fine bright lines, and then into ice: billions of frozen pieces, some finer than dust and some the size of mountains, all drifting the same way at once. You watch small moons carve clean lanes and raise slow waves behind them, hear a gentle unfinished argument about how old it all is, and then settle into the ring plane and stay.</t>
+          <t>You travel out past Mars to a banded planet eleven times the width of the Earth, and find four small worlds standing beside it in a line. The second one is white, smooth as a billiard ball, and cracked all over like a glazed bowl. You learn why it has almost no craters, how a tiny wobble in its orbit keeps an ocean liquid where nothing should be, and how that ocean was found from the outside without anyone touching it. Then you sink through the ice into water that has never once seen light.</t>
         </is>
       </c>
       <c r="V20" s="7" t="inlineStr">
         <is>
-          <t>audio-the-rings-of-saturn-en-v2-aac96</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="W20" s="7" t="inlineStr">
         <is>
-          <t>ElevenLabs_the-rings-of-saturn-v2.wav</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -4491,12 +4487,12 @@
       </c>
       <c r="Z20" s="9" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="AA20" s="9" t="inlineStr">
         <is>
-          <t>READY</t>
+          <t>NOT READY</t>
         </is>
       </c>
       <c r="AB20" s="9" t="inlineStr">
@@ -4526,47 +4522,47 @@
       </c>
       <c r="AG20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AH20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AI20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AJ20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AK20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AL20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AM20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AN20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AO20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AP20" s="9" t="inlineStr">
@@ -4586,14 +4582,14 @@
       </c>
       <c r="AS20" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-rings-of-saturn/story.yaml</t>
+          <t>Stories/the-moons-of-jupiter-europa-s-ice-and-ocean/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>the-slow-life-of-a-redwood</t>
+          <t>the-observatory-on-ben-nevis</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr"/>
@@ -4614,22 +4610,22 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>The Slow Life of a Redwood</t>
+          <t>The Observatory on Ben Nevis</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>A night in the fog with the tallest living things there have ever been</t>
+          <t>Twenty-one years of hourly weather readings, taken by lamplight inside a cloud</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
@@ -4650,12 +4646,12 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>14201A</t>
+          <t>1F2A2E</t>
         </is>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>A8C3A0</t>
+          <t>B9C9CE</t>
         </is>
       </c>
       <c r="P21" s="8" t="inlineStr">
@@ -4665,27 +4661,27 @@
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>The grove waters itself with fog while everyone sleeps, and has done for two thousand summers. Nothing in it moves faster than a slug, and nothing needs watching tonight.</t>
+          <t>Somebody is awake on a mountain, taking a reading on the hour, whether or not you are. The next one is not yours, and it will be taken anyway.</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>Quieting a full mind</t>
+          <t>Letting go of the day</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>Soft, green, ancient</t>
+          <t>Hourly and unhurried</t>
         </is>
       </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>Foggy, hushed, deep green</t>
+          <t>Cold, lamplit, patient</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
         <is>
-          <t>Walk into a coastal grove at dusk and stand at the foot of a tree over three hundred feet tall, wrapped in a foot of soft bark, older than the cathedrals. Follow one unbroken thread of water from the roots to the highest needle, and wait for the summer fog to roll in off the cold Pacific so the forest can water itself in the dark. Along the way, roots that graft into their neighbours and hold each other up, rings of trees standing where their elders stood, a ghost-white redwood fed by its family, and a garden of ferns and huckleberries growing a metre deep in the crown.</t>
+          <t>You climb into the cloud that sits on the highest ground in Britain, and step through a low stone door into lamplight, a warm stove, and a kettle that is always on. For twenty-one years, somebody here walked out into the weather every hour of every night and wrote down what it was doing. You learn how a wet sleeve of muslin measures the dryness of the air, why the thermometer boxes had to be lifted as the snow came up to meet them, and how ice grows sideways into the wind. Then the lamp is turned low, a wet coat goes on the hook, and the mountain carries on without you.</t>
         </is>
       </c>
       <c r="V21" s="7" t="inlineStr">
@@ -4805,40 +4801,40 @@
       </c>
       <c r="AS21" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-slow-life-of-a-redwood/story.yaml</t>
+          <t>Stories/the-observatory-on-ben-nevis/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>voyager-1-a-journey-to-interstellar-space</t>
+          <t>the-rings-of-saturn</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr"/>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>free</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Voyager 1: A Journey to Interstellar Space</t>
+          <t>The Rings of Saturn</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>A small gold machine, forty-nine years out, still quietly drifting away from us</t>
+          <t>Ten metres of ice, two hundred thousand kilometres wide, turning in silence</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -4859,177 +4855,613 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14T17:53:16Z</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>1B2436</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>E8C89A</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>2125.557</v>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>A long way from anything that has ever asked something of you. Nothing out here is in a hurry, and none of it needs watching.</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr">
+        <is>
+          <t>Drifting off slowly</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>Slow and weightless</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
+        <is>
+          <t>Cold, vast, silent</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>You rise gently from your own roof and travel outward, past the Moon and Jupiter, until a tilted gold shape appears in the dark. Up close the rings resolve into thousands of fine bright lines, and then into ice: billions of frozen pieces, some finer than dust and some the size of mountains, all drifting the same way at once. You watch small moons carve clean lanes and raise slow waves behind them, hear a gentle unfinished argument about how old it all is, and then settle into the ring plane and stay.</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-rings-of-saturn-en-v2-aac96</t>
+        </is>
+      </c>
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>ElevenLabs_the-rings-of-saturn-v2.wav</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
+        </is>
+      </c>
+      <c r="Z22" s="9" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="AA22" s="9" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="AB22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AH22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AI22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AO22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AP22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS22" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-rings-of-saturn/story.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>the-slow-life-of-a-redwood</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>The Slow Life of a Redwood</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>A night in the fog with the tallest living things there have ever been</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Lullable</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>gentle-nature</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>14201A</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>A8C3A0</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>The grove waters itself with fog while everyone sleeps, and has done for two thousand summers. Nothing in it moves faster than a slug, and nothing needs watching tonight.</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>Quieting a full mind</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>Soft, green, ancient</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>Foggy, hushed, deep green</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Walk into a coastal grove at dusk and stand at the foot of a tree over three hundred feet tall, wrapped in a foot of soft bark, older than the cathedrals. Follow one unbroken thread of water from the roots to the highest needle, and wait for the summer fog to roll in off the cold Pacific so the forest can water itself in the dark. Along the way, roots that graft into their neighbours and hold each other up, rings of trees standing where their elders stood, a ghost-white redwood fed by its family, and a garden of ferns and huckleberries growing a metre deep in the crown.</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
+        </is>
+      </c>
+      <c r="Z23" s="9" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="AA23" s="9" t="inlineStr">
+        <is>
+          <t>NOT READY</t>
+        </is>
+      </c>
+      <c r="AB23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG23" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AH23" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AI23" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AJ23" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AK23" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AL23" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AM23" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AN23" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AO23" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AP23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS23" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-slow-life-of-a-redwood/story.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>voyager-1-a-journey-to-interstellar-space</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Voyager 1: A Journey to Interstellar Space</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>A small gold machine, forty-nine years out, still quietly drifting away from us</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Lullable</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>cosmic-journeys</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>0A0F1C</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>C7B27A</t>
         </is>
       </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>It left in 1977 and it is not going anywhere in particular. It is simply still going, steadily, and none of it needs watching tonight.</t>
         </is>
       </c>
-      <c r="R22" s="7" t="inlineStr">
+      <c r="R24" s="7" t="inlineStr">
         <is>
           <t>Settling into the quiet</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>Steady and outward</t>
         </is>
       </c>
-      <c r="T22" s="7" t="inlineStr">
+      <c r="T24" s="7" t="inlineStr">
         <is>
           <t>Dark, distant, gold, calm</t>
         </is>
       </c>
-      <c r="U22" s="7" t="inlineStr">
+      <c r="U24" s="7" t="inlineStr">
         <is>
           <t>Follow the most distant object people have ever made, out past Jupiter and Saturn and into the space between the stars. A gold record bolted to its side, a transmitter no brighter than a refrigerator bulb, and a whisper of radio that takes almost a full day to reach a dish in the Australian grass. Along the way, the gentle theft of a gravity assist, the choice to look at Titan, and the faint steady hum the gas out there turns out to make. Nothing about it is urgent. Nothing about it ever was.</t>
         </is>
       </c>
-      <c r="V22" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="W22" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y22" s="7" t="inlineStr">
+      <c r="Y24" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z22" s="9" t="inlineStr">
+      <c r="Z24" s="9" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="AA22" s="9" t="inlineStr">
+      <c r="AA24" s="9" t="inlineStr">
         <is>
           <t>NOT READY</t>
         </is>
       </c>
-      <c r="AB22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AE22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AF22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AG22" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AH22" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AI22" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AJ22" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AK22" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AL22" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AM22" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AN22" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AO22" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AP22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AQ22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AR22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AS22" s="9" t="inlineStr">
+      <c r="AB24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AH24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AI24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AJ24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AK24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AL24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AM24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AN24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AO24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AP24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS24" s="9" t="inlineStr">
         <is>
           <t>Stories/voyager-1-a-journey-to-interstellar-space/story.yaml</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AS22"/>
+  <autoFilter ref="A3:AS24"/>
   <mergeCells count="6">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A2:B2"/>
@@ -5038,7 +5470,7 @@
     <mergeCell ref="A1:AS1"/>
     <mergeCell ref="F2:Y2"/>
   </mergeCells>
-  <conditionalFormatting sqref="AB5:AS22">
+  <conditionalFormatting sqref="AB5:AS24">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"FAIL"</formula>
     </cfRule>
@@ -5046,7 +5478,7 @@
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA5:AA22">
+  <conditionalFormatting sqref="AA5:AA24">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"READY"</formula>
     </cfRule>
@@ -5054,31 +5486,31 @@
       <formula>"NOT READY"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D22">
+  <conditionalFormatting sqref="D5:D24">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"PENDING"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="C5:C62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="workflowStatus" prompt="Pipeline stage." type="list" errorStyle="stop">
+    <dataValidation sqref="C5:C64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="workflowStatus" prompt="Pipeline stage." type="list" errorStyle="stop">
       <formula1>"draft,rendered,qa-approved,staging,published"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="accessDecision" prompt="Free vs premium. Settle before staging." type="list" errorStyle="stop">
+    <dataValidation sqref="D5:D64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="accessDecision" prompt="Free vs premium. Settle before staging." type="list" errorStyle="stop">
       <formula1>"PENDING,free,premium"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_1" prompt="Existing genre IDs only." type="list" errorStyle="stop">
+    <dataValidation sqref="I5:I64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_1" prompt="Existing genre IDs only." type="list" errorStyle="stop">
       <formula1>"ancient-worlds,gentle-nature,cosmic-journeys,cozy-tales"</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_2" prompt="Existing genre IDs only." type="list" errorStyle="stop">
+    <dataValidation sqref="J5:J64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_2" prompt="Existing genre IDs only." type="list" errorStyle="stop">
       <formula1>"ancient-worlds,gentle-nature,cosmic-journeys,cozy-tales"</formula1>
     </dataValidation>
-    <dataValidation sqref="X5:X62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="commercialRightsStatus" prompt="Must be verified to publish." type="list" errorStyle="stop">
+    <dataValidation sqref="X5:X64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="commercialRightsStatus" prompt="Must be verified to publish." type="list" errorStyle="stop">
       <formula1>"pending-verification,verified,restricted"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="trialPreviewEligible" prompt="true or false." type="list" errorStyle="stop">
+    <dataValidation sqref="K5:K64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="trialPreviewEligible" prompt="true or false." type="list" errorStyle="stop">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="isFeatured" prompt="true or false." type="list" errorStyle="stop">
+    <dataValidation sqref="L5:L64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="isFeatured" prompt="true or false." type="list" errorStyle="stop">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -1097,7 +1097,7 @@
       <c r="B5" s="7" t="inlineStr"/>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -1156,44 +1156,42 @@
           <t>E0A96D</t>
         </is>
       </c>
-      <c r="P5" s="8" t="inlineStr">
+      <c r="P5" s="8" t="n">
+        <v>2330</v>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>The fire is banked, the water runs on its own, and the night man is dozing at his post. The building keeps itself warm until morning, and none of it needs you.</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Warming down to sleep</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Lamplit and settling</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Steam, stone, amber light</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Slip into a provincial Roman bathhouse at the gentlest hour of its day, just as the crowds drift home and the attendants light the evening lamps. Walk the warm rooms in their proper order, stand on a floor heated by a fire nobody sees, and listen to water that has been arriving from the hills without pause for a hundred years. Along the way, the bronze strigil and the oil, Seneca's famous list of bathhouse noises, the spring in Britain where the earth itself stokes the furnace, and the banked fire that will breathe warmth under the mosaics all night long.</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
-        <is>
-          <t>The fire is banked, the water runs on its own, and the night man is dozing at his post. The building keeps itself warm until morning, and none of it needs you.</t>
-        </is>
-      </c>
-      <c r="R5" s="7" t="inlineStr">
-        <is>
-          <t>Warming down to sleep</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>Lamplit and settling</t>
-        </is>
-      </c>
-      <c r="T5" s="7" t="inlineStr">
-        <is>
-          <t>Steam, stone, amber light</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Slip into a provincial Roman bathhouse at the gentlest hour of its day, just as the crowds drift home and the attendants light the evening lamps. Walk the warm rooms in their proper order, stand on a floor heated by a fire nobody sees, and listen to water that has been arriving from the hills without pause for a hundred years. Along the way, the bronze strigil and the oil, Seneca's famous list of bathhouse noises, the spring in Britain where the earth itself stokes the furnace, and the banked fire that will breathe warmth under the mosaics all night long.</t>
-        </is>
-      </c>
-      <c r="V5" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W5" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X5" s="7" t="inlineStr">
@@ -1208,7 +1206,7 @@
       </c>
       <c r="Z5" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA5" s="9" t="inlineStr">
@@ -1253,27 +1251,27 @@
       </c>
       <c r="AI5" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ5" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK5" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL5" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM5" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN5" s="9" t="inlineStr">
@@ -1341,7 +1339,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Read by Emma from Oxford</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -1376,7 +1374,7 @@
         </is>
       </c>
       <c r="P6" s="8" t="n">
-        <v>2640</v>
+        <v>2401</v>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
@@ -1490,7 +1488,7 @@
       </c>
       <c r="AM6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN6" s="9" t="inlineStr">
@@ -1515,7 +1513,7 @@
       </c>
       <c r="AR6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AS6" s="9" t="inlineStr">
@@ -1558,7 +1556,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Sleep Stories by AVP</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -1593,7 +1591,7 @@
         </is>
       </c>
       <c r="P7" s="8" t="n">
-        <v>2690</v>
+        <v>2588</v>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
@@ -1707,7 +1705,7 @@
       </c>
       <c r="AM7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN7" s="9" t="inlineStr">
@@ -1732,7 +1730,7 @@
       </c>
       <c r="AR7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AS7" s="9" t="inlineStr">
@@ -1750,7 +1748,7 @@
       <c r="B8" s="7" t="inlineStr"/>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1775,7 +1773,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -1809,44 +1807,42 @@
           <t>C98A6B</t>
         </is>
       </c>
-      <c r="P8" s="8" t="inlineStr">
+      <c r="P8" s="8" t="n">
+        <v>2435</v>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>Nothing out there is waiting for anything. The columns simply stand in the light, giving themselves up to it slowly, and they will go on standing long after tonight.</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>Feeling small and safe</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>Slow and drifting</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>Cold, dusty, lit from above</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>You rise from your own roof and travel outward, past every planet, until the stars themselves begin to thicken into a glowing cloud. Three dark columns stand in the middle of it, each one taller than the gap between our sun and its nearest neighbour. You learn what they are made of, how starlight is quietly carving them, why they are pillars at all, and what is forming in the pockets of shadow inside. Then the light goes on arriving, as it has for six thousand years, and you let all of it go.</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>Nothing out there is waiting for anything. The columns simply stand in the light, giving themselves up to it slowly, and they will go on standing long after tonight.</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>Feeling small and safe</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>Slow and drifting</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>Cold, dusty, lit from above</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>You rise from your own roof and travel outward, past every planet, until the stars themselves begin to thicken into a glowing cloud. Three dark columns stand in the middle of it, each one taller than the gap between our sun and its nearest neighbour. You learn what they are made of, how starlight is quietly carving them, why they are pillars at all, and what is forming in the pockets of shadow inside. Then the light goes on arriving, as it has for six thousand years, and you let all of it go.</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W8" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X8" s="7" t="inlineStr">
@@ -1861,7 +1857,7 @@
       </c>
       <c r="Z8" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA8" s="9" t="inlineStr">
@@ -1906,27 +1902,27 @@
       </c>
       <c r="AI8" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ8" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK8" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL8" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM8" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN8" s="9" t="inlineStr">
@@ -1969,7 +1965,7 @@
       <c r="B9" s="7" t="inlineStr"/>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1994,7 +1990,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -2028,44 +2024,42 @@
           <t>8E9FD0</t>
         </is>
       </c>
-      <c r="P9" s="8" t="inlineStr">
+      <c r="P9" s="8" t="n">
+        <v>2364</v>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>The largest arrangement there is, and it does nothing in any hurry. It was found by people writing down one number a night, and none of it needs your attention tonight.</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>Ending a long day</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>Slow, wide, still</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>Vast, dark, quiet, patient</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>Sit in a cold dome in Arizona in the 1980s, while somebody points a telescope at one faint smudge after another and writes down a number. Do that for years, plot the results, and a shape appears that nobody expected — galaxies strung along threads, gathered at knots, wrapped around enormous quiet rooms with almost nothing inside. Along the way, the mule driver who became one of the great observers, a sound from the early universe frozen into the sky as a ruler, and five thousand small robots that rearrange themselves in the dark.</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>The largest arrangement there is, and it does nothing in any hurry. It was found by people writing down one number a night, and none of it needs your attention tonight.</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>Ending a long day</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>Slow, wide, still</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>Vast, dark, quiet, patient</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>Sit in a cold dome in Arizona in the 1980s, while somebody points a telescope at one faint smudge after another and writes down a number. Do that for years, plot the results, and a shape appears that nobody expected — galaxies strung along threads, gathered at knots, wrapped around enormous quiet rooms with almost nothing inside. Along the way, the mule driver who became one of the great observers, a sound from the early universe frozen into the sky as a ruler, and five thousand small robots that rearrange themselves in the dark.</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W9" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X9" s="7" t="inlineStr">
@@ -2080,7 +2074,7 @@
       </c>
       <c r="Z9" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA9" s="9" t="inlineStr">
@@ -2125,27 +2119,27 @@
       </c>
       <c r="AI9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN9" s="9" t="inlineStr">
@@ -2213,7 +2207,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -2248,7 +2242,7 @@
         </is>
       </c>
       <c r="P10" s="8" t="n">
-        <v>2174</v>
+        <v>2394</v>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
@@ -2282,7 +2276,7 @@
       </c>
       <c r="W10" s="7" t="inlineStr">
         <is>
-          <t>ElevenLabs_the-bakery-before-dawn.wav</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X10" s="7" t="inlineStr">
@@ -2362,7 +2356,7 @@
       </c>
       <c r="AM10" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN10" s="9" t="inlineStr">
@@ -2405,7 +2399,7 @@
       <c r="B11" s="7" t="inlineStr"/>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2430,7 +2424,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Brian from St Ives</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -2464,44 +2458,42 @@
           <t>63D9F2</t>
         </is>
       </c>
-      <c r="P11" s="8" t="inlineStr">
+      <c r="P11" s="8" t="n">
+        <v>2637</v>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>No moon tonight, and that is the point. The paddle rests, the water glows wherever the fish go, and a whole island keeps its darkness like a garden.</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>Dimming a busy mind</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>Adrift and moonless</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>Warm dark, blue sparks</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>Glide out through a tunnel of mangroves onto the brightest glowing bay in the world, on a night with no moon. Learn how a single living cell, one of seven hundred thousand in every gallon, keeps a tiny pantry of light and opens it at a touch. Watch fish write comet trails, hold a handful of blue stars, and float between two skies while warm rain sets the whole surface flickering. With Darwin at the ship's rail, the rare milky seas that glow from horizon to horizon, and an island community that tends its darkness the way other towns tend their gardens.</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>No moon tonight, and that is the point. The paddle rests, the water glows wherever the fish go, and a whole island keeps its darkness like a garden.</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>Dimming a busy mind</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>Adrift and moonless</t>
-        </is>
-      </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>Warm dark, blue sparks</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>Glide out through a tunnel of mangroves onto the brightest glowing bay in the world, on a night with no moon. Learn how a single living cell, one of seven hundred thousand in every gallon, keeps a tiny pantry of light and opens it at a touch. Watch fish write comet trails, hold a handful of blue stars, and float between two skies while warm rain sets the whole surface flickering. With Darwin at the ship's rail, the rare milky seas that glow from horizon to horizon, and an island community that tends its darkness the way other towns tend their gardens.</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W11" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X11" s="7" t="inlineStr">
@@ -2516,7 +2508,7 @@
       </c>
       <c r="Z11" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA11" s="9" t="inlineStr">
@@ -2561,27 +2553,27 @@
       </c>
       <c r="AI11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN11" s="9" t="inlineStr">
@@ -2624,7 +2616,7 @@
       <c r="B12" s="7" t="inlineStr"/>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -2649,7 +2641,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -2683,44 +2675,42 @@
           <t>C9A2C8</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="P12" s="8" t="n">
+        <v>2308</v>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>Sixty years done, eighty to go, and every person on the site content with that arithmetic. Nothing in your life needs finishing by morning either.</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>Setting worries down</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>Generational and calm</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>Stone, dusk, gold, chant</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>Walk into a thirteenth-century city at dusk, where the largest unfinished thing in the world has been rising for sixty years and will not be done for eighty more. Visit the lodge where stone dust turns gold in the doorway light, and the plaster tracing floor where three generations of masters have scratched their thinking at full size. Learn why the pointed arch lets stone float, how a timber centering is struck and a vault suddenly holds itself, and why lime mortar sets the pace of the whole century. Then watch the site put itself to bed, wrapped in straw against the frost, still quietly turning back into stone in the dark.</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>Sixty years done, eighty to go, and every person on the site content with that arithmetic. Nothing in your life needs finishing by morning either.</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>Setting worries down</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>Generational and calm</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>Stone, dusk, gold, chant</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>Walk into a thirteenth-century city at dusk, where the largest unfinished thing in the world has been rising for sixty years and will not be done for eighty more. Visit the lodge where stone dust turns gold in the doorway light, and the plaster tracing floor where three generations of masters have scratched their thinking at full size. Learn why the pointed arch lets stone float, how a timber centering is struck and a vault suddenly holds itself, and why lime mortar sets the pace of the whole century. Then watch the site put itself to bed, wrapped in straw against the frost, still quietly turning back into stone in the dark.</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W12" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X12" s="7" t="inlineStr">
@@ -2735,7 +2725,7 @@
       </c>
       <c r="Z12" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA12" s="9" t="inlineStr">
@@ -2780,27 +2770,27 @@
       </c>
       <c r="AI12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN12" s="9" t="inlineStr">
@@ -2843,7 +2833,7 @@
       <c r="B13" s="7" t="inlineStr"/>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2868,7 +2858,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -2902,44 +2892,42 @@
           <t>C98F3D</t>
         </is>
       </c>
-      <c r="P13" s="8" t="inlineStr">
+      <c r="P13" s="8" t="n">
+        <v>2376</v>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>The shop is locked, the lamp is out, and every pendulum keeps its small agreement in the dark. Nobody has to keep time while they sleep. It is being handled.</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>Ticking down to rest</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>Once a second, forever</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>Brass, oil, a hundred ticks</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>Step through a door with a brass bell into a small-town shop where a hundred clocks tick softly out of step, like rain on a roof. At the bench, an unhurried craftsman tends a movement of polished wheels with tools that have not changed in two centuries. Learn what a clock really is, a falling weight let down slowly over a week, and why two clocks on the same wall drift into perfect step with each other, a mystery first noticed from a sickbed in 1665. With painted moon dials, a drawer of orphaned keys that all fit something somewhere, winding day, house calls taken over tea, and the repairers' names penciled inside case doors, a century apart.</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>The shop is locked, the lamp is out, and every pendulum keeps its small agreement in the dark. Nobody has to keep time while they sleep. It is being handled.</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>Ticking down to rest</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>Once a second, forever</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>Brass, oil, a hundred ticks</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>Step through a door with a brass bell into a small-town shop where a hundred clocks tick softly out of step, like rain on a roof. At the bench, an unhurried craftsman tends a movement of polished wheels with tools that have not changed in two centuries. Learn what a clock really is, a falling weight let down slowly over a week, and why two clocks on the same wall drift into perfect step with each other, a mystery first noticed from a sickbed in 1665. With painted moon dials, a drawer of orphaned keys that all fit something somewhere, winding day, house calls taken over tea, and the repairers' names penciled inside case doors, a century apart.</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W13" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X13" s="7" t="inlineStr">
@@ -2954,7 +2942,7 @@
       </c>
       <c r="Z13" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA13" s="9" t="inlineStr">
@@ -2999,27 +2987,27 @@
       </c>
       <c r="AI13" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ13" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK13" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL13" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM13" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN13" s="9" t="inlineStr">
@@ -3062,7 +3050,7 @@
       <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -3087,7 +3075,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Read by Brian from St Ives</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -3121,44 +3109,42 @@
           <t>5FA8C4</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="8" t="n">
+        <v>2409</v>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>One slow direction, downward, and nothing waiting at the end of it. An easy thing to follow, and an easier thing to let go of.</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>Letting the day end</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>Slow and sinking</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>Dark, cool, weightless</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>You slip beneath a starlit sea and sink, without effort, through the sunlit water and the long blue twilight into a darkness the sun has never reached. Small living lights blink on and drift away. Marine snow falls, soft and endless, all the way down to a floor of pale sediment older than memory. Further down still lie the trenches, where the pressure feels only like stillness and there is nowhere deeper to go.</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>One slow direction, downward, and nothing waiting at the end of it. An easy thing to follow, and an easier thing to let go of.</t>
-        </is>
-      </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>Letting the day end</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>Slow and sinking</t>
-        </is>
-      </c>
-      <c r="T14" s="7" t="inlineStr">
-        <is>
-          <t>Dark, cool, weightless</t>
-        </is>
-      </c>
-      <c r="U14" s="7" t="inlineStr">
-        <is>
-          <t>You slip beneath a starlit sea and sink, without effort, through the sunlit water and the long blue twilight into a darkness the sun has never reached. Small living lights blink on and drift away. Marine snow falls, soft and endless, all the way down to a floor of pale sediment older than memory. Further down still lie the trenches, where the pressure feels only like stillness and there is nowhere deeper to go.</t>
-        </is>
-      </c>
-      <c r="V14" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W14" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X14" s="7" t="inlineStr">
@@ -3173,7 +3159,7 @@
       </c>
       <c r="Z14" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA14" s="9" t="inlineStr">
@@ -3218,27 +3204,27 @@
       </c>
       <c r="AI14" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ14" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK14" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL14" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM14" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN14" s="9" t="inlineStr">
@@ -3281,7 +3267,7 @@
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -3306,7 +3292,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -3340,44 +3326,42 @@
           <t>D9A55C</t>
         </is>
       </c>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="P15" s="8" t="n">
+        <v>2159</v>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>Nothing here is urgent and nothing needs remembering. Only scribes at their tables, copying one careful line at a time.</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>Slowing a busy day</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>Slow, unhurried</t>
+        </is>
+      </c>
+      <c r="T15" s="7" t="inlineStr">
+        <is>
+          <t>Warm, dusty, lamplit</t>
+        </is>
+      </c>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>You arrive at a harbour in the evening, when the light is going gold and the sea wind is moving up through the streets. Inside the cool halls, thousands of scrolls lie in their niches, and scribes copy them by hand, one careful line at a time. You learn how papyrus was pressed from river reeds, how ink was made from soot, how the first catalogue was written, and how a man measured the whole earth from the length of a shadow. Then the lamps are lit, and the work is set down.</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>Nothing here is urgent and nothing needs remembering. Only scribes at their tables, copying one careful line at a time.</t>
-        </is>
-      </c>
-      <c r="R15" s="7" t="inlineStr">
-        <is>
-          <t>Slowing a busy day</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>Slow, unhurried</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>Warm, dusty, lamplit</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>You arrive at a harbour in the evening, when the light is going gold and the sea wind is moving up through the streets. Inside the cool halls, thousands of scrolls lie in their niches, and scribes copy them by hand, one careful line at a time. You learn how papyrus was pressed from river reeds, how ink was made from soot, how the first catalogue was written, and how a man measured the whole earth from the length of a shadow. Then the lamps are lit, and the work is set down.</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W15" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X15" s="7" t="inlineStr">
@@ -3392,7 +3376,7 @@
       </c>
       <c r="Z15" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA15" s="9" t="inlineStr">
@@ -3437,27 +3421,27 @@
       </c>
       <c r="AI15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN15" s="9" t="inlineStr">
@@ -3500,7 +3484,7 @@
       <c r="B16" s="7" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -3525,7 +3509,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -3559,44 +3543,42 @@
           <t>C4B49A</t>
         </is>
       </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="P16" s="8" t="n">
+        <v>2226</v>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>Nothing here was ever nailed, so nothing is ever finished. It has been taken apart and put back together for thirteen hundred years, and none of it needs watching tonight.</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>Putting the day down</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>Careful and unhurried</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>Wooden, misty, still, warm</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>Stand in a raked gravel courtyard at dawn and look up at a building with no nails in it. No screws, no brackets, nothing but wood cut to hold wood. Along the way, the joint that grips harder the more you load it, the carpenter who said to buy the mountain rather than the timber, a central pillar that holds up nothing and rests loose on a stone, and roof bark peeled from living trees that grow it back in ten years. And at Ise, a shrine rebuilt from new wood every twenty years for thirteen centuries, because twenty years is the length of human memory.</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>Nothing here was ever nailed, so nothing is ever finished. It has been taken apart and put back together for thirteen hundred years, and none of it needs watching tonight.</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>Putting the day down</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>Careful and unhurried</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr">
-        <is>
-          <t>Wooden, misty, still, warm</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>Stand in a raked gravel courtyard at dawn and look up at a building with no nails in it. No screws, no brackets, nothing but wood cut to hold wood. Along the way, the joint that grips harder the more you load it, the carpenter who said to buy the mountain rather than the timber, a central pillar that holds up nothing and rests loose on a stone, and roof bark peeled from living trees that grow it back in ten years. And at Ise, a shrine rebuilt from new wood every twenty years for thirteen centuries, because twenty years is the length of human memory.</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W16" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X16" s="7" t="inlineStr">
@@ -3611,7 +3593,7 @@
       </c>
       <c r="Z16" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA16" s="9" t="inlineStr">
@@ -3656,27 +3638,27 @@
       </c>
       <c r="AI16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN16" s="9" t="inlineStr">
@@ -3719,7 +3701,7 @@
       <c r="B17" s="7" t="inlineStr"/>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -3744,7 +3726,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -3778,44 +3760,42 @@
           <t>7FD0C9</t>
         </is>
       </c>
-      <c r="P17" s="8" t="inlineStr">
+      <c r="P17" s="8" t="n">
+        <v>2360</v>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>Water never has to choose. It goes the one way it can go, at whatever pace it is given, and tonight you can go with it, downhill the whole way.</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>Drifting downstream</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>Downhill, all the way</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>Blue ice, cold water, calm</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>Follow a single snowflake from a windless high snowfield down to the salt water, a journey of two centuries in one direction only. Be buried into blue glacier ice with a breath of old sky sealed inside, ride the slowest river there is, and emerge at the ice cave where the young river is born, milky with the flour of ground mountains. Then down through the braided gravel plains, into a turquoise lake that sorts the sunlight, through pine forests where a small brown bird walks underwater, and out at last across the mudflats to the sea, where the sun is already lifting the water to begin again.</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>Water never has to choose. It goes the one way it can go, at whatever pace it is given, and tonight you can go with it, downhill the whole way.</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>Drifting downstream</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>Downhill, all the way</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>Blue ice, cold water, calm</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>Follow a single snowflake from a windless high snowfield down to the salt water, a journey of two centuries in one direction only. Be buried into blue glacier ice with a breath of old sky sealed inside, ride the slowest river there is, and emerge at the ice cave where the young river is born, milky with the flour of ground mountains. Then down through the braided gravel plains, into a turquoise lake that sorts the sunlight, through pine forests where a small brown bird walks underwater, and out at last across the mudflats to the sea, where the sun is already lifting the water to begin again.</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W17" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X17" s="7" t="inlineStr">
@@ -3830,7 +3810,7 @@
       </c>
       <c r="Z17" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA17" s="9" t="inlineStr">
@@ -3875,27 +3855,27 @@
       </c>
       <c r="AI17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN17" s="9" t="inlineStr">
@@ -3938,7 +3918,7 @@
       <c r="B18" s="7" t="inlineStr"/>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -3963,7 +3943,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -3997,44 +3977,42 @@
           <t>D97A55</t>
         </is>
       </c>
-      <c r="P18" s="8" t="inlineStr">
+      <c r="P18" s="8" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>Not one red dwarf has ever run down. The universe is far too young. Every single one ever made is still quietly burning, and none of it needs watching tonight.</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>Unwinding without hurry</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>Low, warm, unchanging</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>Dim, orange, warm, endless</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>Travel four light years to Proxima Centauri, a small orange star so dim you could look straight at it, and so ordinary that three quarters of the galaxy is made of stars like it. Inside, the whole body slowly turns itself over, which is why it will still be burning in ten trillion years. Along the way, why nature makes far more small stars than large ones, the women at Harvard who sorted the spectra by hand, the titanium chemistry that survives in a star's atmosphere, and the quiet fact that not one red dwarf anywhere has ever finished.</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>Not one red dwarf has ever run down. The universe is far too young. Every single one ever made is still quietly burning, and none of it needs watching tonight.</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>Unwinding without hurry</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>Low, warm, unchanging</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>Dim, orange, warm, endless</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>Travel four light years to Proxima Centauri, a small orange star so dim you could look straight at it, and so ordinary that three quarters of the galaxy is made of stars like it. Inside, the whole body slowly turns itself over, which is why it will still be burning in ten trillion years. Along the way, why nature makes far more small stars than large ones, the women at Harvard who sorted the spectra by hand, the titanium chemistry that survives in a star's atmosphere, and the quiet fact that not one red dwarf anywhere has ever finished.</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W18" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X18" s="7" t="inlineStr">
@@ -4049,7 +4027,7 @@
       </c>
       <c r="Z18" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA18" s="9" t="inlineStr">
@@ -4094,27 +4072,27 @@
       </c>
       <c r="AI18" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ18" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK18" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL18" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM18" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN18" s="9" t="inlineStr">
@@ -4157,7 +4135,7 @@
       <c r="B19" s="7" t="inlineStr"/>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -4182,7 +4160,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -4216,44 +4194,42 @@
           <t>D9B36C</t>
         </is>
       </c>
-      <c r="P19" s="8" t="inlineStr">
+      <c r="P19" s="8" t="n">
+        <v>2404</v>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>The signals are turning green all the way to the lake, and the attendant is awake so you need not be. The train knows the rest, and none of it is your business tonight.</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>Being gently carried</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>Rocking and westward</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>Warm, amber, moonlit, moving</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>Board the midnight-blue sleeper in Vienna, hand your passport to the attendant, and let the train do the rest. Cross the Alps in a rocking berth while borders pass over you like weather, carriages are quietly sorted toward separate mornings, and a freight train washes past in the dark. Along the way, why the clickety-clack disappeared when the rails were welded into seamless miles, the 1884 tunnel bored from both ends to meet like a handshake, and the whole quiet profession of people who stay awake so that everyone else can sleep at seventy miles an hour.</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>The signals are turning green all the way to the lake, and the attendant is awake so you need not be. The train knows the rest, and none of it is your business tonight.</t>
-        </is>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>Being gently carried</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>Rocking and westward</t>
-        </is>
-      </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>Warm, amber, moonlit, moving</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>Board the midnight-blue sleeper in Vienna, hand your passport to the attendant, and let the train do the rest. Cross the Alps in a rocking berth while borders pass over you like weather, carriages are quietly sorted toward separate mornings, and a freight train washes past in the dark. Along the way, why the clickety-clack disappeared when the rails were welded into seamless miles, the 1884 tunnel bored from both ends to meet like a handshake, and the whole quiet profession of people who stay awake so that everyone else can sleep at seventy miles an hour.</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W19" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -4268,7 +4244,7 @@
       </c>
       <c r="Z19" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA19" s="9" t="inlineStr">
@@ -4313,27 +4289,27 @@
       </c>
       <c r="AI19" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ19" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK19" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL19" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM19" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN19" s="9" t="inlineStr">
@@ -4376,7 +4352,7 @@
       <c r="B20" s="7" t="inlineStr"/>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -4401,7 +4377,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -4435,44 +4411,42 @@
           <t>9FC8DA</t>
         </is>
       </c>
-      <c r="P20" s="8" t="inlineStr">
+      <c r="P20" s="8" t="n">
+        <v>2369</v>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>There is no light down there and there never has been. The water simply turns over in the dark, as it has for a very long time, and none of it needs watching tonight.</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr">
+        <is>
+          <t>Sinking into sleep</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>Quiet and downward</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
+        <is>
+          <t>Cold, white, deep, quiet</t>
+        </is>
+      </c>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>You travel out past Mars to a banded planet eleven times the width of the Earth, and find four small worlds standing beside it in a line. The second one is white, smooth as a billiard ball, and cracked all over like a glazed bowl. You learn why it has almost no craters, how a tiny wobble in its orbit keeps an ocean liquid where nothing should be, and how that ocean was found from the outside without anyone touching it. Then you sink through the ice into water that has never once seen light.</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>There is no light down there and there never has been. The water simply turns over in the dark, as it has for a very long time, and none of it needs watching tonight.</t>
-        </is>
-      </c>
-      <c r="R20" s="7" t="inlineStr">
-        <is>
-          <t>Sinking into sleep</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>Quiet and downward</t>
-        </is>
-      </c>
-      <c r="T20" s="7" t="inlineStr">
-        <is>
-          <t>Cold, white, deep, quiet</t>
-        </is>
-      </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>You travel out past Mars to a banded planet eleven times the width of the Earth, and find four small worlds standing beside it in a line. The second one is white, smooth as a billiard ball, and cracked all over like a glazed bowl. You learn why it has almost no craters, how a tiny wobble in its orbit keeps an ocean liquid where nothing should be, and how that ocean was found from the outside without anyone touching it. Then you sink through the ice into water that has never once seen light.</t>
-        </is>
-      </c>
-      <c r="V20" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W20" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X20" s="7" t="inlineStr">
@@ -4487,7 +4461,7 @@
       </c>
       <c r="Z20" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA20" s="9" t="inlineStr">
@@ -4532,27 +4506,27 @@
       </c>
       <c r="AI20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN20" s="9" t="inlineStr">
@@ -4595,7 +4569,7 @@
       <c r="B21" s="7" t="inlineStr"/>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -4620,7 +4594,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Read by Patrick from Block Island, Rhode Island</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -4654,44 +4628,42 @@
           <t>B9C9CE</t>
         </is>
       </c>
-      <c r="P21" s="8" t="inlineStr">
+      <c r="P21" s="8" t="n">
+        <v>2418</v>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>Somebody is awake on a mountain, taking a reading on the hour, whether or not you are. The next one is not yours, and it will be taken anyway.</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>Letting go of the day</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>Hourly and unhurried</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>Cold, lamplit, patient</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>You climb into the cloud that sits on the highest ground in Britain, and step through a low stone door into lamplight, a warm stove, and a kettle that is always on. For twenty-one years, somebody here walked out into the weather every hour of every night and wrote down what it was doing. You learn how a wet sleeve of muslin measures the dryness of the air, why the thermometer boxes had to be lifted as the snow came up to meet them, and how ice grows sideways into the wind. Then the lamp is turned low, a wet coat goes on the hook, and the mountain carries on without you.</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>Somebody is awake on a mountain, taking a reading on the hour, whether or not you are. The next one is not yours, and it will be taken anyway.</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>Letting go of the day</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>Hourly and unhurried</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>Cold, lamplit, patient</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>You climb into the cloud that sits on the highest ground in Britain, and step through a low stone door into lamplight, a warm stove, and a kettle that is always on. For twenty-one years, somebody here walked out into the weather every hour of every night and wrote down what it was doing. You learn how a wet sleeve of muslin measures the dryness of the air, why the thermometer boxes had to be lifted as the snow came up to meet them, and how ice grows sideways into the wind. Then the lamp is turned low, a wet coat goes on the hook, and the mountain carries on without you.</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W21" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X21" s="7" t="inlineStr">
@@ -4706,7 +4678,7 @@
       </c>
       <c r="Z21" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA21" s="9" t="inlineStr">
@@ -4731,7 +4703,7 @@
       </c>
       <c r="AE21" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AF21" s="9" t="inlineStr">
@@ -4751,27 +4723,27 @@
       </c>
       <c r="AI21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN21" s="9" t="inlineStr">
@@ -4839,7 +4811,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -4874,7 +4846,7 @@
         </is>
       </c>
       <c r="P22" s="8" t="n">
-        <v>2125.557</v>
+        <v>2298</v>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
@@ -4908,7 +4880,7 @@
       </c>
       <c r="W22" s="7" t="inlineStr">
         <is>
-          <t>ElevenLabs_the-rings-of-saturn-v2.wav</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X22" s="7" t="inlineStr">
@@ -5031,7 +5003,7 @@
       <c r="B23" s="7" t="inlineStr"/>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -5056,7 +5028,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Patrick from Block Island, Rhode Island</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -5090,44 +5062,42 @@
           <t>A8C3A0</t>
         </is>
       </c>
-      <c r="P23" s="8" t="inlineStr">
+      <c r="P23" s="8" t="n">
+        <v>2431</v>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>The grove waters itself with fog while everyone sleeps, and has done for two thousand summers. Nothing in it moves faster than a slug, and nothing needs watching tonight.</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>Quieting a full mind</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>Soft, green, ancient</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>Foggy, hushed, deep green</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Walk into a coastal grove at dusk and stand at the foot of a tree over three hundred feet tall, wrapped in a foot of soft bark, older than the cathedrals. Follow one unbroken thread of water from the roots to the highest needle, and wait for the summer fog to roll in off the cold Pacific so the forest can water itself in the dark. Along the way, roots that graft into their neighbours and hold each other up, rings of trees standing where their elders stood, a ghost-white redwood fed by its family, and a garden of ferns and huckleberries growing a metre deep in the crown.</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>The grove waters itself with fog while everyone sleeps, and has done for two thousand summers. Nothing in it moves faster than a slug, and nothing needs watching tonight.</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>Quieting a full mind</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>Soft, green, ancient</t>
-        </is>
-      </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>Foggy, hushed, deep green</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>Walk into a coastal grove at dusk and stand at the foot of a tree over three hundred feet tall, wrapped in a foot of soft bark, older than the cathedrals. Follow one unbroken thread of water from the roots to the highest needle, and wait for the summer fog to roll in off the cold Pacific so the forest can water itself in the dark. Along the way, roots that graft into their neighbours and hold each other up, rings of trees standing where their elders stood, a ghost-white redwood fed by its family, and a garden of ferns and huckleberries growing a metre deep in the crown.</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W23" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X23" s="7" t="inlineStr">
@@ -5142,7 +5112,7 @@
       </c>
       <c r="Z23" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA23" s="9" t="inlineStr">
@@ -5167,7 +5137,7 @@
       </c>
       <c r="AE23" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AF23" s="9" t="inlineStr">
@@ -5187,27 +5157,27 @@
       </c>
       <c r="AI23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN23" s="9" t="inlineStr">
@@ -5250,7 +5220,7 @@
       <c r="B24" s="7" t="inlineStr"/>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -5275,7 +5245,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -5309,44 +5279,42 @@
           <t>C7B27A</t>
         </is>
       </c>
-      <c r="P24" s="8" t="inlineStr">
+      <c r="P24" s="8" t="n">
+        <v>2290</v>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>It left in 1977 and it is not going anywhere in particular. It is simply still going, steadily, and none of it needs watching tonight.</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr">
+        <is>
+          <t>Settling into the quiet</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>Steady and outward</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr">
+        <is>
+          <t>Dark, distant, gold, calm</t>
+        </is>
+      </c>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>Follow the most distant object people have ever made, out past Jupiter and Saturn and into the space between the stars. A gold record bolted to its side, a transmitter no brighter than a refrigerator bulb, and a whisper of radio that takes almost a full day to reach a dish in the Australian grass. Along the way, the gentle theft of a gravity assist, the choice to look at Titan, and the faint steady hum the gas out there turns out to make. Nothing about it is urgent. Nothing about it ever was.</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>It left in 1977 and it is not going anywhere in particular. It is simply still going, steadily, and none of it needs watching tonight.</t>
-        </is>
-      </c>
-      <c r="R24" s="7" t="inlineStr">
-        <is>
-          <t>Settling into the quiet</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>Steady and outward</t>
-        </is>
-      </c>
-      <c r="T24" s="7" t="inlineStr">
-        <is>
-          <t>Dark, distant, gold, calm</t>
-        </is>
-      </c>
-      <c r="U24" s="7" t="inlineStr">
-        <is>
-          <t>Follow the most distant object people have ever made, out past Jupiter and Saturn and into the space between the stars. A gold record bolted to its side, a transmitter no brighter than a refrigerator bulb, and a whisper of radio that takes almost a full day to reach a dish in the Australian grass. Along the way, the gentle theft of a gravity assist, the choice to look at Titan, and the faint steady hum the gas out there turns out to make. Nothing about it is urgent. Nothing about it ever was.</t>
-        </is>
-      </c>
-      <c r="V24" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="W24" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>master.wav</t>
         </is>
       </c>
       <c r="X24" s="7" t="inlineStr">
@@ -5361,7 +5329,7 @@
       </c>
       <c r="Z24" s="9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA24" s="9" t="inlineStr">
@@ -5406,27 +5374,27 @@
       </c>
       <c r="AI24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AJ24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AK24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AM24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AN24" s="9" t="inlineStr">

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Story Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Story Tracker'!$A$3:$AS$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Story Tracker'!$A$3:$AS$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS24"/>
+  <dimension ref="A1:AS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3478,7 +3478,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>the-joinery-of-japan-s-wooden-temples</t>
+          <t>the-hidden-clocks-of-the-night-sky</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3499,22 +3499,22 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>The Joinery of Japan's Wooden Temples</t>
+          <t>The Hidden Clocks of the Night Sky</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Thirteen centuries of buildings held together by shape alone, and not one nail</t>
+          <t>Stars, moonlight, and slow planets, each quietly keeping their own kind of time</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Read by Arthur from Ludlow</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>ancient-worlds</t>
+          <t>cosmic-journeys</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr"/>
@@ -3535,40 +3535,40 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>1E241C</t>
+          <t>121A2E</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>C4B49A</t>
+          <t>D9C9A0</t>
         </is>
       </c>
       <c r="P16" s="8" t="n">
-        <v>2226</v>
+        <v>1148</v>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>Nothing here was ever nailed, so nothing is ever finished. It has been taken apart and put back together for thirteen hundred years, and none of it needs watching tonight.</t>
+          <t>The sky above your roof is the oldest clock there is, and it has never once run down or needed you to watch it. Let it keep the hour tonight. You can simply rest.</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>Putting the day down</t>
+          <t>Watching the sky turn</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>Careful and unhurried</t>
+          <t>Slow, wide, unhurried</t>
         </is>
       </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
-          <t>Wooden, misty, still, warm</t>
+          <t>Starlit, quiet, vast</t>
         </is>
       </c>
       <c r="U16" s="7" t="inlineStr">
         <is>
-          <t>Stand in a raked gravel courtyard at dawn and look up at a building with no nails in it. No screws, no brackets, nothing but wood cut to hold wood. Along the way, the joint that grips harder the more you load it, the carpenter who said to buy the mountain rather than the timber, a central pillar that holds up nothing and rests loose on a stone, and roof bark peeled from living trees that grow it back in ten years. And at Ise, a shrine rebuilt from new wood every twenty years for thirteen centuries, because twenty years is the length of human memory.</t>
+          <t>You lie back in a dark meadow and read the oldest clock there is: the night sky. The whole dome of stars turns once a day around a quiet pole star. The moon counts twenty-nine nights and tows the tides behind it. Five wandering planets keep their own slow paces, one of them lending its name to Saturday. Starlight even comes in colors that tell a star's age, blue youth to red old age. And beneath every quick hand, one wobble of the Earth's axis takes twenty-six thousand years to complete, mid-tick since before the first cities rose. None of these clocks needs winding, watching, or you.</t>
         </is>
       </c>
       <c r="V16" s="7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AQ16" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AR16" s="9" t="inlineStr">
@@ -3688,14 +3688,14 @@
       </c>
       <c r="AS16" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-joinery-of-japan-s-wooden-temples/story.yaml</t>
+          <t>Stories/the-hidden-clocks-of-the-night-sky/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>the-journey-of-a-glacial-river</t>
+          <t>the-joinery-of-japan-s-wooden-temples</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr"/>
@@ -3716,22 +3716,22 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>The Journey of a Glacial River</t>
+          <t>The Joinery of Japan's Wooden Temples</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>One snowflake's two-hundred-year trip from a silent snowfield to the sea</t>
+          <t>Thirteen centuries of buildings held together by shape alone, and not one nail</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Read by Niamh from Kinsale</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr"/>
@@ -3752,40 +3752,40 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>0F2230</t>
+          <t>1E241C</t>
         </is>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>7FD0C9</t>
+          <t>C4B49A</t>
         </is>
       </c>
       <c r="P17" s="8" t="n">
-        <v>2360</v>
+        <v>2226</v>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>Water never has to choose. It goes the one way it can go, at whatever pace it is given, and tonight you can go with it, downhill the whole way.</t>
+          <t>Nothing here was ever nailed, so nothing is ever finished. It has been taken apart and put back together for thirteen hundred years, and none of it needs watching tonight.</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>Drifting downstream</t>
+          <t>Putting the day down</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>Downhill, all the way</t>
+          <t>Careful and unhurried</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>Blue ice, cold water, calm</t>
+          <t>Wooden, misty, still, warm</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
-          <t>Follow a single snowflake from a windless high snowfield down to the salt water, a journey of two centuries in one direction only. Be buried into blue glacier ice with a breath of old sky sealed inside, ride the slowest river there is, and emerge at the ice cave where the young river is born, milky with the flour of ground mountains. Then down through the braided gravel plains, into a turquoise lake that sorts the sunlight, through pine forests where a small brown bird walks underwater, and out at last across the mudflats to the sea, where the sun is already lifting the water to begin again.</t>
+          <t>Stand in a raked gravel courtyard at dawn and look up at a building with no nails in it. No screws, no brackets, nothing but wood cut to hold wood. Along the way, the joint that grips harder the more you load it, the carpenter who said to buy the mountain rather than the timber, a central pillar that holds up nothing and rests loose on a stone, and roof bark peeled from living trees that grow it back in ten years. And at Ise, a shrine rebuilt from new wood every twenty years for thirteen centuries, because twenty years is the length of human memory.</t>
         </is>
       </c>
       <c r="V17" s="7" t="inlineStr">
@@ -3905,14 +3905,14 @@
       </c>
       <c r="AS17" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-journey-of-a-glacial-river/story.yaml</t>
+          <t>Stories/the-joinery-of-japan-s-wooden-temples/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>the-life-cycle-of-a-red-dwarf-star</t>
+          <t>the-journey-of-a-glacial-river</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr"/>
@@ -3933,22 +3933,22 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>The Life Cycle of a Red Dwarf Star</t>
+          <t>The Journey of a Glacial River</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>The commonest star in the galaxy, burning so slowly that none has ever finished</t>
+          <t>One snowflake's two-hundred-year trip from a silent snowfield to the sea</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr"/>
@@ -3969,40 +3969,40 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>1C1013</t>
+          <t>0F2230</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>D97A55</t>
+          <t>7FD0C9</t>
         </is>
       </c>
       <c r="P18" s="8" t="n">
-        <v>2341</v>
+        <v>2360</v>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>Not one red dwarf has ever run down. The universe is far too young. Every single one ever made is still quietly burning, and none of it needs watching tonight.</t>
+          <t>Water never has to choose. It goes the one way it can go, at whatever pace it is given, and tonight you can go with it, downhill the whole way.</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>Unwinding without hurry</t>
+          <t>Drifting downstream</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>Low, warm, unchanging</t>
+          <t>Downhill, all the way</t>
         </is>
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>Dim, orange, warm, endless</t>
+          <t>Blue ice, cold water, calm</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
         <is>
-          <t>Travel four light years to Proxima Centauri, a small orange star so dim you could look straight at it, and so ordinary that three quarters of the galaxy is made of stars like it. Inside, the whole body slowly turns itself over, which is why it will still be burning in ten trillion years. Along the way, why nature makes far more small stars than large ones, the women at Harvard who sorted the spectra by hand, the titanium chemistry that survives in a star's atmosphere, and the quiet fact that not one red dwarf anywhere has ever finished.</t>
+          <t>Follow a single snowflake from a windless high snowfield down to the salt water, a journey of two centuries in one direction only. Be buried into blue glacier ice with a breath of old sky sealed inside, ride the slowest river there is, and emerge at the ice cave where the young river is born, milky with the flour of ground mountains. Then down through the braided gravel plains, into a turquoise lake that sorts the sunlight, through pine forests where a small brown bird walks underwater, and out at last across the mudflats to the sea, where the sun is already lifting the water to begin again.</t>
         </is>
       </c>
       <c r="V18" s="7" t="inlineStr">
@@ -4122,14 +4122,14 @@
       </c>
       <c r="AS18" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-life-cycle-of-a-red-dwarf-star/story.yaml</t>
+          <t>Stories/the-journey-of-a-glacial-river/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>the-midnight-sleeper-train-across-the-alps</t>
+          <t>the-life-cycle-of-a-red-dwarf-star</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr"/>
@@ -4150,22 +4150,22 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>The Midnight Sleeper Train Across the Alps</t>
+          <t>The Life Cycle of a Red Dwarf Star</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>A warm berth, a folder of sleeping passports, and mountains passing in the dark</t>
+          <t>The commonest star in the galaxy, burning so slowly that none has ever finished</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Read by Niamh from Kinsale</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>cozy-tales</t>
+          <t>cosmic-journeys</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -4186,40 +4186,40 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>151A2E</t>
+          <t>1C1013</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>D9B36C</t>
+          <t>D97A55</t>
         </is>
       </c>
       <c r="P19" s="8" t="n">
-        <v>2404</v>
+        <v>2341</v>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>The signals are turning green all the way to the lake, and the attendant is awake so you need not be. The train knows the rest, and none of it is your business tonight.</t>
+          <t>Not one red dwarf has ever run down. The universe is far too young. Every single one ever made is still quietly burning, and none of it needs watching tonight.</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>Being gently carried</t>
+          <t>Unwinding without hurry</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>Rocking and westward</t>
+          <t>Low, warm, unchanging</t>
         </is>
       </c>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>Warm, amber, moonlit, moving</t>
+          <t>Dim, orange, warm, endless</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
         <is>
-          <t>Board the midnight-blue sleeper in Vienna, hand your passport to the attendant, and let the train do the rest. Cross the Alps in a rocking berth while borders pass over you like weather, carriages are quietly sorted toward separate mornings, and a freight train washes past in the dark. Along the way, why the clickety-clack disappeared when the rails were welded into seamless miles, the 1884 tunnel bored from both ends to meet like a handshake, and the whole quiet profession of people who stay awake so that everyone else can sleep at seventy miles an hour.</t>
+          <t>Travel four light years to Proxima Centauri, a small orange star so dim you could look straight at it, and so ordinary that three quarters of the galaxy is made of stars like it. Inside, the whole body slowly turns itself over, which is why it will still be burning in ten trillion years. Along the way, why nature makes far more small stars than large ones, the women at Harvard who sorted the spectra by hand, the titanium chemistry that survives in a star's atmosphere, and the quiet fact that not one red dwarf anywhere has ever finished.</t>
         </is>
       </c>
       <c r="V19" s="7" t="inlineStr">
@@ -4339,14 +4339,14 @@
       </c>
       <c r="AS19" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-midnight-sleeper-train-across-the-alps/story.yaml</t>
+          <t>Stories/the-life-cycle-of-a-red-dwarf-star/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>the-moons-of-jupiter-europa-s-ice-and-ocean</t>
+          <t>the-lighthouse-on-the-windswept-island</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -4367,22 +4367,22 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>The Moons of Jupiter: Europa's Ice and Ocean</t>
+          <t>The Lighthouse on the Windswept Island</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>A small cracked moon of ice, and the dark ocean turning over beneath it</t>
+          <t>A keeper winds the weight, lights the lens, and keeps the coast safe till dawn</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Read by Patrick from Block Island, Rhode Island</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -4403,40 +4403,40 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>0E1A2B</t>
+          <t>1B2A33</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>9FC8DA</t>
+          <t>E8B84B</t>
         </is>
       </c>
       <c r="P20" s="8" t="n">
-        <v>2369</v>
+        <v>1468</v>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>There is no light down there and there never has been. The water simply turns over in the dark, as it has for a very long time, and none of it needs watching tonight.</t>
+          <t>Somewhere on a cold coast tonight, a lighthouse keeper is turning a great patient light so that strangers can pass safely by. You are as watched-over as any ship out there.</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>Sinking into sleep</t>
+          <t>Feeling watched over</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>Quiet and downward</t>
+          <t>Steady and slow</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Cold, white, deep, quiet</t>
+          <t>Granite, lamplight, rain</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
         <is>
-          <t>You travel out past Mars to a banded planet eleven times the width of the Earth, and find four small worlds standing beside it in a line. The second one is white, smooth as a billiard ball, and cracked all over like a glazed bowl. You learn why it has almost no craters, how a tiny wobble in its orbit keeps an ocean liquid where nothing should be, and how that ocean was found from the outside without anyone touching it. Then you sink through the ice into water that has never once seen light.</t>
+          <t>You climb a windswept island to a granite lighthouse, where a keeper is beginning his night watch. Ninety-nine steps up, past the watch room, to a great Fresnel lens turning on a bath of mercury, sweeping one long beam over the sea. Below, a snug round room holds a stove, an armchair, and a logbook of a hundred years of nights that all end the same reassuring way: all well. Rain arrives off the sea and streams down the tower in one continuous whisper, and out in the dark a coaster's mate counts the flashes and marks his position, never once thinking of the tower keeping him safe.</t>
         </is>
       </c>
       <c r="V20" s="7" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AF20" s="9" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="AQ20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AR20" s="9" t="inlineStr">
@@ -4556,14 +4556,14 @@
       </c>
       <c r="AS20" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-moons-of-jupiter-europa-s-ice-and-ocean/story.yaml</t>
+          <t>Stories/the-lighthouse-on-the-windswept-island/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>the-observatory-on-ben-nevis</t>
+          <t>the-long-way-home-a-slow-evening-journey</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr"/>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -4584,17 +4584,17 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>The Observatory on Ben Nevis</t>
+          <t>The Long Way Home: A Slow Evening Journey</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Twenty-one years of hourly weather readings, taken by lamplight inside a cloud</t>
+          <t>A quiet walk down a coast road, through a sleeping village, to a banked fire</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Read by Patrick from Block Island, Rhode Island</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -4620,40 +4620,40 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>1F2A2E</t>
+          <t>2B2E3A</t>
         </is>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>B9C9CE</t>
+          <t>E4703C</t>
         </is>
       </c>
       <c r="P21" s="8" t="n">
-        <v>2418</v>
+        <v>2032</v>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>Somebody is awake on a mountain, taking a reading on the hour, whether or not you are. The next one is not yours, and it will be taken anyway.</t>
+          <t>There is no adventure in tonight's walk, only lanes and hedges and a lamp left burning in a window for whoever is still out. That lamp is for you too.</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>Letting go of the day</t>
+          <t>Walking off the day</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>Hourly and unhurried</t>
+          <t>Unhurried, step by ste</t>
         </is>
       </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>Cold, lamplit, patient</t>
+          <t>Coastal, hedgerowed, hushed</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
         <is>
-          <t>You climb into the cloud that sits on the highest ground in Britain, and step through a low stone door into lamplight, a warm stove, and a kettle that is always on. For twenty-one years, somebody here walked out into the weather every hour of every night and wrote down what it was doing. You learn how a wet sleeve of muslin measures the dryness of the air, why the thermometer boxes had to be lifted as the snow came up to meet them, and how ice grows sideways into the wind. Then the lamp is turned low, a wet coat goes on the hook, and the mountain carries on without you.</t>
+          <t>You walk the long way home down an Irish coast road at dusk, with the sea keeping pace on one side and stone walls built to let the wind through on the other. The road passes a small harbor of knocking boats, a bridge over a talking stream, and a sleeping village where lamplight goes window by window from white to amber to out. Soft rain arrives in the hedges, right on time. A lamp burns in a neighbor's window for late travelers, an old coastal custom, and at last a whitewashed house appears with its own window lit, its turf fire banked low and patient under its ash, waiting to be climbed into.</t>
         </is>
       </c>
       <c r="V21" s="7" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="AE21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AF21" s="9" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AK21" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AL21" s="9" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AQ21" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AR21" s="9" t="inlineStr">
@@ -4773,50 +4773,50 @@
       </c>
       <c r="AS21" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-observatory-on-ben-nevis/story.yaml</t>
+          <t>Stories/the-long-way-home-a-slow-evening-journey/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>the-rings-of-saturn</t>
+          <t>the-medieval-inn-at-candlemas</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr"/>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>The Rings of Saturn</t>
+          <t>The Medieval Inn at Candlemas</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Ten metres of ice, two hundred thousand kilometres wide, turning in silence</t>
+          <t>A traveler arrives at a fourteenth-century wayside inn on the feast of the returning light</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr"/>
@@ -4827,55 +4827,55 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14T17:53:16Z</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>1B2436</t>
+          <t>241A12</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>E8C89A</t>
+          <t>E0A855</t>
         </is>
       </c>
       <c r="P22" s="8" t="n">
-        <v>2298</v>
+        <v>1606</v>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>A long way from anything that has ever asked something of you. Nothing out here is in a hurry, and none of it needs watching.</t>
+          <t>Six centuries ago, a bell rang a whole valley to bed, fires were banked under clay covers, and travelers slept easy, all facing one fire. Borrow that old, whole kind of night.</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>Drifting off slowly</t>
+          <t>Settling in after travel</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>Slow and weightless</t>
+          <t>Slow and fireside</t>
         </is>
       </c>
       <c r="T22" s="7" t="inlineStr">
         <is>
-          <t>Cold, vast, silent</t>
+          <t>Candlelit, timbered, snowy</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
         <is>
-          <t>You rise gently from your own roof and travel outward, past the Moon and Jupiter, until a tilted gold shape appears in the dark. Up close the rings resolve into thousands of fine bright lines, and then into ice: billions of frozen pieces, some finer than dust and some the size of mountains, all drifting the same way at once. You watch small moons carve clean lanes and raise slow waves behind them, hear a gentle unfinished argument about how old it all is, and then settle into the ring plane and stay.</t>
+          <t>You ride into a fourteenth-century wayside inn on Candlemas, the old feast of blessed candles marking winter's turn. A green bush over the door promises ale, beds, and fire, and inside, strangers share one hearth, a thick pottage, and low unimportant talk. At curfew the innkeeper covers the fire under a clay dome, candles are pinched out one by one, and the village church bell rings the valley to rest. Upstairs under a thick thatch roof, travelers share a chamber the old way, speaking of first sleep and second sleep as easily as dinner and supper, while outside, in perfect silence, it begins to snow.</t>
         </is>
       </c>
       <c r="V22" s="7" t="inlineStr">
         <is>
-          <t>audio-the-rings-of-saturn-en-v2-aac96</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="W22" s="7" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="Z22" s="9" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AA22" s="9" t="inlineStr">
         <is>
-          <t>READY</t>
+          <t>NOT READY</t>
         </is>
       </c>
       <c r="AB22" s="9" t="inlineStr">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="AG22" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AH22" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AI22" s="9" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AK22" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AL22" s="9" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="AN22" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AO22" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AP22" s="9" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="AQ22" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AR22" s="9" t="inlineStr">
@@ -4990,14 +4990,14 @@
       </c>
       <c r="AS22" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-rings-of-saturn/story.yaml</t>
+          <t>Stories/the-medieval-inn-at-candlemas/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>the-slow-life-of-a-redwood</t>
+          <t>the-midnight-museum-beneath-the-sea</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr"/>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -5018,17 +5018,17 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>The Slow Life of a Redwood</t>
+          <t>The Midnight Museum Beneath the Sea</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>A night in the fog with the tallest living things there have ever been</t>
+          <t>A slow descent through the deep ocean's glowing halls of glass, light, and patient history</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Read by Patrick from Block Island, Rhode Island</t>
+          <t>Read by Brian from St Ives</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -5054,40 +5054,40 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>14201A</t>
+          <t>071826</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>A8C3A0</t>
+          <t>4FD1C5</t>
         </is>
       </c>
       <c r="P23" s="8" t="n">
-        <v>2431</v>
+        <v>1197</v>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>The grove waters itself with fog while everyone sleeps, and has done for two thousand summers. Nothing in it moves faster than a slug, and nothing needs watching tonight.</t>
+          <t>A hundred million years of quiet lives below the waves, lit by their own small lamps, needing nothing from anyone. Tonight you get to drift through it and rest.</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>Quieting a full mind</t>
+          <t>Sinking into stillness</t>
         </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>Soft, green, ancient</t>
+          <t>Slow, weightless drift</t>
         </is>
       </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>Foggy, hushed, deep green</t>
+          <t>Deep, glowing, silent</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">
         <is>
-          <t>Walk into a coastal grove at dusk and stand at the foot of a tree over three hundred feet tall, wrapped in a foot of soft bark, older than the cathedrals. Follow one unbroken thread of water from the roots to the highest needle, and wait for the summer fog to roll in off the cold Pacific so the forest can water itself in the dark. Along the way, roots that graft into their neighbours and hold each other up, rings of trees standing where their elders stood, a ghost-white redwood fed by its family, and a garden of ferns and huckleberries growing a metre deep in the crown.</t>
+          <t>You sink through the ocean's floors of light, from sunlit gold down through a deep cathedral blue into the midnight zone, where nine of ten creatures make their own cold light to say here I am. You drift past a lanternfish's blinking rows, an anglerfish's small warm lamp, and glass sponges that have filtered the same gentle current for ten thousand years. Marine snow falls without pause through halls holding an old ship and a whale fall's soft, fed city, all the way down to a trench floor where a small pink snailfish is entirely at home. The museum keeps everything for you until morning, softly, with its own lamps.</t>
         </is>
       </c>
       <c r="V23" s="7" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="AE23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AF23" s="9" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AQ23" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AR23" s="9" t="inlineStr">
@@ -5207,14 +5207,14 @@
       </c>
       <c r="AS23" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-slow-life-of-a-redwood/story.yaml</t>
+          <t>Stories/the-midnight-museum-beneath-the-sea/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>voyager-1-a-journey-to-interstellar-space</t>
+          <t>the-midnight-sleeper-train-across-the-alps</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr"/>
@@ -5235,22 +5235,22 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Voyager 1: A Journey to Interstellar Space</t>
+          <t>The Midnight Sleeper Train Across the Alps</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>A small gold machine, forty-nine years out, still quietly drifting away from us</t>
+          <t>A warm berth, a folder of sleeping passports, and mountains passing in the dark</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr"/>
@@ -5271,165 +5271,1467 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
+          <t>151A2E</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>D9B36C</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>2404</v>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>The signals are turning green all the way to the lake, and the attendant is awake so you need not be. The train knows the rest, and none of it is your business tonight.</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr">
+        <is>
+          <t>Being gently carried</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>Rocking and westward</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr">
+        <is>
+          <t>Warm, amber, moonlit, moving</t>
+        </is>
+      </c>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>Board the midnight-blue sleeper in Vienna, hand your passport to the attendant, and let the train do the rest. Cross the Alps in a rocking berth while borders pass over you like weather, carriages are quietly sorted toward separate mornings, and a freight train washes past in the dark. Along the way, why the clickety-clack disappeared when the rails were welded into seamless miles, the 1884 tunnel bored from both ends to meet like a handshake, and the whole quiet profession of people who stay awake so that everyone else can sleep at seventy miles an hour.</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>master.wav</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
+        </is>
+      </c>
+      <c r="Z24" s="9" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="AA24" s="9" t="inlineStr">
+        <is>
+          <t>NOT READY</t>
+        </is>
+      </c>
+      <c r="AB24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AH24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AI24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AO24" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AP24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS24" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-midnight-sleeper-train-across-the-alps/story.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>the-moons-of-jupiter-europa-s-ice-and-ocean</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>The Moons of Jupiter: Europa's Ice and Ocean</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>A small cracked moon of ice, and the dark ocean turning over beneath it</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Read by Amy from Greenwich</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>cosmic-journeys</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>0E1A2B</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>9FC8DA</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>2369</v>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>There is no light down there and there never has been. The water simply turns over in the dark, as it has for a very long time, and none of it needs watching tonight.</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>Sinking into sleep</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>Quiet and downward</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr">
+        <is>
+          <t>Cold, white, deep, quiet</t>
+        </is>
+      </c>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>You travel out past Mars to a banded planet eleven times the width of the Earth, and find four small worlds standing beside it in a line. The second one is white, smooth as a billiard ball, and cracked all over like a glazed bowl. You learn why it has almost no craters, how a tiny wobble in its orbit keeps an ocean liquid where nothing should be, and how that ocean was found from the outside without anyone touching it. Then you sink through the ice into water that has never once seen light.</t>
+        </is>
+      </c>
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>master.wav</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
+        </is>
+      </c>
+      <c r="Z25" s="9" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="AA25" s="9" t="inlineStr">
+        <is>
+          <t>NOT READY</t>
+        </is>
+      </c>
+      <c r="AB25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG25" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AH25" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AI25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN25" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AO25" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AP25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS25" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-moons-of-jupiter-europa-s-ice-and-ocean/story.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>the-observatory-on-ben-nevis</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr"/>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>The Observatory on Ben Nevis</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Twenty-one years of hourly weather readings, taken by lamplight inside a cloud</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Read by Patrick from Block Island, Rhode Island</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>cozy-tales</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>1F2A2E</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>B9C9CE</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>2418</v>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>Somebody is awake on a mountain, taking a reading on the hour, whether or not you are. The next one is not yours, and it will be taken anyway.</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr">
+        <is>
+          <t>Letting go of the day</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>Hourly and unhurried</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr">
+        <is>
+          <t>Cold, lamplit, patient</t>
+        </is>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>You climb into the cloud that sits on the highest ground in Britain, and step through a low stone door into lamplight, a warm stove, and a kettle that is always on. For twenty-one years, somebody here walked out into the weather every hour of every night and wrote down what it was doing. You learn how a wet sleeve of muslin measures the dryness of the air, why the thermometer boxes had to be lifted as the snow came up to meet them, and how ice grows sideways into the wind. Then the lamp is turned low, a wet coat goes on the hook, and the mountain carries on without you.</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W26" s="7" t="inlineStr">
+        <is>
+          <t>master.wav</t>
+        </is>
+      </c>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
+        </is>
+      </c>
+      <c r="Z26" s="9" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="AA26" s="9" t="inlineStr">
+        <is>
+          <t>NOT READY</t>
+        </is>
+      </c>
+      <c r="AB26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE26" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AF26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG26" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AH26" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AI26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN26" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AO26" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AP26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS26" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-observatory-on-ben-nevis/story.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>the-quiet-observatory-questions-about-time</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr"/>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>The Quiet Observatory: Questions About Time</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>A gentle night among telescopes, old clocks, and the soft, bending nature of time itself</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Read by Emma from Oxford</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>cosmic-journeys</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>141B2E</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>C9D6E8</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>2115</v>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>Time only flows, never hurries, never waits. Tonight it is only asking you to lie still while it carries you, the way it has carried every sleeper before you.</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>Quieting a busy mind</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>Slow and thoughtful</t>
+        </is>
+      </c>
+      <c r="T27" s="7" t="inlineStr">
+        <is>
+          <t>Starlit, hushed, timeless</t>
+        </is>
+      </c>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>You climb a small hill to a small observatory to spend the night with the gentlest big question there is: what is time. A telescope shows that starlight is an old patient archive, arriving from a hundred different pasts all at once, and that there is no single now shared by the whole universe. Pendulum clocks, water clocks, and candle clocks each try to hang a bucket in a stream that never pools. A carpenter's son builds four clocks to solve longitude at sea, a hill at Greenwich becomes the world's meridian, and modern clocks now count the hum inside an atom. At the end, the astronomer closes the logbook with one word, closed, and so can you.</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>master.wav</t>
+        </is>
+      </c>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
+        </is>
+      </c>
+      <c r="Z27" s="9" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="AA27" s="9" t="inlineStr">
+        <is>
+          <t>NOT READY</t>
+        </is>
+      </c>
+      <c r="AB27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG27" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AH27" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AI27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK27" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AL27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN27" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AO27" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AP27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ27" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AR27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS27" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-quiet-observatory-questions-about-time/story.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>the-rings-of-saturn</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr"/>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>The Rings of Saturn</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Ten metres of ice, two hundred thousand kilometres wide, turning in silence</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Read by Amy from Greenwich</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>cosmic-journeys</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14T17:53:16Z</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>1B2436</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>E8C89A</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>2298</v>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>A long way from anything that has ever asked something of you. Nothing out here is in a hurry, and none of it needs watching.</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>Drifting off slowly</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>Slow and weightless</t>
+        </is>
+      </c>
+      <c r="T28" s="7" t="inlineStr">
+        <is>
+          <t>Cold, vast, silent</t>
+        </is>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>You rise gently from your own roof and travel outward, past the Moon and Jupiter, until a tilted gold shape appears in the dark. Up close the rings resolve into thousands of fine bright lines, and then into ice: billions of frozen pieces, some finer than dust and some the size of mountains, all drifting the same way at once. You watch small moons carve clean lanes and raise slow waves behind them, hear a gentle unfinished argument about how old it all is, and then settle into the ring plane and stay.</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-rings-of-saturn-en-v2-aac96</t>
+        </is>
+      </c>
+      <c r="W28" s="7" t="inlineStr">
+        <is>
+          <t>master.wav</t>
+        </is>
+      </c>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="Y28" s="7" t="inlineStr">
+        <is>
+          <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
+        </is>
+      </c>
+      <c r="Z28" s="9" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="AA28" s="9" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="AB28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AH28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AI28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AO28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AP28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS28" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-rings-of-saturn/story.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>the-slow-life-of-a-redwood</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr"/>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>The Slow Life of a Redwood</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>A night in the fog with the tallest living things there have ever been</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Read by Patrick from Block Island, Rhode Island</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>gentle-nature</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>14201A</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>A8C3A0</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>2431</v>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>The grove waters itself with fog while everyone sleeps, and has done for two thousand summers. Nothing in it moves faster than a slug, and nothing needs watching tonight.</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr">
+        <is>
+          <t>Quieting a full mind</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>Soft, green, ancient</t>
+        </is>
+      </c>
+      <c r="T29" s="7" t="inlineStr">
+        <is>
+          <t>Foggy, hushed, deep green</t>
+        </is>
+      </c>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>Walk into a coastal grove at dusk and stand at the foot of a tree over three hundred feet tall, wrapped in a foot of soft bark, older than the cathedrals. Follow one unbroken thread of water from the roots to the highest needle, and wait for the summer fog to roll in off the cold Pacific so the forest can water itself in the dark. Along the way, roots that graft into their neighbours and hold each other up, rings of trees standing where their elders stood, a ghost-white redwood fed by its family, and a garden of ferns and huckleberries growing a metre deep in the crown.</t>
+        </is>
+      </c>
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W29" s="7" t="inlineStr">
+        <is>
+          <t>master.wav</t>
+        </is>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="Y29" s="7" t="inlineStr">
+        <is>
+          <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
+        </is>
+      </c>
+      <c r="Z29" s="9" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="AA29" s="9" t="inlineStr">
+        <is>
+          <t>NOT READY</t>
+        </is>
+      </c>
+      <c r="AB29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE29" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AF29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG29" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AH29" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AI29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN29" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AO29" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AP29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS29" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-slow-life-of-a-redwood/story.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>voyager-1-a-journey-to-interstellar-space</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr"/>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Voyager 1: A Journey to Interstellar Space</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>A small gold machine, forty-nine years out, still quietly drifting away from us</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Read by Amy from Greenwich</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>cosmic-journeys</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
           <t>0A0F1C</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>C7B27A</t>
         </is>
       </c>
-      <c r="P24" s="8" t="n">
+      <c r="P30" s="8" t="n">
         <v>2290</v>
       </c>
-      <c r="Q24" s="7" t="inlineStr">
+      <c r="Q30" s="7" t="inlineStr">
         <is>
           <t>It left in 1977 and it is not going anywhere in particular. It is simply still going, steadily, and none of it needs watching tonight.</t>
         </is>
       </c>
-      <c r="R24" s="7" t="inlineStr">
+      <c r="R30" s="7" t="inlineStr">
         <is>
           <t>Settling into the quiet</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>Steady and outward</t>
         </is>
       </c>
-      <c r="T24" s="7" t="inlineStr">
+      <c r="T30" s="7" t="inlineStr">
         <is>
           <t>Dark, distant, gold, calm</t>
         </is>
       </c>
-      <c r="U24" s="7" t="inlineStr">
+      <c r="U30" s="7" t="inlineStr">
         <is>
           <t>Follow the most distant object people have ever made, out past Jupiter and Saturn and into the space between the stars. A gold record bolted to its side, a transmitter no brighter than a refrigerator bulb, and a whisper of radio that takes almost a full day to reach a dish in the Australian grass. Along the way, the gentle theft of a gravity assist, the choice to look at Titan, and the faint steady hum the gas out there turns out to make. Nothing about it is urgent. Nothing about it ever was.</t>
         </is>
       </c>
-      <c r="V24" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="W24" s="7" t="inlineStr">
+      <c r="V30" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W30" s="7" t="inlineStr">
         <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X24" s="7" t="inlineStr">
+      <c r="X30" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y24" s="7" t="inlineStr">
+      <c r="Y30" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z24" s="9" t="inlineStr">
+      <c r="Z30" s="9" t="inlineStr">
         <is>
           <t>rendered</t>
         </is>
       </c>
-      <c r="AA24" s="9" t="inlineStr">
+      <c r="AA30" s="9" t="inlineStr">
         <is>
           <t>NOT READY</t>
         </is>
       </c>
-      <c r="AB24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AE24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AF24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AG24" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AH24" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AI24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AJ24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AK24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AL24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AM24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AN24" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AO24" s="9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="AP24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AQ24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AR24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AS24" s="9" t="inlineStr">
+      <c r="AB30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AC30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG30" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AH30" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AI30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN30" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AO30" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AP30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS30" s="9" t="inlineStr">
         <is>
           <t>Stories/voyager-1-a-journey-to-interstellar-space/story.yaml</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AS24"/>
+  <autoFilter ref="A3:AS30"/>
   <mergeCells count="6">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A2:B2"/>
@@ -5438,7 +6740,7 @@
     <mergeCell ref="A1:AS1"/>
     <mergeCell ref="F2:Y2"/>
   </mergeCells>
-  <conditionalFormatting sqref="AB5:AS24">
+  <conditionalFormatting sqref="AB5:AS30">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"FAIL"</formula>
     </cfRule>
@@ -5446,7 +6748,7 @@
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA5:AA24">
+  <conditionalFormatting sqref="AA5:AA30">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"READY"</formula>
     </cfRule>
@@ -5454,31 +6756,31 @@
       <formula>"NOT READY"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D24">
+  <conditionalFormatting sqref="D5:D30">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"PENDING"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="C5:C64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="workflowStatus" prompt="Pipeline stage." type="list" errorStyle="stop">
+    <dataValidation sqref="C5:C70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="workflowStatus" prompt="Pipeline stage." type="list" errorStyle="stop">
       <formula1>"draft,rendered,qa-approved,staging,published"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="accessDecision" prompt="Free vs premium. Settle before staging." type="list" errorStyle="stop">
+    <dataValidation sqref="D5:D70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="accessDecision" prompt="Free vs premium. Settle before staging." type="list" errorStyle="stop">
       <formula1>"PENDING,free,premium"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_1" prompt="Existing genre IDs only." type="list" errorStyle="stop">
+    <dataValidation sqref="I5:I70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_1" prompt="Existing genre IDs only." type="list" errorStyle="stop">
       <formula1>"ancient-worlds,gentle-nature,cosmic-journeys,cozy-tales"</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_2" prompt="Existing genre IDs only." type="list" errorStyle="stop">
+    <dataValidation sqref="J5:J70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_2" prompt="Existing genre IDs only." type="list" errorStyle="stop">
       <formula1>"ancient-worlds,gentle-nature,cosmic-journeys,cozy-tales"</formula1>
     </dataValidation>
-    <dataValidation sqref="X5:X64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="commercialRightsStatus" prompt="Must be verified to publish." type="list" errorStyle="stop">
+    <dataValidation sqref="X5:X70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="commercialRightsStatus" prompt="Must be verified to publish." type="list" errorStyle="stop">
       <formula1>"pending-verification,verified,restricted"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="trialPreviewEligible" prompt="true or false." type="list" errorStyle="stop">
+    <dataValidation sqref="K5:K70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="trialPreviewEligible" prompt="true or false." type="list" errorStyle="stop">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="isFeatured" prompt="true or false." type="list" errorStyle="stop">
+    <dataValidation sqref="L5:L70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="isFeatured" prompt="true or false." type="list" errorStyle="stop">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -6202,7 +6202,7 @@
       </c>
       <c r="AA28" s="9" t="inlineStr">
         <is>
-          <t>READY</t>
+          <t>NOT READY</t>
         </is>
       </c>
       <c r="AB28" s="9" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="AN28" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AO28" s="9" t="inlineStr">

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AQ16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AR16" s="9" t="inlineStr">
@@ -4357,14 +4357,14 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
           <t>The Lighthouse on the Windswept Island</t>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Read by Patrick from Block Island, Rhode Island</t>
+          <t>Read by Patrick, Block Island</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AE20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AF20" s="9" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="AQ20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AR20" s="9" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AK21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL21" s="9" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AQ21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AR21" s="9" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AK22" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL22" s="9" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="AQ22" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AR22" s="9" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AQ23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AR23" s="9" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Read by Patrick from Block Island, Rhode Island</t>
+          <t>Read by Patrick, Block Island</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="AE26" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AF26" s="9" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="AK27" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AL27" s="9" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AQ27" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AR27" s="9" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Read by Patrick from Block Island, Rhode Island</t>
+          <t>Read by Patrick, Block Island</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AE29" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AF29" s="9" t="inlineStr">

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -1097,7 +1097,7 @@
       <c r="B5" s="7" t="inlineStr"/>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="V5" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-a-roman-bathhouse-at-closing-time-en-v1-aac96</t>
         </is>
       </c>
       <c r="W5" s="7" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="Z5" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA5" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB5" s="9" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="AG5" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH5" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI5" s="9" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="AN5" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO5" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP5" s="9" t="inlineStr">
@@ -1314,7 +1314,7 @@
       <c r="B6" s="7" t="inlineStr"/>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>staging</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>audio-aristotle-en-v1-aac96</t>
+          <t>audio-aristotle-en-v2-aac96</t>
         </is>
       </c>
       <c r="W6" s="7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="Z6" s="9" t="inlineStr">
         <is>
-          <t>staging</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA6" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB6" s="9" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AH6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI6" s="9" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="AN6" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO6" s="9" t="inlineStr">
@@ -1531,7 +1531,7 @@
       <c r="B7" s="7" t="inlineStr"/>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>staging</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="V7" s="7" t="inlineStr">
         <is>
-          <t>audio-dinosaurs-en-v1-aac96</t>
+          <t>audio-dinosaurs-en-v2-aac96</t>
         </is>
       </c>
       <c r="W7" s="7" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="Z7" s="9" t="inlineStr">
         <is>
-          <t>staging</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA7" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB7" s="9" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AH7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI7" s="9" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AN7" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO7" s="9" t="inlineStr">
@@ -1748,7 +1748,7 @@
       <c r="B8" s="7" t="inlineStr"/>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="V8" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-floating-through-the-pillars-of-creation-en-v1-aac96</t>
         </is>
       </c>
       <c r="W8" s="7" t="inlineStr">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="Z8" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA8" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB8" s="9" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AG8" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH8" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI8" s="9" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="AN8" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO8" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP8" s="9" t="inlineStr">
@@ -1965,7 +1965,7 @@
       <c r="B9" s="7" t="inlineStr"/>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="V9" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-mapping-the-cosmic-web-en-v1-aac96</t>
         </is>
       </c>
       <c r="W9" s="7" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="Z9" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA9" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB9" s="9" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="AG9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI9" s="9" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="AN9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO9" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP9" s="9" t="inlineStr">
@@ -2182,7 +2182,7 @@
       <c r="B10" s="7" t="inlineStr"/>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>staging</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="V10" s="7" t="inlineStr">
         <is>
-          <t>audio-the-bakery-before-dawn-en-v1-aac96</t>
+          <t>audio-the-bakery-before-dawn-en-v2-aac96</t>
         </is>
       </c>
       <c r="W10" s="7" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="Z10" s="9" t="inlineStr">
         <is>
-          <t>staging</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA10" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB10" s="9" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AH10" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI10" s="9" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AN10" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO10" s="9" t="inlineStr">
@@ -2399,7 +2399,7 @@
       <c r="B11" s="7" t="inlineStr"/>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="V11" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-bay-that-glows-at-night-en-v1-aac96</t>
         </is>
       </c>
       <c r="W11" s="7" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="Z11" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA11" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB11" s="9" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="AG11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI11" s="9" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="AN11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO11" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP11" s="9" t="inlineStr">
@@ -2616,7 +2616,7 @@
       <c r="B12" s="7" t="inlineStr"/>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="V12" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-building-of-a-cathedral-en-v1-aac96</t>
         </is>
       </c>
       <c r="W12" s="7" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="Z12" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA12" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB12" s="9" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="AG12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI12" s="9" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AN12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP12" s="9" t="inlineStr">
@@ -2833,7 +2833,7 @@
       <c r="B13" s="7" t="inlineStr"/>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="V13" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-clockmaker-s-workshop-en-v1-aac96</t>
         </is>
       </c>
       <c r="W13" s="7" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="Z13" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA13" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB13" s="9" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="AG13" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH13" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI13" s="9" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="AN13" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO13" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP13" s="9" t="inlineStr">
@@ -3050,7 +3050,7 @@
       <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="V14" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-deep-ocean-trenches-en-v1-aac96</t>
         </is>
       </c>
       <c r="W14" s="7" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="Z14" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA14" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB14" s="9" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="AG14" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH14" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI14" s="9" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AN14" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO14" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP14" s="9" t="inlineStr">
@@ -3267,7 +3267,7 @@
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="V15" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-great-library-of-alexandria-en-v1-aac96</t>
         </is>
       </c>
       <c r="W15" s="7" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="Z15" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA15" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB15" s="9" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="AG15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI15" s="9" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="AN15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP15" s="9" t="inlineStr">
@@ -3484,7 +3484,7 @@
       <c r="B16" s="7" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="V16" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-hidden-clocks-of-the-night-sky-en-v1-aac96</t>
         </is>
       </c>
       <c r="W16" s="7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="Z16" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA16" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB16" s="9" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="AG16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI16" s="9" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="AN16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO16" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP16" s="9" t="inlineStr">
@@ -3701,7 +3701,7 @@
       <c r="B17" s="7" t="inlineStr"/>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="V17" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-joinery-of-japan-s-wooden-temples-en-v1-aac96</t>
         </is>
       </c>
       <c r="W17" s="7" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="Z17" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA17" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB17" s="9" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="AG17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI17" s="9" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="AN17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP17" s="9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       <c r="B18" s="7" t="inlineStr"/>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="V18" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-journey-of-a-glacial-river-en-v1-aac96</t>
         </is>
       </c>
       <c r="W18" s="7" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="Z18" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA18" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB18" s="9" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="AG18" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH18" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI18" s="9" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AN18" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO18" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP18" s="9" t="inlineStr">
@@ -4135,7 +4135,7 @@
       <c r="B19" s="7" t="inlineStr"/>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="V19" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-life-cycle-of-a-red-dwarf-star-en-v1-aac96</t>
         </is>
       </c>
       <c r="W19" s="7" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="Z19" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA19" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB19" s="9" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="AG19" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH19" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI19" s="9" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="AN19" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO19" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP19" s="9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       <c r="B20" s="7" t="inlineStr"/>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="V20" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-lighthouse-on-the-windswept-island-en-v1-aac96</t>
         </is>
       </c>
       <c r="W20" s="7" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="Z20" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA20" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB20" s="9" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="AG20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI20" s="9" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="AN20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO20" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP20" s="9" t="inlineStr">
@@ -4569,7 +4569,7 @@
       <c r="B21" s="7" t="inlineStr"/>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="V21" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-long-way-home-a-slow-evening-journey-en-v1-aac96</t>
         </is>
       </c>
       <c r="W21" s="7" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="Z21" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA21" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB21" s="9" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="AG21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI21" s="9" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="AN21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO21" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP21" s="9" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="B22" s="7" t="inlineStr"/>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="V22" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-medieval-inn-at-candlemas-en-v1-aac96</t>
         </is>
       </c>
       <c r="W22" s="7" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="Z22" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA22" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB22" s="9" t="inlineStr">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="AG22" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH22" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI22" s="9" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="AN22" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO22" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP22" s="9" t="inlineStr">
@@ -5003,7 +5003,7 @@
       <c r="B23" s="7" t="inlineStr"/>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="V23" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-midnight-museum-beneath-the-sea-en-v1-aac96</t>
         </is>
       </c>
       <c r="W23" s="7" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="Z23" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA23" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB23" s="9" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="AG23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI23" s="9" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="AN23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP23" s="9" t="inlineStr">
@@ -5220,7 +5220,7 @@
       <c r="B24" s="7" t="inlineStr"/>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="V24" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-midnight-sleeper-train-across-the-alps-en-v1-aac96</t>
         </is>
       </c>
       <c r="W24" s="7" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Z24" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA24" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB24" s="9" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="AG24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI24" s="9" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="AN24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP24" s="9" t="inlineStr">
@@ -5437,7 +5437,7 @@
       <c r="B25" s="7" t="inlineStr"/>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="V25" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-moons-of-jupiter-europa-s-ice-and-ocean-en-v1-aac96</t>
         </is>
       </c>
       <c r="W25" s="7" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="Z25" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA25" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB25" s="9" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="AG25" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH25" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI25" s="9" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="AN25" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO25" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP25" s="9" t="inlineStr">
@@ -5654,7 +5654,7 @@
       <c r="B26" s="7" t="inlineStr"/>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="V26" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-observatory-on-ben-nevis-en-v1-aac96</t>
         </is>
       </c>
       <c r="W26" s="7" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="Z26" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA26" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB26" s="9" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="AG26" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH26" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI26" s="9" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AN26" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO26" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP26" s="9" t="inlineStr">
@@ -5871,7 +5871,7 @@
       <c r="B27" s="7" t="inlineStr"/>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="V27" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-quiet-observatory-questions-about-time-en-v1-aac96</t>
         </is>
       </c>
       <c r="W27" s="7" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="Z27" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA27" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB27" s="9" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="AG27" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH27" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI27" s="9" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="AN27" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO27" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP27" s="9" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="V28" s="7" t="inlineStr">
         <is>
-          <t>audio-the-rings-of-saturn-en-v2-aac96</t>
+          <t>audio-the-rings-of-saturn-en-v3-aac96</t>
         </is>
       </c>
       <c r="W28" s="7" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="AA28" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB28" s="9" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="AN28" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO28" s="9" t="inlineStr">
@@ -6305,7 +6305,7 @@
       <c r="B29" s="7" t="inlineStr"/>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="V29" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-the-slow-life-of-a-redwood-en-v1-aac96</t>
         </is>
       </c>
       <c r="W29" s="7" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="Z29" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA29" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB29" s="9" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="AG29" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH29" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI29" s="9" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="AN29" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO29" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP29" s="9" t="inlineStr">
@@ -6522,7 +6522,7 @@
       <c r="B30" s="7" t="inlineStr"/>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="V30" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>audio-voyager-1-a-journey-to-interstellar-space-en-v1-aac96</t>
         </is>
       </c>
       <c r="W30" s="7" t="inlineStr">
@@ -6631,12 +6631,12 @@
       </c>
       <c r="Z30" s="9" t="inlineStr">
         <is>
-          <t>rendered</t>
+          <t>published</t>
         </is>
       </c>
       <c r="AA30" s="9" t="inlineStr">
         <is>
-          <t>NOT READY</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="AB30" s="9" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="AG30" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AH30" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AI30" s="9" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="AN30" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AO30" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP30" s="9" t="inlineStr">

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Story Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Story Tracker'!$A$3:$AS$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Story Tracker'!$A$3:$AT$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS30"/>
+  <dimension ref="A1:AT30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,8 @@
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -869,6 +870,11 @@
       </c>
       <c r="AS3" s="4" t="inlineStr">
         <is>
+          <t>G18</t>
+        </is>
+      </c>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
           <t>manifest</t>
         </is>
       </c>
@@ -1068,7 +1074,7 @@
       </c>
       <c r="AO4" s="6" t="inlineStr">
         <is>
-          <t>Supabase + catalog</t>
+          <t>staging landed</t>
         </is>
       </c>
       <c r="AP4" s="6" t="inlineStr">
@@ -1086,7 +1092,12 @@
           <t>SSML integrity</t>
         </is>
       </c>
-      <c r="AS4" s="6" t="inlineStr"/>
+      <c r="AS4" s="6" t="inlineStr">
+        <is>
+          <t>production landed</t>
+        </is>
+      </c>
+      <c r="AT4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -1281,7 +1292,7 @@
       </c>
       <c r="AO5" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP5" s="9" t="inlineStr">
@@ -1300,6 +1311,11 @@
         </is>
       </c>
       <c r="AS5" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT5" s="9" t="inlineStr">
         <is>
           <t>Stories/a-roman-bathhouse-at-closing-time/story.yaml</t>
         </is>
@@ -1498,7 +1514,7 @@
       </c>
       <c r="AO6" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP6" s="9" t="inlineStr">
@@ -1517,6 +1533,11 @@
         </is>
       </c>
       <c r="AS6" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT6" s="9" t="inlineStr">
         <is>
           <t>Stories/aristotle-the-greatest-philosopher/story.yaml</t>
         </is>
@@ -1715,7 +1736,7 @@
       </c>
       <c r="AO7" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP7" s="9" t="inlineStr">
@@ -1734,6 +1755,11 @@
         </is>
       </c>
       <c r="AS7" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT7" s="9" t="inlineStr">
         <is>
           <t>Stories/dinosaurs-from-rule-to-ruin/story.yaml</t>
         </is>
@@ -1932,7 +1958,7 @@
       </c>
       <c r="AO8" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP8" s="9" t="inlineStr">
@@ -1951,6 +1977,11 @@
         </is>
       </c>
       <c r="AS8" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT8" s="9" t="inlineStr">
         <is>
           <t>Stories/floating-through-the-pillars-of-creation/story.yaml</t>
         </is>
@@ -2149,7 +2180,7 @@
       </c>
       <c r="AO9" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP9" s="9" t="inlineStr">
@@ -2168,6 +2199,11 @@
         </is>
       </c>
       <c r="AS9" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT9" s="9" t="inlineStr">
         <is>
           <t>Stories/mapping-the-cosmic-web/story.yaml</t>
         </is>
@@ -2366,7 +2402,7 @@
       </c>
       <c r="AO10" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP10" s="9" t="inlineStr">
@@ -2385,6 +2421,11 @@
         </is>
       </c>
       <c r="AS10" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT10" s="9" t="inlineStr">
         <is>
           <t>Stories/the-bakery-before-dawn/story.yaml</t>
         </is>
@@ -2583,7 +2624,7 @@
       </c>
       <c r="AO11" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP11" s="9" t="inlineStr">
@@ -2602,6 +2643,11 @@
         </is>
       </c>
       <c r="AS11" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT11" s="9" t="inlineStr">
         <is>
           <t>Stories/the-bay-that-glows-at-night/story.yaml</t>
         </is>
@@ -2800,7 +2846,7 @@
       </c>
       <c r="AO12" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP12" s="9" t="inlineStr">
@@ -2819,6 +2865,11 @@
         </is>
       </c>
       <c r="AS12" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT12" s="9" t="inlineStr">
         <is>
           <t>Stories/the-building-of-a-cathedral/story.yaml</t>
         </is>
@@ -3017,7 +3068,7 @@
       </c>
       <c r="AO13" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP13" s="9" t="inlineStr">
@@ -3036,6 +3087,11 @@
         </is>
       </c>
       <c r="AS13" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT13" s="9" t="inlineStr">
         <is>
           <t>Stories/the-clockmaker-s-workshop/story.yaml</t>
         </is>
@@ -3234,7 +3290,7 @@
       </c>
       <c r="AO14" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP14" s="9" t="inlineStr">
@@ -3253,6 +3309,11 @@
         </is>
       </c>
       <c r="AS14" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT14" s="9" t="inlineStr">
         <is>
           <t>Stories/the-deep-ocean-trenches/story.yaml</t>
         </is>
@@ -3451,7 +3512,7 @@
       </c>
       <c r="AO15" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP15" s="9" t="inlineStr">
@@ -3470,6 +3531,11 @@
         </is>
       </c>
       <c r="AS15" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT15" s="9" t="inlineStr">
         <is>
           <t>Stories/the-great-library-of-alexandria/story.yaml</t>
         </is>
@@ -3688,6 +3754,11 @@
       </c>
       <c r="AS16" s="9" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT16" s="9" t="inlineStr">
+        <is>
           <t>Stories/the-hidden-clocks-of-the-night-sky/story.yaml</t>
         </is>
       </c>
@@ -3885,7 +3956,7 @@
       </c>
       <c r="AO17" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP17" s="9" t="inlineStr">
@@ -3904,6 +3975,11 @@
         </is>
       </c>
       <c r="AS17" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT17" s="9" t="inlineStr">
         <is>
           <t>Stories/the-joinery-of-japan-s-wooden-temples/story.yaml</t>
         </is>
@@ -4102,7 +4178,7 @@
       </c>
       <c r="AO18" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP18" s="9" t="inlineStr">
@@ -4121,6 +4197,11 @@
         </is>
       </c>
       <c r="AS18" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT18" s="9" t="inlineStr">
         <is>
           <t>Stories/the-journey-of-a-glacial-river/story.yaml</t>
         </is>
@@ -4319,7 +4400,7 @@
       </c>
       <c r="AO19" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP19" s="9" t="inlineStr">
@@ -4338,6 +4419,11 @@
         </is>
       </c>
       <c r="AS19" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT19" s="9" t="inlineStr">
         <is>
           <t>Stories/the-life-cycle-of-a-red-dwarf-star/story.yaml</t>
         </is>
@@ -4536,7 +4622,7 @@
       </c>
       <c r="AO20" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP20" s="9" t="inlineStr">
@@ -4555,6 +4641,11 @@
         </is>
       </c>
       <c r="AS20" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT20" s="9" t="inlineStr">
         <is>
           <t>Stories/the-lighthouse-on-the-windswept-island/story.yaml</t>
         </is>
@@ -4753,7 +4844,7 @@
       </c>
       <c r="AO21" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP21" s="9" t="inlineStr">
@@ -4772,6 +4863,11 @@
         </is>
       </c>
       <c r="AS21" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT21" s="9" t="inlineStr">
         <is>
           <t>Stories/the-long-way-home-a-slow-evening-journey/story.yaml</t>
         </is>
@@ -4970,7 +5066,7 @@
       </c>
       <c r="AO22" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP22" s="9" t="inlineStr">
@@ -4989,6 +5085,11 @@
         </is>
       </c>
       <c r="AS22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT22" s="9" t="inlineStr">
         <is>
           <t>Stories/the-medieval-inn-at-candlemas/story.yaml</t>
         </is>
@@ -5187,7 +5288,7 @@
       </c>
       <c r="AO23" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP23" s="9" t="inlineStr">
@@ -5206,6 +5307,11 @@
         </is>
       </c>
       <c r="AS23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT23" s="9" t="inlineStr">
         <is>
           <t>Stories/the-midnight-museum-beneath-the-sea/story.yaml</t>
         </is>
@@ -5404,7 +5510,7 @@
       </c>
       <c r="AO24" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP24" s="9" t="inlineStr">
@@ -5423,6 +5529,11 @@
         </is>
       </c>
       <c r="AS24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT24" s="9" t="inlineStr">
         <is>
           <t>Stories/the-midnight-sleeper-train-across-the-alps/story.yaml</t>
         </is>
@@ -5621,7 +5732,7 @@
       </c>
       <c r="AO25" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP25" s="9" t="inlineStr">
@@ -5640,6 +5751,11 @@
         </is>
       </c>
       <c r="AS25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT25" s="9" t="inlineStr">
         <is>
           <t>Stories/the-moons-of-jupiter-europa-s-ice-and-ocean/story.yaml</t>
         </is>
@@ -5838,7 +5954,7 @@
       </c>
       <c r="AO26" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP26" s="9" t="inlineStr">
@@ -5857,6 +5973,11 @@
         </is>
       </c>
       <c r="AS26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT26" s="9" t="inlineStr">
         <is>
           <t>Stories/the-observatory-on-ben-nevis/story.yaml</t>
         </is>
@@ -6055,7 +6176,7 @@
       </c>
       <c r="AO27" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP27" s="9" t="inlineStr">
@@ -6074,6 +6195,11 @@
         </is>
       </c>
       <c r="AS27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT27" s="9" t="inlineStr">
         <is>
           <t>Stories/the-quiet-observatory-questions-about-time/story.yaml</t>
         </is>
@@ -6272,7 +6398,7 @@
       </c>
       <c r="AO28" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP28" s="9" t="inlineStr">
@@ -6291,6 +6417,11 @@
         </is>
       </c>
       <c r="AS28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT28" s="9" t="inlineStr">
         <is>
           <t>Stories/the-rings-of-saturn/story.yaml</t>
         </is>
@@ -6489,7 +6620,7 @@
       </c>
       <c r="AO29" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP29" s="9" t="inlineStr">
@@ -6508,6 +6639,11 @@
         </is>
       </c>
       <c r="AS29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT29" s="9" t="inlineStr">
         <is>
           <t>Stories/the-slow-life-of-a-redwood/story.yaml</t>
         </is>
@@ -6706,7 +6842,7 @@
       </c>
       <c r="AO30" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AP30" s="9" t="inlineStr">
@@ -6725,22 +6861,27 @@
         </is>
       </c>
       <c r="AS30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT30" s="9" t="inlineStr">
         <is>
           <t>Stories/voyager-1-a-journey-to-interstellar-space/story.yaml</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AS30"/>
+  <autoFilter ref="A3:AT30"/>
   <mergeCells count="6">
     <mergeCell ref="C2:E2"/>
+    <mergeCell ref="AB2:AT2"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="AB2:AS2"/>
-    <mergeCell ref="A1:AS1"/>
     <mergeCell ref="F2:Y2"/>
+    <mergeCell ref="A1:AT1"/>
   </mergeCells>
-  <conditionalFormatting sqref="AB5:AS30">
+  <conditionalFormatting sqref="AB5:AT30">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"FAIL"</formula>
     </cfRule>

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AO5" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP5" s="9" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AO6" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP6" s="9" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AO7" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP7" s="9" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AO8" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP8" s="9" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AO9" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP9" s="9" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Read by Niamh from Kinsale</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AO10" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP10" s="9" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AO11" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP11" s="9" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AO12" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP12" s="9" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="AO13" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP13" s="9" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Read by Brian from St Ives</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AO14" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP14" s="9" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Read by Arthur from Ludlow</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AO15" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP15" s="9" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AO17" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP17" s="9" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AO18" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP18" s="9" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AO19" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP19" s="9" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AO20" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP20" s="9" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AO21" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP21" s="9" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AO22" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP22" s="9" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="AO23" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP23" s="9" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AO24" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP24" s="9" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AO25" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP25" s="9" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Read by Patrick, Block Island</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AO26" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP26" s="9" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="AO27" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP27" s="9" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AO28" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP28" s="9" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="AO29" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP29" s="9" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="AO30" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="AP30" s="9" t="inlineStr">

--- a/Lullable_Story_Card_Tracker.xlsx
+++ b/Lullable_Story_Card_Tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Story Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Story Tracker'!$A$3:$AT$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Story Tracker'!$A$3:$AW$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT30"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -580,21 +580,21 @@
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="44" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="26" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="32" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="44" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="48" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
@@ -610,7 +610,10 @@
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="16" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="16" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -636,12 +639,12 @@
           <t>CARD COPY</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>GATES</t>
         </is>
@@ -725,155 +728,170 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
+          <t>sigil</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>glowHex</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>baseHex</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
           <t>durationSeconds</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>bedtimeNote</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>bestFor</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>sleepPace</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>atmosphere</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>audioAssetID</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>audioMasterFilename</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>commercialRightsStatus</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>audioDelivery</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>STAGE</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AD3" s="4" t="inlineStr">
         <is>
           <t>PUBLISH READY</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>G01</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>G02</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>G03</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>G04</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>G05</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>G06</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
+      <c r="AK3" s="4" t="inlineStr">
         <is>
           <t>G07</t>
         </is>
       </c>
-      <c r="AI3" s="4" t="inlineStr">
+      <c r="AL3" s="4" t="inlineStr">
         <is>
           <t>G08</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr">
+      <c r="AM3" s="4" t="inlineStr">
         <is>
           <t>G09</t>
         </is>
       </c>
-      <c r="AK3" s="4" t="inlineStr">
+      <c r="AN3" s="4" t="inlineStr">
         <is>
           <t>G10</t>
         </is>
       </c>
-      <c r="AL3" s="4" t="inlineStr">
+      <c r="AO3" s="4" t="inlineStr">
         <is>
           <t>G11</t>
         </is>
       </c>
-      <c r="AM3" s="4" t="inlineStr">
+      <c r="AP3" s="4" t="inlineStr">
         <is>
           <t>G12</t>
         </is>
       </c>
-      <c r="AN3" s="4" t="inlineStr">
+      <c r="AQ3" s="4" t="inlineStr">
         <is>
           <t>G13</t>
         </is>
       </c>
-      <c r="AO3" s="4" t="inlineStr">
+      <c r="AR3" s="4" t="inlineStr">
         <is>
           <t>G14</t>
         </is>
       </c>
-      <c r="AP3" s="4" t="inlineStr">
+      <c r="AS3" s="4" t="inlineStr">
         <is>
           <t>G15</t>
         </is>
       </c>
-      <c r="AQ3" s="4" t="inlineStr">
+      <c r="AT3" s="4" t="inlineStr">
         <is>
           <t>G16</t>
         </is>
       </c>
-      <c r="AR3" s="4" t="inlineStr">
+      <c r="AU3" s="4" t="inlineStr">
         <is>
           <t>G17</t>
         </is>
       </c>
-      <c r="AS3" s="4" t="inlineStr">
+      <c r="AV3" s="4" t="inlineStr">
         <is>
           <t>G18</t>
         </is>
       </c>
-      <c r="AT3" s="4" t="inlineStr">
+      <c r="AW3" s="4" t="inlineStr">
         <is>
           <t>manifest</t>
         </is>
@@ -957,188 +975,203 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
+          <t>mark id, blank = echo fallback</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>6 uppercase hex</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>6 uppercase hex</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
           <t>measured from final audio</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>90-180 chars</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>10-24 chars</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>8-22 chars</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>10-28 chars</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>220-650 chars</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>immutable once minted</t>
         </is>
       </c>
-      <c r="W4" s="5" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>exact .wav name</t>
         </is>
       </c>
-      <c r="X4" s="5" t="inlineStr">
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>pending-verification | verified | restricted</t>
         </is>
       </c>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="Z4" s="6" t="inlineStr"/>
-      <c r="AA4" s="6" t="inlineStr"/>
-      <c r="AB4" s="6" t="inlineStr">
+      <c r="AC4" s="6" t="inlineStr"/>
+      <c r="AD4" s="6" t="inlineStr"/>
+      <c r="AE4" s="6" t="inlineStr">
         <is>
           <t>manifest schema</t>
         </is>
       </c>
-      <c r="AC4" s="6" t="inlineStr">
+      <c r="AF4" s="6" t="inlineStr">
         <is>
           <t>story identity</t>
         </is>
       </c>
-      <c r="AD4" s="6" t="inlineStr">
+      <c r="AG4" s="6" t="inlineStr">
         <is>
           <t>allowed values</t>
         </is>
       </c>
-      <c r="AE4" s="6" t="inlineStr">
+      <c r="AH4" s="6" t="inlineStr">
         <is>
           <t>card copy lengths</t>
         </is>
       </c>
-      <c r="AF4" s="6" t="inlineStr">
+      <c r="AI4" s="6" t="inlineStr">
         <is>
           <t>artwork colours</t>
         </is>
       </c>
-      <c r="AG4" s="6" t="inlineStr">
+      <c r="AJ4" s="6" t="inlineStr">
         <is>
           <t>publish date ISO-8601</t>
         </is>
       </c>
-      <c r="AH4" s="6" t="inlineStr">
+      <c r="AK4" s="6" t="inlineStr">
         <is>
           <t>no placeholders left</t>
         </is>
       </c>
-      <c r="AI4" s="6" t="inlineStr">
+      <c r="AL4" s="6" t="inlineStr">
         <is>
           <t>audio + rights files</t>
         </is>
       </c>
-      <c r="AJ4" s="6" t="inlineStr">
+      <c r="AM4" s="6" t="inlineStr">
         <is>
           <t>audio checksums</t>
         </is>
       </c>
-      <c r="AK4" s="6" t="inlineStr">
+      <c r="AN4" s="6" t="inlineStr">
         <is>
           <t>delivery encoding</t>
         </is>
       </c>
-      <c r="AL4" s="6" t="inlineStr">
+      <c r="AO4" s="6" t="inlineStr">
         <is>
           <t>duration matches audio</t>
         </is>
       </c>
-      <c r="AM4" s="6" t="inlineStr">
+      <c r="AP4" s="6" t="inlineStr">
         <is>
           <t>render manifest</t>
         </is>
       </c>
-      <c r="AN4" s="6" t="inlineStr">
+      <c r="AQ4" s="6" t="inlineStr">
         <is>
           <t>QA + device sign-off</t>
         </is>
       </c>
-      <c r="AO4" s="6" t="inlineStr">
+      <c r="AR4" s="6" t="inlineStr">
         <is>
           <t>staging landed</t>
         </is>
       </c>
-      <c r="AP4" s="6" t="inlineStr">
+      <c r="AS4" s="6" t="inlineStr">
         <is>
           <t>commercial rights</t>
         </is>
       </c>
-      <c r="AQ4" s="6" t="inlineStr">
+      <c r="AT4" s="6" t="inlineStr">
         <is>
           <t>access decision final</t>
         </is>
       </c>
-      <c r="AR4" s="6" t="inlineStr">
+      <c r="AU4" s="6" t="inlineStr">
         <is>
           <t>SSML integrity</t>
         </is>
       </c>
-      <c r="AS4" s="6" t="inlineStr">
+      <c r="AV4" s="6" t="inlineStr">
         <is>
           <t>production landed</t>
         </is>
       </c>
-      <c r="AT4" s="6" t="inlineStr"/>
+      <c r="AW4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>a-roman-bathhouse-at-closing-time</t>
+          <t>a-night-in-a-temperate-forest</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr"/>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>A Roman Bathhouse at Closing Time</t>
+          <t>A Night in a Temperate Forest</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Warm floors, running water, and the last lamps of an ordinary Roman evening</t>
+          <t>A slow wander through moss, bark, and dew after dark falls.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Read by Arthur from Ludlow</t>
+          <t>Read by Patrick, Block Island</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>ancient-worlds</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr"/>
@@ -1154,90 +1187,78 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20T19:30:00Z</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>2B1B12</t>
+          <t>121A14</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>E0A96D</t>
-        </is>
-      </c>
-      <c r="P5" s="8" t="n">
-        <v>2330</v>
-      </c>
-      <c r="Q5" s="7" t="inlineStr">
-        <is>
-          <t>The fire is banked, the water runs on its own, and the night man is dozing at his post. The building keeps itself warm until morning, and none of it needs you.</t>
-        </is>
-      </c>
-      <c r="R5" s="7" t="inlineStr">
-        <is>
-          <t>Warming down to sleep</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>Lamplit and settling</t>
-        </is>
+          <t>9BB68C</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr"/>
+      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="R5" s="7" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>3295</v>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>Steam, stone, amber light</t>
+          <t>For a mind still humming at day's end. The forest asks nothing of you tonight but to walk slowly and notice small, quiet things.</t>
         </is>
       </c>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>Slip into a provincial Roman bathhouse at the gentlest hour of its day, just as the crowds drift home and the attendants light the evening lamps. Walk the warm rooms in their proper order, stand on a floor heated by a fire nobody sees, and listen to water that has been arriving from the hills without pause for a hundred years. Along the way, the bronze strigil and the oil, Seneca's famous list of bathhouse noises, the spring in Britain where the earth itself stokes the furnace, and the banked fire that will breathe warmth under the mosaics all night long.</t>
+          <t>Quieting a busy mind</t>
         </is>
       </c>
       <c r="V5" s="7" t="inlineStr">
         <is>
-          <t>audio-a-roman-bathhouse-at-closing-time-en-v1-aac96</t>
+          <t>Slow, close, unhurried</t>
         </is>
       </c>
       <c r="W5" s="7" t="inlineStr">
         <is>
+          <t>Mossy, cool, nocturnal</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>Follow a quiet path from the forest edge into deep woods after sunset, where moss holds the day's last water and an owl settles into a beech tree. Along the way — how dew forms, how tree roots trade sugar underground, how bats read the dark in echoes, and how a fallen log slowly becomes soil again. A gentle, factual wander built for drifting off.</t>
+        </is>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X5" s="7" t="inlineStr">
+      <c r="AA5" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y5" s="7" t="inlineStr">
+      <c r="AB5" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z5" s="9" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="AA5" s="9" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="AB5" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AC5" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>rendered</t>
         </is>
       </c>
       <c r="AD5" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT READY</t>
         </is>
       </c>
       <c r="AE5" s="9" t="inlineStr">
@@ -1267,12 +1288,12 @@
       </c>
       <c r="AJ5" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AK5" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AL5" s="9" t="inlineStr">
@@ -1302,12 +1323,12 @@
       </c>
       <c r="AQ5" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AR5" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="AS5" s="9" t="inlineStr">
@@ -1317,14 +1338,29 @@
       </c>
       <c r="AT5" s="9" t="inlineStr">
         <is>
-          <t>Stories/a-roman-bathhouse-at-closing-time/story.yaml</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AU5" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV5" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AW5" s="9" t="inlineStr">
+        <is>
+          <t>Stories/a-night-in-a-temperate-forest/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>aristotle-the-greatest-philosopher</t>
+          <t>a-roman-bathhouse-at-closing-time</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr"/>
@@ -1335,27 +1371,27 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Aristotle, the Greatest Philosopher</t>
+          <t>A Roman Bathhouse at Closing Time</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>A quiet journey through reason, virtue, and the good life</t>
+          <t>Warm floors, running water, and the last lamps of an ordinary Roman evening</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Read by Emma from Oxford</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -1371,97 +1407,85 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09T00:00:00Z</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>26384A</t>
+          <t>2B1B12</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>B89A6A</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="n">
-        <v>2401</v>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>One calm mind, examined slowly — reason, virtue, and the good life, laid out like a quiet evening walk. Nothing here needs to be solved tonight.</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>Curious, wandering minds</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>Slow and steady</t>
-        </is>
+          <t>E0A96D</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr"/>
+      <c r="Q6" s="7" t="inlineStr"/>
+      <c r="R6" s="7" t="inlineStr"/>
+      <c r="S6" s="8" t="n">
+        <v>2330</v>
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>Marble, lamplight, reason</t>
+          <t>The fire is banked, the water runs on its own, and the night man is dozing at his post. The building keeps itself warm until morning, and none of it needs you.</t>
         </is>
       </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
-          <t>You settle in beside one of history’s calmest minds. This is a slow exploration of Aristotle’s life and ideas — how he watched the natural world, what he taught about knowledge, character, and friendship, and why his patient way of thinking still shapes how we understand ourselves. The questions are old, the pace is gentle, and nothing needs deciding tonight.</t>
+          <t>Warming down to sleep</t>
         </is>
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>audio-aristotle-en-v2-aac96</t>
+          <t>Lamplit and settling</t>
         </is>
       </c>
       <c r="W6" s="7" t="inlineStr">
         <is>
+          <t>Steam, stone, amber light</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>Slip into a provincial Roman bathhouse at the gentlest hour of its day, just as the crowds drift home and the attendants light the evening lamps. Walk the warm rooms in their proper order, stand on a floor heated by a fire nobody sees, and listen to water that has been arriving from the hills without pause for a hundred years. Along the way, the bronze strigil and the oil, Seneca's famous list of bathhouse noises, the spring in Britain where the earth itself stokes the furnace, and the banked fire that will breathe warmth under the mosaics all night long.</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>audio-a-roman-bathhouse-at-closing-time-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X6" s="7" t="inlineStr">
+      <c r="AA6" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y6" s="7" t="inlineStr">
+      <c r="AB6" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z6" s="9" t="inlineStr">
+      <c r="AC6" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA6" s="9" t="inlineStr">
+      <c r="AD6" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB6" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC6" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD6" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE6" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1539,14 +1563,29 @@
       </c>
       <c r="AT6" s="9" t="inlineStr">
         <is>
-          <t>Stories/aristotle-the-greatest-philosopher/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU6" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV6" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW6" s="9" t="inlineStr">
+        <is>
+          <t>Stories/a-roman-bathhouse-at-closing-time/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>dinosaurs-from-rule-to-ruin</t>
+          <t>aristotle-the-greatest-philosopher</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr"/>
@@ -1557,27 +1596,27 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>The Dinosaurs: From Rule to Ruin</t>
+          <t>Aristotle, the Greatest Philosopher</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>A 44-minute journey through deep time</t>
+          <t>A quiet journey through reason, virtue, and the good life</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Read by Arthur from Ludlow</t>
+          <t>Read by Emma from Oxford</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -1593,12 +1632,12 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11T02:11:43Z</t>
+          <t>2026-08-09T00:00:00Z</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -1611,79 +1650,67 @@
           <t>B89A6A</t>
         </is>
       </c>
-      <c r="P7" s="8" t="n">
-        <v>2588</v>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>Deep time moves slowly here. Every age in this story settled into stillness long ago, and nothing in it asks anything of you tonight.</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>Drifting through time</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr"/>
+      <c r="R7" s="7" t="inlineStr"/>
+      <c r="S7" s="8" t="n">
+        <v>2401</v>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>One calm mind, examined slowly — reason, virtue, and the good life, laid out like a quiet evening walk. Nothing here needs to be solved tonight.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Curious, wandering minds</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
         <is>
           <t>Slow and steady</t>
         </is>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>Ancient, vast, hushed</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>Drift through the rise, reign, and quiet fading of the dinosaurs in a calm story of deep time. You move slowly across changing continents and warm shallow seas, through long ages when giants grazed in the light of an older sun, and follow the traces they left behind in stone — a world that never fully ended, still with us in every morning’s birdsong.</t>
-        </is>
-      </c>
-      <c r="V7" s="7" t="inlineStr">
-        <is>
-          <t>audio-dinosaurs-en-v2-aac96</t>
-        </is>
-      </c>
       <c r="W7" s="7" t="inlineStr">
         <is>
+          <t>Marble, lamplight, reason</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>You settle in beside one of history’s calmest minds. This is a slow exploration of Aristotle’s life and ideas — how he watched the natural world, what he taught about knowledge, character, and friendship, and why his patient way of thinking still shapes how we understand ourselves. The questions are old, the pace is gentle, and nothing needs deciding tonight.</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>audio-aristotle-en-v2-aac96</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X7" s="7" t="inlineStr">
+      <c r="AA7" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y7" s="7" t="inlineStr">
+      <c r="AB7" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z7" s="9" t="inlineStr">
+      <c r="AC7" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA7" s="9" t="inlineStr">
+      <c r="AD7" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB7" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC7" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD7" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE7" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1761,14 +1788,29 @@
       </c>
       <c r="AT7" s="9" t="inlineStr">
         <is>
-          <t>Stories/dinosaurs-from-rule-to-ruin/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU7" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV7" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW7" s="9" t="inlineStr">
+        <is>
+          <t>Stories/aristotle-the-greatest-philosopher/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>floating-through-the-pillars-of-creation</t>
+          <t>dinosaurs-from-rule-to-ruin</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr"/>
@@ -1789,22 +1831,22 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Floating Through the Pillars of Creation</t>
+          <t>The Dinosaurs: From Rule to Ruin</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Cold columns of dust and gas, six thousand light years out, quietly making stars</t>
+          <t>A 44-minute journey through deep time</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr"/>
@@ -1820,92 +1862,80 @@
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20T19:30:00Z</t>
+          <t>2026-08-11T02:11:43Z</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>1A1026</t>
+          <t>26384A</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>C98A6B</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>2435</v>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>Nothing out there is waiting for anything. The columns simply stand in the light, giving themselves up to it slowly, and they will go on standing long after tonight.</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>Feeling small and safe</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>Slow and drifting</t>
-        </is>
+          <t>B89A6A</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr"/>
+      <c r="Q8" s="7" t="inlineStr"/>
+      <c r="R8" s="7" t="inlineStr"/>
+      <c r="S8" s="8" t="n">
+        <v>2588</v>
       </c>
       <c r="T8" s="7" t="inlineStr">
         <is>
-          <t>Cold, dusty, lit from above</t>
+          <t>Deep time moves slowly here. Every age in this story settled into stillness long ago, and nothing in it asks anything of you tonight.</t>
         </is>
       </c>
       <c r="U8" s="7" t="inlineStr">
         <is>
-          <t>You rise from your own roof and travel outward, past every planet, until the stars themselves begin to thicken into a glowing cloud. Three dark columns stand in the middle of it, each one taller than the gap between our sun and its nearest neighbour. You learn what they are made of, how starlight is quietly carving them, why they are pillars at all, and what is forming in the pockets of shadow inside. Then the light goes on arriving, as it has for six thousand years, and you let all of it go.</t>
+          <t>Drifting through time</t>
         </is>
       </c>
       <c r="V8" s="7" t="inlineStr">
         <is>
-          <t>audio-floating-through-the-pillars-of-creation-en-v1-aac96</t>
+          <t>Slow and steady</t>
         </is>
       </c>
       <c r="W8" s="7" t="inlineStr">
         <is>
+          <t>Ancient, vast, hushed</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
+        <is>
+          <t>Drift through the rise, reign, and quiet fading of the dinosaurs in a calm story of deep time. You move slowly across changing continents and warm shallow seas, through long ages when giants grazed in the light of an older sun, and follow the traces they left behind in stone — a world that never fully ended, still with us in every morning’s birdsong.</t>
+        </is>
+      </c>
+      <c r="Y8" s="7" t="inlineStr">
+        <is>
+          <t>audio-dinosaurs-en-v2-aac96</t>
+        </is>
+      </c>
+      <c r="Z8" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="AA8" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y8" s="7" t="inlineStr">
+      <c r="AB8" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z8" s="9" t="inlineStr">
+      <c r="AC8" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA8" s="9" t="inlineStr">
+      <c r="AD8" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB8" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC8" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD8" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE8" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1983,14 +2013,29 @@
       </c>
       <c r="AT8" s="9" t="inlineStr">
         <is>
-          <t>Stories/floating-through-the-pillars-of-creation/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU8" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV8" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW8" s="9" t="inlineStr">
+        <is>
+          <t>Stories/dinosaurs-from-rule-to-ruin/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>mapping-the-cosmic-web</t>
+          <t>floating-through-the-pillars-of-creation</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr"/>
@@ -2011,12 +2056,12 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Mapping the Cosmic Web</t>
+          <t>Floating Through the Pillars of Creation</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Decades of cold nights on mountains, one galaxy at a time, until a shape appeared</t>
+          <t>Cold columns of dust and gas, six thousand light years out, quietly making stars</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -2047,87 +2092,75 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>10131F</t>
+          <t>1A1026</t>
         </is>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>8E9FD0</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="n">
-        <v>2364</v>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>The largest arrangement there is, and it does nothing in any hurry. It was found by people writing down one number a night, and none of it needs your attention tonight.</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>Ending a long day</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>Slow, wide, still</t>
-        </is>
+          <t>C98A6B</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="R9" s="7" t="inlineStr"/>
+      <c r="S9" s="8" t="n">
+        <v>2435</v>
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>Vast, dark, quiet, patient</t>
+          <t>Nothing out there is waiting for anything. The columns simply stand in the light, giving themselves up to it slowly, and they will go on standing long after tonight.</t>
         </is>
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
-          <t>Sit in a cold dome in Arizona in the 1980s, while somebody points a telescope at one faint smudge after another and writes down a number. Do that for years, plot the results, and a shape appears that nobody expected — galaxies strung along threads, gathered at knots, wrapped around enormous quiet rooms with almost nothing inside. Along the way, the mule driver who became one of the great observers, a sound from the early universe frozen into the sky as a ruler, and five thousand small robots that rearrange themselves in the dark.</t>
+          <t>Feeling small and safe</t>
         </is>
       </c>
       <c r="V9" s="7" t="inlineStr">
         <is>
-          <t>audio-mapping-the-cosmic-web-en-v1-aac96</t>
+          <t>Slow and drifting</t>
         </is>
       </c>
       <c r="W9" s="7" t="inlineStr">
         <is>
+          <t>Cold, dusty, lit from above</t>
+        </is>
+      </c>
+      <c r="X9" s="7" t="inlineStr">
+        <is>
+          <t>You rise from your own roof and travel outward, past every planet, until the stars themselves begin to thicken into a glowing cloud. Three dark columns stand in the middle of it, each one taller than the gap between our sun and its nearest neighbour. You learn what they are made of, how starlight is quietly carving them, why they are pillars at all, and what is forming in the pockets of shadow inside. Then the light goes on arriving, as it has for six thousand years, and you let all of it go.</t>
+        </is>
+      </c>
+      <c r="Y9" s="7" t="inlineStr">
+        <is>
+          <t>audio-floating-through-the-pillars-of-creation-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z9" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X9" s="7" t="inlineStr">
+      <c r="AA9" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y9" s="7" t="inlineStr">
+      <c r="AB9" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z9" s="9" t="inlineStr">
+      <c r="AC9" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA9" s="9" t="inlineStr">
+      <c r="AD9" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB9" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC9" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD9" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE9" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -2205,14 +2238,29 @@
       </c>
       <c r="AT9" s="9" t="inlineStr">
         <is>
-          <t>Stories/mapping-the-cosmic-web/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU9" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV9" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW9" s="9" t="inlineStr">
+        <is>
+          <t>Stories/floating-through-the-pillars-of-creation/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>the-bakery-before-dawn</t>
+          <t>mapping-the-cosmic-web</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr"/>
@@ -2223,32 +2271,32 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>The Bakery Before Dawn</t>
+          <t>Mapping the Cosmic Web</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Warm flour, a slow rising, and the long quiet hours before a town wakes</t>
+          <t>Decades of cold nights on mountains, one galaxy at a time, until a shape appeared</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>cozy-tales</t>
+          <t>cosmic-journeys</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr"/>
@@ -2264,92 +2312,80 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16T15:26:08Z</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>2E1F14</t>
+          <t>10131F</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>E3B778</t>
-        </is>
-      </c>
-      <c r="P10" s="8" t="n">
-        <v>2394</v>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>Someone else is already awake, working gently in the warm, at something that cannot be hurried. There is nothing here you need to do.</t>
-        </is>
-      </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>Feeling safe and warm</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>Slow and steady</t>
-        </is>
+          <t>8E9FD0</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr"/>
+      <c r="Q10" s="7" t="inlineStr"/>
+      <c r="R10" s="7" t="inlineStr"/>
+      <c r="S10" s="8" t="n">
+        <v>2364</v>
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>Warm, floury, hushed</t>
+          <t>The largest arrangement there is, and it does nothing in any hurry. It was found by people writing down one number a night, and none of it needs your attention tonight.</t>
         </is>
       </c>
       <c r="U10" s="7" t="inlineStr">
         <is>
-          <t>You cross a frozen street at two in the morning toward the one lit window on the corner, and step into a small tiled room that smells of warm flour. A baker works alone at a wooden bench, unhurried, feeding a glass jar that is older than she is. You learn what is living inside it, why the dough rests before it is touched, what the salt is quietly doing, and how a loaf lifts and sets and turns gold in the last half hour. Then the light goes off, and she walks home to sleep.</t>
+          <t>Ending a long day</t>
         </is>
       </c>
       <c r="V10" s="7" t="inlineStr">
         <is>
-          <t>audio-the-bakery-before-dawn-en-v2-aac96</t>
+          <t>Slow, wide, still</t>
         </is>
       </c>
       <c r="W10" s="7" t="inlineStr">
         <is>
+          <t>Vast, dark, quiet, patient</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
+        <is>
+          <t>Sit in a cold dome in Arizona in the 1980s, while somebody points a telescope at one faint smudge after another and writes down a number. Do that for years, plot the results, and a shape appears that nobody expected — galaxies strung along threads, gathered at knots, wrapped around enormous quiet rooms with almost nothing inside. Along the way, the mule driver who became one of the great observers, a sound from the early universe frozen into the sky as a ruler, and five thousand small robots that rearrange themselves in the dark.</t>
+        </is>
+      </c>
+      <c r="Y10" s="7" t="inlineStr">
+        <is>
+          <t>audio-mapping-the-cosmic-web-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z10" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X10" s="7" t="inlineStr">
+      <c r="AA10" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y10" s="7" t="inlineStr">
+      <c r="AB10" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z10" s="9" t="inlineStr">
+      <c r="AC10" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA10" s="9" t="inlineStr">
+      <c r="AD10" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB10" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC10" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD10" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE10" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -2427,14 +2463,29 @@
       </c>
       <c r="AT10" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-bakery-before-dawn/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU10" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV10" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW10" s="9" t="inlineStr">
+        <is>
+          <t>Stories/mapping-the-cosmic-web/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>the-bay-that-glows-at-night</t>
+          <t>the-bakery-before-dawn</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr"/>
@@ -2445,32 +2496,32 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>The Bay That Glows at Night</t>
+          <t>The Bakery Before Dawn</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Adrift on a moonless Caribbean bay where every touch of the water answers in blue</t>
+          <t>Warm flour, a slow rising, and the long quiet hours before a town wakes</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Read by Brian from St Ives</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr"/>
@@ -2486,92 +2537,92 @@
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20T19:30:00Z</t>
+          <t>2026-08-16T15:26:08Z</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>0A1622</t>
+          <t>2E1F14</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>63D9F2</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="n">
-        <v>2637</v>
+          <t>E3B778</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>bakery</t>
+        </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>No moon tonight, and that is the point. The paddle rests, the water glows wherever the fish go, and a whole island keeps its darkness like a garden.</t>
+          <t>6B4638</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>Dimming a busy mind</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>Adrift and moonless</t>
-        </is>
+          <t>2B1F1B</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>2394</v>
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>Warm dark, blue sparks</t>
+          <t>Someone else is already awake, working gently in the warm, at something that cannot be hurried. There is nothing here you need to do.</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
         <is>
-          <t>Glide out through a tunnel of mangroves onto the brightest glowing bay in the world, on a night with no moon. Learn how a single living cell, one of seven hundred thousand in every gallon, keeps a tiny pantry of light and opens it at a touch. Watch fish write comet trails, hold a handful of blue stars, and float between two skies while warm rain sets the whole surface flickering. With Darwin at the ship's rail, the rare milky seas that glow from horizon to horizon, and an island community that tends its darkness the way other towns tend their gardens.</t>
+          <t>Feeling safe and warm</t>
         </is>
       </c>
       <c r="V11" s="7" t="inlineStr">
         <is>
-          <t>audio-the-bay-that-glows-at-night-en-v1-aac96</t>
+          <t>Slow and steady</t>
         </is>
       </c>
       <c r="W11" s="7" t="inlineStr">
         <is>
+          <t>Warm, floury, hushed</t>
+        </is>
+      </c>
+      <c r="X11" s="7" t="inlineStr">
+        <is>
+          <t>You cross a frozen street at two in the morning toward the one lit window on the corner, and step into a small tiled room that smells of warm flour. A baker works alone at a wooden bench, unhurried, feeding a glass jar that is older than she is. You learn what is living inside it, why the dough rests before it is touched, what the salt is quietly doing, and how a loaf lifts and sets and turns gold in the last half hour. Then the light goes off, and she walks home to sleep.</t>
+        </is>
+      </c>
+      <c r="Y11" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-bakery-before-dawn-en-v2-aac96</t>
+        </is>
+      </c>
+      <c r="Z11" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X11" s="7" t="inlineStr">
+      <c r="AA11" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y11" s="7" t="inlineStr">
+      <c r="AB11" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z11" s="9" t="inlineStr">
+      <c r="AC11" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA11" s="9" t="inlineStr">
+      <c r="AD11" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB11" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC11" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD11" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE11" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -2649,14 +2700,29 @@
       </c>
       <c r="AT11" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-bay-that-glows-at-night/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU11" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV11" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW11" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-bakery-before-dawn/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>the-building-of-a-cathedral</t>
+          <t>the-bay-that-glows-at-night</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr"/>
@@ -2677,22 +2743,22 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>The Building of a Cathedral</t>
+          <t>The Bay That Glows at Night</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>An evening among people entirely at peace with never finishing</t>
+          <t>Adrift on a moonless Caribbean bay where every touch of the water answers in blue</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Read by Arthur from Ludlow</t>
+          <t>Read by Brian from St Ives</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>ancient-worlds</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr"/>
@@ -2713,87 +2779,75 @@
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>26222B</t>
+          <t>0A1622</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>C9A2C8</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>2308</v>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>Sixty years done, eighty to go, and every person on the site content with that arithmetic. Nothing in your life needs finishing by morning either.</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>Setting worries down</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>Generational and calm</t>
-        </is>
+          <t>63D9F2</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr"/>
+      <c r="Q12" s="7" t="inlineStr"/>
+      <c r="R12" s="7" t="inlineStr"/>
+      <c r="S12" s="8" t="n">
+        <v>2637</v>
       </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
-          <t>Stone, dusk, gold, chant</t>
+          <t>No moon tonight, and that is the point. The paddle rests, the water glows wherever the fish go, and a whole island keeps its darkness like a garden.</t>
         </is>
       </c>
       <c r="U12" s="7" t="inlineStr">
         <is>
-          <t>Walk into a thirteenth-century city at dusk, where the largest unfinished thing in the world has been rising for sixty years and will not be done for eighty more. Visit the lodge where stone dust turns gold in the doorway light, and the plaster tracing floor where three generations of masters have scratched their thinking at full size. Learn why the pointed arch lets stone float, how a timber centering is struck and a vault suddenly holds itself, and why lime mortar sets the pace of the whole century. Then watch the site put itself to bed, wrapped in straw against the frost, still quietly turning back into stone in the dark.</t>
+          <t>Dimming a busy mind</t>
         </is>
       </c>
       <c r="V12" s="7" t="inlineStr">
         <is>
-          <t>audio-the-building-of-a-cathedral-en-v1-aac96</t>
+          <t>Adrift and moonless</t>
         </is>
       </c>
       <c r="W12" s="7" t="inlineStr">
         <is>
+          <t>Warm dark, blue sparks</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>Glide out through a tunnel of mangroves onto the brightest glowing bay in the world, on a night with no moon. Learn how a single living cell, one of seven hundred thousand in every gallon, keeps a tiny pantry of light and opens it at a touch. Watch fish write comet trails, hold a handful of blue stars, and float between two skies while warm rain sets the whole surface flickering. With Darwin at the ship's rail, the rare milky seas that glow from horizon to horizon, and an island community that tends its darkness the way other towns tend their gardens.</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-bay-that-glows-at-night-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X12" s="7" t="inlineStr">
+      <c r="AA12" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y12" s="7" t="inlineStr">
+      <c r="AB12" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z12" s="9" t="inlineStr">
+      <c r="AC12" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA12" s="9" t="inlineStr">
+      <c r="AD12" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB12" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC12" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD12" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE12" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -2871,14 +2925,29 @@
       </c>
       <c r="AT12" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-building-of-a-cathedral/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU12" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV12" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-bay-that-glows-at-night/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>the-clockmaker-s-workshop</t>
+          <t>the-building-of-a-cathedral</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr"/>
@@ -2899,22 +2968,22 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>The Clockmaker's Workshop</t>
+          <t>The Building of a Cathedral</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>An evening among a hundred gentle clocks, none of them quite in agreement</t>
+          <t>An evening among people entirely at peace with never finishing</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Read by Niamh from Kinsale</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>cozy-tales</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr"/>
@@ -2935,87 +3004,75 @@
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>1C140E</t>
+          <t>26222B</t>
         </is>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>C98F3D</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>2376</v>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>The shop is locked, the lamp is out, and every pendulum keeps its small agreement in the dark. Nobody has to keep time while they sleep. It is being handled.</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>Ticking down to rest</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>Once a second, forever</t>
-        </is>
+          <t>C9A2C8</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="R13" s="7" t="inlineStr"/>
+      <c r="S13" s="8" t="n">
+        <v>2308</v>
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>Brass, oil, a hundred ticks</t>
+          <t>Sixty years done, eighty to go, and every person on the site content with that arithmetic. Nothing in your life needs finishing by morning either.</t>
         </is>
       </c>
       <c r="U13" s="7" t="inlineStr">
         <is>
-          <t>Step through a door with a brass bell into a small-town shop where a hundred clocks tick softly out of step, like rain on a roof. At the bench, an unhurried craftsman tends a movement of polished wheels with tools that have not changed in two centuries. Learn what a clock really is, a falling weight let down slowly over a week, and why two clocks on the same wall drift into perfect step with each other, a mystery first noticed from a sickbed in 1665. With painted moon dials, a drawer of orphaned keys that all fit something somewhere, winding day, house calls taken over tea, and the repairers' names penciled inside case doors, a century apart.</t>
+          <t>Setting worries down</t>
         </is>
       </c>
       <c r="V13" s="7" t="inlineStr">
         <is>
-          <t>audio-the-clockmaker-s-workshop-en-v1-aac96</t>
+          <t>Generational and calm</t>
         </is>
       </c>
       <c r="W13" s="7" t="inlineStr">
         <is>
+          <t>Stone, dusk, gold, chant</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>Walk into a thirteenth-century city at dusk, where the largest unfinished thing in the world has been rising for sixty years and will not be done for eighty more. Visit the lodge where stone dust turns gold in the doorway light, and the plaster tracing floor where three generations of masters have scratched their thinking at full size. Learn why the pointed arch lets stone float, how a timber centering is struck and a vault suddenly holds itself, and why lime mortar sets the pace of the whole century. Then watch the site put itself to bed, wrapped in straw against the frost, still quietly turning back into stone in the dark.</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-building-of-a-cathedral-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X13" s="7" t="inlineStr">
+      <c r="AA13" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y13" s="7" t="inlineStr">
+      <c r="AB13" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z13" s="9" t="inlineStr">
+      <c r="AC13" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA13" s="9" t="inlineStr">
+      <c r="AD13" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB13" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC13" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD13" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE13" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3093,14 +3150,29 @@
       </c>
       <c r="AT13" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-clockmaker-s-workshop/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU13" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV13" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-building-of-a-cathedral/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>the-deep-ocean-trenches</t>
+          <t>the-clockmaker-s-workshop</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
@@ -3121,22 +3193,22 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>The Deep Ocean Trenches</t>
+          <t>The Clockmaker's Workshop</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>A slow descent past the last of the light, into the stillest water on earth</t>
+          <t>An evening among a hundred gentle clocks, none of them quite in agreement</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr"/>
@@ -3157,87 +3229,75 @@
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>0B1F33</t>
+          <t>1C140E</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>5FA8C4</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>2409</v>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>One slow direction, downward, and nothing waiting at the end of it. An easy thing to follow, and an easier thing to let go of.</t>
-        </is>
-      </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>Letting the day end</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>Slow and sinking</t>
-        </is>
+          <t>C98F3D</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr"/>
+      <c r="Q14" s="7" t="inlineStr"/>
+      <c r="R14" s="7" t="inlineStr"/>
+      <c r="S14" s="8" t="n">
+        <v>2376</v>
       </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
-          <t>Dark, cool, weightless</t>
+          <t>The shop is locked, the lamp is out, and every pendulum keeps its small agreement in the dark. Nobody has to keep time while they sleep. It is being handled.</t>
         </is>
       </c>
       <c r="U14" s="7" t="inlineStr">
         <is>
-          <t>You slip beneath a starlit sea and sink, without effort, through the sunlit water and the long blue twilight into a darkness the sun has never reached. Small living lights blink on and drift away. Marine snow falls, soft and endless, all the way down to a floor of pale sediment older than memory. Further down still lie the trenches, where the pressure feels only like stillness and there is nowhere deeper to go.</t>
+          <t>Ticking down to rest</t>
         </is>
       </c>
       <c r="V14" s="7" t="inlineStr">
         <is>
-          <t>audio-the-deep-ocean-trenches-en-v1-aac96</t>
+          <t>Once a second, forever</t>
         </is>
       </c>
       <c r="W14" s="7" t="inlineStr">
         <is>
+          <t>Brass, oil, a hundred ticks</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>Step through a door with a brass bell into a small-town shop where a hundred clocks tick softly out of step, like rain on a roof. At the bench, an unhurried craftsman tends a movement of polished wheels with tools that have not changed in two centuries. Learn what a clock really is, a falling weight let down slowly over a week, and why two clocks on the same wall drift into perfect step with each other, a mystery first noticed from a sickbed in 1665. With painted moon dials, a drawer of orphaned keys that all fit something somewhere, winding day, house calls taken over tea, and the repairers' names penciled inside case doors, a century apart.</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-clockmaker-s-workshop-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X14" s="7" t="inlineStr">
+      <c r="AA14" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y14" s="7" t="inlineStr">
+      <c r="AB14" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z14" s="9" t="inlineStr">
+      <c r="AC14" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA14" s="9" t="inlineStr">
+      <c r="AD14" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB14" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC14" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD14" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE14" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3315,14 +3375,29 @@
       </c>
       <c r="AT14" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-deep-ocean-trenches/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU14" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV14" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-clockmaker-s-workshop/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>the-great-library-of-alexandria</t>
+          <t>the-deep-ocean-trenches</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr"/>
@@ -3343,12 +3418,12 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>The Great Library of Alexandria</t>
+          <t>The Deep Ocean Trenches</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Lamplight, papyrus and patient work beside a warm and quiet sea</t>
+          <t>A slow descent past the last of the light, into the stillest water on earth</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -3358,7 +3433,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>ancient-worlds</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr"/>
@@ -3379,87 +3454,75 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>3A2A18</t>
+          <t>0B1F33</t>
         </is>
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>D9A55C</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="n">
-        <v>2159</v>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>Nothing here is urgent and nothing needs remembering. Only scribes at their tables, copying one careful line at a time.</t>
-        </is>
-      </c>
-      <c r="R15" s="7" t="inlineStr">
-        <is>
-          <t>Slowing a busy day</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>Slow, unhurried</t>
-        </is>
+          <t>5FA8C4</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="R15" s="7" t="inlineStr"/>
+      <c r="S15" s="8" t="n">
+        <v>2409</v>
       </c>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>Warm, dusty, lamplit</t>
+          <t>One slow direction, downward, and nothing waiting at the end of it. An easy thing to follow, and an easier thing to let go of.</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
-          <t>You arrive at a harbour in the evening, when the light is going gold and the sea wind is moving up through the streets. Inside the cool halls, thousands of scrolls lie in their niches, and scribes copy them by hand, one careful line at a time. You learn how papyrus was pressed from river reeds, how ink was made from soot, how the first catalogue was written, and how a man measured the whole earth from the length of a shadow. Then the lamps are lit, and the work is set down.</t>
+          <t>Letting the day end</t>
         </is>
       </c>
       <c r="V15" s="7" t="inlineStr">
         <is>
-          <t>audio-the-great-library-of-alexandria-en-v1-aac96</t>
+          <t>Slow and sinking</t>
         </is>
       </c>
       <c r="W15" s="7" t="inlineStr">
         <is>
+          <t>Dark, cool, weightless</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>You slip beneath a starlit sea and sink, without effort, through the sunlit water and the long blue twilight into a darkness the sun has never reached. Small living lights blink on and drift away. Marine snow falls, soft and endless, all the way down to a floor of pale sediment older than memory. Further down still lie the trenches, where the pressure feels only like stillness and there is nowhere deeper to go.</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-deep-ocean-trenches-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X15" s="7" t="inlineStr">
+      <c r="AA15" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y15" s="7" t="inlineStr">
+      <c r="AB15" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z15" s="9" t="inlineStr">
+      <c r="AC15" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA15" s="9" t="inlineStr">
+      <c r="AD15" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB15" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC15" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD15" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE15" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3537,14 +3600,29 @@
       </c>
       <c r="AT15" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-great-library-of-alexandria/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU15" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV15" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-deep-ocean-trenches/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>the-hidden-clocks-of-the-night-sky</t>
+          <t>the-great-library-of-alexandria</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr"/>
@@ -3565,22 +3643,22 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>The Hidden Clocks of the Night Sky</t>
+          <t>The Great Library of Alexandria</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Stars, moonlight, and slow planets, each quietly keeping their own kind of time</t>
+          <t>Lamplight, papyrus and patient work beside a warm and quiet sea</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr"/>
@@ -3601,87 +3679,87 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>121A2E</t>
+          <t>3A2A18</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>D9C9A0</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="n">
-        <v>1148</v>
+          <t>D9A55C</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>alexandria</t>
+        </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>The sky above your roof is the oldest clock there is, and it has never once run down or needed you to watch it. Let it keep the hour tonight. You can simply rest.</t>
+          <t>805C35</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>Watching the sky turn</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>Slow, wide, unhurried</t>
-        </is>
+          <t>3A2A18</t>
+        </is>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>2159</v>
       </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
-          <t>Starlit, quiet, vast</t>
+          <t>Nothing here is urgent and nothing needs remembering. Only scribes at their tables, copying one careful line at a time.</t>
         </is>
       </c>
       <c r="U16" s="7" t="inlineStr">
         <is>
-          <t>You lie back in a dark meadow and read the oldest clock there is: the night sky. The whole dome of stars turns once a day around a quiet pole star. The moon counts twenty-nine nights and tows the tides behind it. Five wandering planets keep their own slow paces, one of them lending its name to Saturday. Starlight even comes in colors that tell a star's age, blue youth to red old age. And beneath every quick hand, one wobble of the Earth's axis takes twenty-six thousand years to complete, mid-tick since before the first cities rose. None of these clocks needs winding, watching, or you.</t>
+          <t>Slowing a busy day</t>
         </is>
       </c>
       <c r="V16" s="7" t="inlineStr">
         <is>
-          <t>audio-the-hidden-clocks-of-the-night-sky-en-v1-aac96</t>
+          <t>Slow, unhurried</t>
         </is>
       </c>
       <c r="W16" s="7" t="inlineStr">
         <is>
+          <t>Warm, dusty, lamplit</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>You arrive at a harbour in the evening, when the light is going gold and the sea wind is moving up through the streets. Inside the cool halls, thousands of scrolls lie in their niches, and scribes copy them by hand, one careful line at a time. You learn how papyrus was pressed from river reeds, how ink was made from soot, how the first catalogue was written, and how a man measured the whole earth from the length of a shadow. Then the lamps are lit, and the work is set down.</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-great-library-of-alexandria-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X16" s="7" t="inlineStr">
+      <c r="AA16" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y16" s="7" t="inlineStr">
+      <c r="AB16" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z16" s="9" t="inlineStr">
+      <c r="AC16" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA16" s="9" t="inlineStr">
+      <c r="AD16" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB16" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC16" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD16" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE16" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3759,14 +3837,29 @@
       </c>
       <c r="AT16" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-hidden-clocks-of-the-night-sky/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU16" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV16" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-great-library-of-alexandria/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>the-joinery-of-japan-s-wooden-temples</t>
+          <t>the-hidden-clocks-of-the-night-sky</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr"/>
@@ -3787,22 +3880,22 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>The Joinery of Japan's Wooden Temples</t>
+          <t>The Hidden Clocks of the Night Sky</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Thirteen centuries of buildings held together by shape alone, and not one nail</t>
+          <t>Stars, moonlight, and slow planets, each quietly keeping their own kind of time</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Read by Arthur from Ludlow</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>ancient-worlds</t>
+          <t>cosmic-journeys</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr"/>
@@ -3823,87 +3916,75 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>1E241C</t>
+          <t>121A2E</t>
         </is>
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>C4B49A</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>2226</v>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>Nothing here was ever nailed, so nothing is ever finished. It has been taken apart and put back together for thirteen hundred years, and none of it needs watching tonight.</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>Putting the day down</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>Careful and unhurried</t>
-        </is>
+          <t>D9C9A0</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr"/>
+      <c r="Q17" s="7" t="inlineStr"/>
+      <c r="R17" s="7" t="inlineStr"/>
+      <c r="S17" s="8" t="n">
+        <v>1148</v>
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>Wooden, misty, still, warm</t>
+          <t>The sky above your roof is the oldest clock there is, and it has never once run down or needed you to watch it. Let it keep the hour tonight. You can simply rest.</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
-          <t>Stand in a raked gravel courtyard at dawn and look up at a building with no nails in it. No screws, no brackets, nothing but wood cut to hold wood. Along the way, the joint that grips harder the more you load it, the carpenter who said to buy the mountain rather than the timber, a central pillar that holds up nothing and rests loose on a stone, and roof bark peeled from living trees that grow it back in ten years. And at Ise, a shrine rebuilt from new wood every twenty years for thirteen centuries, because twenty years is the length of human memory.</t>
+          <t>Watching the sky turn</t>
         </is>
       </c>
       <c r="V17" s="7" t="inlineStr">
         <is>
-          <t>audio-the-joinery-of-japan-s-wooden-temples-en-v1-aac96</t>
+          <t>Slow, wide, unhurried</t>
         </is>
       </c>
       <c r="W17" s="7" t="inlineStr">
         <is>
+          <t>Starlit, quiet, vast</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>You lie back in a dark meadow and read the oldest clock there is: the night sky. The whole dome of stars turns once a day around a quiet pole star. The moon counts twenty-nine nights and tows the tides behind it. Five wandering planets keep their own slow paces, one of them lending its name to Saturday. Starlight even comes in colors that tell a star's age, blue youth to red old age. And beneath every quick hand, one wobble of the Earth's axis takes twenty-six thousand years to complete, mid-tick since before the first cities rose. None of these clocks needs winding, watching, or you.</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-hidden-clocks-of-the-night-sky-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X17" s="7" t="inlineStr">
+      <c r="AA17" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y17" s="7" t="inlineStr">
+      <c r="AB17" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z17" s="9" t="inlineStr">
+      <c r="AC17" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA17" s="9" t="inlineStr">
+      <c r="AD17" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB17" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC17" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD17" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE17" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -3981,14 +4062,29 @@
       </c>
       <c r="AT17" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-joinery-of-japan-s-wooden-temples/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU17" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV17" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-hidden-clocks-of-the-night-sky/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>the-journey-of-a-glacial-river</t>
+          <t>the-joinery-of-japan-s-wooden-temples</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr"/>
@@ -4009,22 +4105,22 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>The Journey of a Glacial River</t>
+          <t>The Joinery of Japan's Wooden Temples</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>One snowflake's two-hundred-year trip from a silent snowfield to the sea</t>
+          <t>Thirteen centuries of buildings held together by shape alone, and not one nail</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Read by Niamh from Kinsale</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr"/>
@@ -4045,87 +4141,75 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>0F2230</t>
+          <t>1E241C</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>7FD0C9</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>2360</v>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>Water never has to choose. It goes the one way it can go, at whatever pace it is given, and tonight you can go with it, downhill the whole way.</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>Drifting downstream</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>Downhill, all the way</t>
-        </is>
+          <t>C4B49A</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr"/>
+      <c r="R18" s="7" t="inlineStr"/>
+      <c r="S18" s="8" t="n">
+        <v>2226</v>
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>Blue ice, cold water, calm</t>
+          <t>Nothing here was ever nailed, so nothing is ever finished. It has been taken apart and put back together for thirteen hundred years, and none of it needs watching tonight.</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
         <is>
-          <t>Follow a single snowflake from a windless high snowfield down to the salt water, a journey of two centuries in one direction only. Be buried into blue glacier ice with a breath of old sky sealed inside, ride the slowest river there is, and emerge at the ice cave where the young river is born, milky with the flour of ground mountains. Then down through the braided gravel plains, into a turquoise lake that sorts the sunlight, through pine forests where a small brown bird walks underwater, and out at last across the mudflats to the sea, where the sun is already lifting the water to begin again.</t>
+          <t>Putting the day down</t>
         </is>
       </c>
       <c r="V18" s="7" t="inlineStr">
         <is>
-          <t>audio-the-journey-of-a-glacial-river-en-v1-aac96</t>
+          <t>Careful and unhurried</t>
         </is>
       </c>
       <c r="W18" s="7" t="inlineStr">
         <is>
+          <t>Wooden, misty, still, warm</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>Stand in a raked gravel courtyard at dawn and look up at a building with no nails in it. No screws, no brackets, nothing but wood cut to hold wood. Along the way, the joint that grips harder the more you load it, the carpenter who said to buy the mountain rather than the timber, a central pillar that holds up nothing and rests loose on a stone, and roof bark peeled from living trees that grow it back in ten years. And at Ise, a shrine rebuilt from new wood every twenty years for thirteen centuries, because twenty years is the length of human memory.</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-joinery-of-japan-s-wooden-temples-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X18" s="7" t="inlineStr">
+      <c r="AA18" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y18" s="7" t="inlineStr">
+      <c r="AB18" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z18" s="9" t="inlineStr">
+      <c r="AC18" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA18" s="9" t="inlineStr">
+      <c r="AD18" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB18" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC18" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD18" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE18" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4203,14 +4287,29 @@
       </c>
       <c r="AT18" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-journey-of-a-glacial-river/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU18" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV18" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-joinery-of-japan-s-wooden-temples/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>the-life-cycle-of-a-red-dwarf-star</t>
+          <t>the-journey-of-a-glacial-river</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr"/>
@@ -4231,22 +4330,22 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>The Life Cycle of a Red Dwarf Star</t>
+          <t>The Journey of a Glacial River</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>The commonest star in the galaxy, burning so slowly that none has ever finished</t>
+          <t>One snowflake's two-hundred-year trip from a silent snowfield to the sea</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -4267,87 +4366,75 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>1C1013</t>
+          <t>0F2230</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>D97A55</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>Not one red dwarf has ever run down. The universe is far too young. Every single one ever made is still quietly burning, and none of it needs watching tonight.</t>
-        </is>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>Unwinding without hurry</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>Low, warm, unchanging</t>
-        </is>
+          <t>7FD0C9</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr"/>
+      <c r="Q19" s="7" t="inlineStr"/>
+      <c r="R19" s="7" t="inlineStr"/>
+      <c r="S19" s="8" t="n">
+        <v>2360</v>
       </c>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>Dim, orange, warm, endless</t>
+          <t>Water never has to choose. It goes the one way it can go, at whatever pace it is given, and tonight you can go with it, downhill the whole way.</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
         <is>
-          <t>Travel four light years to Proxima Centauri, a small orange star so dim you could look straight at it, and so ordinary that three quarters of the galaxy is made of stars like it. Inside, the whole body slowly turns itself over, which is why it will still be burning in ten trillion years. Along the way, why nature makes far more small stars than large ones, the women at Harvard who sorted the spectra by hand, the titanium chemistry that survives in a star's atmosphere, and the quiet fact that not one red dwarf anywhere has ever finished.</t>
+          <t>Drifting downstream</t>
         </is>
       </c>
       <c r="V19" s="7" t="inlineStr">
         <is>
-          <t>audio-the-life-cycle-of-a-red-dwarf-star-en-v1-aac96</t>
+          <t>Downhill, all the way</t>
         </is>
       </c>
       <c r="W19" s="7" t="inlineStr">
         <is>
+          <t>Blue ice, cold water, calm</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>Follow a single snowflake from a windless high snowfield down to the salt water, a journey of two centuries in one direction only. Be buried into blue glacier ice with a breath of old sky sealed inside, ride the slowest river there is, and emerge at the ice cave where the young river is born, milky with the flour of ground mountains. Then down through the braided gravel plains, into a turquoise lake that sorts the sunlight, through pine forests where a small brown bird walks underwater, and out at last across the mudflats to the sea, where the sun is already lifting the water to begin again.</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-journey-of-a-glacial-river-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X19" s="7" t="inlineStr">
+      <c r="AA19" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y19" s="7" t="inlineStr">
+      <c r="AB19" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z19" s="9" t="inlineStr">
+      <c r="AC19" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA19" s="9" t="inlineStr">
+      <c r="AD19" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB19" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC19" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD19" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE19" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4425,14 +4512,29 @@
       </c>
       <c r="AT19" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-life-cycle-of-a-red-dwarf-star/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU19" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV19" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-journey-of-a-glacial-river/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>the-lighthouse-on-the-windswept-island</t>
+          <t>the-life-cycle-of-a-red-dwarf-star</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr"/>
@@ -4453,22 +4555,22 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>The Lighthouse on the Windswept Island</t>
+          <t>The Life Cycle of a Red Dwarf Star</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>A keeper winds the weight, lights the lens, and keeps the coast safe till dawn</t>
+          <t>The commonest star in the galaxy, burning so slowly that none has ever finished</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Read by Patrick, Block Island</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>cozy-tales</t>
+          <t>cosmic-journeys</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -4489,87 +4591,75 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>1B2A33</t>
+          <t>1C1013</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>E8B84B</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="n">
-        <v>1468</v>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>Somewhere on a cold coast tonight, a lighthouse keeper is turning a great patient light so that strangers can pass safely by. You are as watched-over as any ship out there.</t>
-        </is>
-      </c>
-      <c r="R20" s="7" t="inlineStr">
-        <is>
-          <t>Feeling watched over</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>Steady and slow</t>
-        </is>
+          <t>D97A55</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr"/>
+      <c r="Q20" s="7" t="inlineStr"/>
+      <c r="R20" s="7" t="inlineStr"/>
+      <c r="S20" s="8" t="n">
+        <v>2341</v>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Granite, lamplight, rain</t>
+          <t>Not one red dwarf has ever run down. The universe is far too young. Every single one ever made is still quietly burning, and none of it needs watching tonight.</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
         <is>
-          <t>You climb a windswept island to a granite lighthouse, where a keeper is beginning his night watch. Ninety-nine steps up, past the watch room, to a great Fresnel lens turning on a bath of mercury, sweeping one long beam over the sea. Below, a snug round room holds a stove, an armchair, and a logbook of a hundred years of nights that all end the same reassuring way: all well. Rain arrives off the sea and streams down the tower in one continuous whisper, and out in the dark a coaster's mate counts the flashes and marks his position, never once thinking of the tower keeping him safe.</t>
+          <t>Unwinding without hurry</t>
         </is>
       </c>
       <c r="V20" s="7" t="inlineStr">
         <is>
-          <t>audio-the-lighthouse-on-the-windswept-island-en-v1-aac96</t>
+          <t>Low, warm, unchanging</t>
         </is>
       </c>
       <c r="W20" s="7" t="inlineStr">
         <is>
+          <t>Dim, orange, warm, endless</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>Travel four light years to Proxima Centauri, a small orange star so dim you could look straight at it, and so ordinary that three quarters of the galaxy is made of stars like it. Inside, the whole body slowly turns itself over, which is why it will still be burning in ten trillion years. Along the way, why nature makes far more small stars than large ones, the women at Harvard who sorted the spectra by hand, the titanium chemistry that survives in a star's atmosphere, and the quiet fact that not one red dwarf anywhere has ever finished.</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-life-cycle-of-a-red-dwarf-star-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X20" s="7" t="inlineStr">
+      <c r="AA20" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y20" s="7" t="inlineStr">
+      <c r="AB20" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z20" s="9" t="inlineStr">
+      <c r="AC20" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA20" s="9" t="inlineStr">
+      <c r="AD20" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB20" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC20" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD20" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE20" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4647,14 +4737,29 @@
       </c>
       <c r="AT20" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-lighthouse-on-the-windswept-island/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU20" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV20" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-life-cycle-of-a-red-dwarf-star/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>the-long-way-home-a-slow-evening-journey</t>
+          <t>the-lighthouse-on-the-windswept-island</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr"/>
@@ -4675,17 +4780,17 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>The Long Way Home: A Slow Evening Journey</t>
+          <t>The Lighthouse on the Windswept Island</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>A quiet walk down a coast road, through a sleeping village, to a banked fire</t>
+          <t>A keeper winds the weight, lights the lens, and keeps the coast safe till dawn</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Read by Niamh from Kinsale</t>
+          <t>Read by Patrick, Block Island</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -4711,87 +4816,75 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>2B2E3A</t>
+          <t>1B2A33</t>
         </is>
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>E4703C</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>2032</v>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>There is no adventure in tonight's walk, only lanes and hedges and a lamp left burning in a window for whoever is still out. That lamp is for you too.</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>Walking off the day</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>Unhurried, step by ste</t>
-        </is>
+          <t>E8B84B</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr"/>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="8" t="n">
+        <v>1468</v>
       </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>Coastal, hedgerowed, hushed</t>
+          <t>Somewhere on a cold coast tonight, a lighthouse keeper is turning a great patient light so that strangers can pass safely by. You are as watched-over as any ship out there.</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
         <is>
-          <t>You walk the long way home down an Irish coast road at dusk, with the sea keeping pace on one side and stone walls built to let the wind through on the other. The road passes a small harbor of knocking boats, a bridge over a talking stream, and a sleeping village where lamplight goes window by window from white to amber to out. Soft rain arrives in the hedges, right on time. A lamp burns in a neighbor's window for late travelers, an old coastal custom, and at last a whitewashed house appears with its own window lit, its turf fire banked low and patient under its ash, waiting to be climbed into.</t>
+          <t>Feeling watched over</t>
         </is>
       </c>
       <c r="V21" s="7" t="inlineStr">
         <is>
-          <t>audio-the-long-way-home-a-slow-evening-journey-en-v1-aac96</t>
+          <t>Steady and slow</t>
         </is>
       </c>
       <c r="W21" s="7" t="inlineStr">
         <is>
+          <t>Granite, lamplight, rain</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>You climb a windswept island to a granite lighthouse, where a keeper is beginning his night watch. Ninety-nine steps up, past the watch room, to a great Fresnel lens turning on a bath of mercury, sweeping one long beam over the sea. Below, a snug round room holds a stove, an armchair, and a logbook of a hundred years of nights that all end the same reassuring way: all well. Rain arrives off the sea and streams down the tower in one continuous whisper, and out in the dark a coaster's mate counts the flashes and marks his position, never once thinking of the tower keeping him safe.</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-lighthouse-on-the-windswept-island-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X21" s="7" t="inlineStr">
+      <c r="AA21" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y21" s="7" t="inlineStr">
+      <c r="AB21" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z21" s="9" t="inlineStr">
+      <c r="AC21" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA21" s="9" t="inlineStr">
+      <c r="AD21" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB21" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC21" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD21" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE21" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4869,14 +4962,29 @@
       </c>
       <c r="AT21" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-long-way-home-a-slow-evening-journey/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU21" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV21" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-lighthouse-on-the-windswept-island/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>the-medieval-inn-at-candlemas</t>
+          <t>the-long-way-home-a-slow-evening-journey</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr"/>
@@ -4897,22 +5005,22 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>The Medieval Inn at Candlemas</t>
+          <t>The Long Way Home: A Slow Evening Journey</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>A traveler arrives at a fourteenth-century wayside inn on the feast of the returning light</t>
+          <t>A quiet walk down a coast road, through a sleeping village, to a banked fire</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Read by Arthur from Ludlow</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>ancient-worlds</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr"/>
@@ -4933,87 +5041,75 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>241A12</t>
+          <t>2B2E3A</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>E0A855</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>1606</v>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>Six centuries ago, a bell rang a whole valley to bed, fires were banked under clay covers, and travelers slept easy, all facing one fire. Borrow that old, whole kind of night.</t>
-        </is>
-      </c>
-      <c r="R22" s="7" t="inlineStr">
-        <is>
-          <t>Settling in after travel</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>Slow and fireside</t>
-        </is>
+          <t>E4703C</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr"/>
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="8" t="n">
+        <v>2032</v>
       </c>
       <c r="T22" s="7" t="inlineStr">
         <is>
-          <t>Candlelit, timbered, snowy</t>
+          <t>There is no adventure in tonight's walk, only lanes and hedges and a lamp left burning in a window for whoever is still out. That lamp is for you too.</t>
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
         <is>
-          <t>You ride into a fourteenth-century wayside inn on Candlemas, the old feast of blessed candles marking winter's turn. A green bush over the door promises ale, beds, and fire, and inside, strangers share one hearth, a thick pottage, and low unimportant talk. At curfew the innkeeper covers the fire under a clay dome, candles are pinched out one by one, and the village church bell rings the valley to rest. Upstairs under a thick thatch roof, travelers share a chamber the old way, speaking of first sleep and second sleep as easily as dinner and supper, while outside, in perfect silence, it begins to snow.</t>
+          <t>Walking off the day</t>
         </is>
       </c>
       <c r="V22" s="7" t="inlineStr">
         <is>
-          <t>audio-the-medieval-inn-at-candlemas-en-v1-aac96</t>
+          <t>Unhurried, step by ste</t>
         </is>
       </c>
       <c r="W22" s="7" t="inlineStr">
         <is>
+          <t>Coastal, hedgerowed, hushed</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>You walk the long way home down an Irish coast road at dusk, with the sea keeping pace on one side and stone walls built to let the wind through on the other. The road passes a small harbor of knocking boats, a bridge over a talking stream, and a sleeping village where lamplight goes window by window from white to amber to out. Soft rain arrives in the hedges, right on time. A lamp burns in a neighbor's window for late travelers, an old coastal custom, and at last a whitewashed house appears with its own window lit, its turf fire banked low and patient under its ash, waiting to be climbed into.</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-long-way-home-a-slow-evening-journey-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X22" s="7" t="inlineStr">
+      <c r="AA22" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y22" s="7" t="inlineStr">
+      <c r="AB22" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z22" s="9" t="inlineStr">
+      <c r="AC22" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA22" s="9" t="inlineStr">
+      <c r="AD22" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE22" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5091,14 +5187,29 @@
       </c>
       <c r="AT22" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-medieval-inn-at-candlemas/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-long-way-home-a-slow-evening-journey/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>the-midnight-museum-beneath-the-sea</t>
+          <t>the-medieval-inn-at-candlemas</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr"/>
@@ -5119,22 +5230,22 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>The Midnight Museum Beneath the Sea</t>
+          <t>The Medieval Inn at Candlemas</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>A slow descent through the deep ocean's glowing halls of glass, light, and patient history</t>
+          <t>A traveler arrives at a fourteenth-century wayside inn on the feast of the returning light</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Read by Brian from St Ives</t>
+          <t>Read by Arthur from Ludlow</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>ancient-worlds</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr"/>
@@ -5155,87 +5266,75 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>071826</t>
+          <t>241A12</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>4FD1C5</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="n">
-        <v>1197</v>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>A hundred million years of quiet lives below the waves, lit by their own small lamps, needing nothing from anyone. Tonight you get to drift through it and rest.</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>Sinking into stillness</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>Slow, weightless drift</t>
-        </is>
+          <t>E0A855</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr"/>
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="8" t="n">
+        <v>1606</v>
       </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>Deep, glowing, silent</t>
+          <t>Six centuries ago, a bell rang a whole valley to bed, fires were banked under clay covers, and travelers slept easy, all facing one fire. Borrow that old, whole kind of night.</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">
         <is>
-          <t>You sink through the ocean's floors of light, from sunlit gold down through a deep cathedral blue into the midnight zone, where nine of ten creatures make their own cold light to say here I am. You drift past a lanternfish's blinking rows, an anglerfish's small warm lamp, and glass sponges that have filtered the same gentle current for ten thousand years. Marine snow falls without pause through halls holding an old ship and a whale fall's soft, fed city, all the way down to a trench floor where a small pink snailfish is entirely at home. The museum keeps everything for you until morning, softly, with its own lamps.</t>
+          <t>Settling in after travel</t>
         </is>
       </c>
       <c r="V23" s="7" t="inlineStr">
         <is>
-          <t>audio-the-midnight-museum-beneath-the-sea-en-v1-aac96</t>
+          <t>Slow and fireside</t>
         </is>
       </c>
       <c r="W23" s="7" t="inlineStr">
         <is>
+          <t>Candlelit, timbered, snowy</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>You ride into a fourteenth-century wayside inn on Candlemas, the old feast of blessed candles marking winter's turn. A green bush over the door promises ale, beds, and fire, and inside, strangers share one hearth, a thick pottage, and low unimportant talk. At curfew the innkeeper covers the fire under a clay dome, candles are pinched out one by one, and the village church bell rings the valley to rest. Upstairs under a thick thatch roof, travelers share a chamber the old way, speaking of first sleep and second sleep as easily as dinner and supper, while outside, in perfect silence, it begins to snow.</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-medieval-inn-at-candlemas-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X23" s="7" t="inlineStr">
+      <c r="AA23" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y23" s="7" t="inlineStr">
+      <c r="AB23" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z23" s="9" t="inlineStr">
+      <c r="AC23" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA23" s="9" t="inlineStr">
+      <c r="AD23" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB23" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC23" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD23" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE23" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5313,14 +5412,29 @@
       </c>
       <c r="AT23" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-midnight-museum-beneath-the-sea/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-medieval-inn-at-candlemas/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>the-midnight-sleeper-train-across-the-alps</t>
+          <t>the-midnight-museum-beneath-the-sea</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr"/>
@@ -5341,22 +5455,22 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>The Midnight Sleeper Train Across the Alps</t>
+          <t>The Midnight Museum Beneath the Sea</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>A warm berth, a folder of sleeping passports, and mountains passing in the dark</t>
+          <t>A slow descent through the deep ocean's glowing halls of glass, light, and patient history</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Read by Niamh from Kinsale</t>
+          <t>Read by Brian from St Ives</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>cozy-tales</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr"/>
@@ -5377,87 +5491,75 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>151A2E</t>
+          <t>071826</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>D9B36C</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>2404</v>
-      </c>
-      <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>The signals are turning green all the way to the lake, and the attendant is awake so you need not be. The train knows the rest, and none of it is your business tonight.</t>
-        </is>
-      </c>
-      <c r="R24" s="7" t="inlineStr">
-        <is>
-          <t>Being gently carried</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>Rocking and westward</t>
-        </is>
+          <t>4FD1C5</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="7" t="inlineStr"/>
+      <c r="R24" s="7" t="inlineStr"/>
+      <c r="S24" s="8" t="n">
+        <v>1197</v>
       </c>
       <c r="T24" s="7" t="inlineStr">
         <is>
-          <t>Warm, amber, moonlit, moving</t>
+          <t>A hundred million years of quiet lives below the waves, lit by their own small lamps, needing nothing from anyone. Tonight you get to drift through it and rest.</t>
         </is>
       </c>
       <c r="U24" s="7" t="inlineStr">
         <is>
-          <t>Board the midnight-blue sleeper in Vienna, hand your passport to the attendant, and let the train do the rest. Cross the Alps in a rocking berth while borders pass over you like weather, carriages are quietly sorted toward separate mornings, and a freight train washes past in the dark. Along the way, why the clickety-clack disappeared when the rails were welded into seamless miles, the 1884 tunnel bored from both ends to meet like a handshake, and the whole quiet profession of people who stay awake so that everyone else can sleep at seventy miles an hour.</t>
+          <t>Sinking into stillness</t>
         </is>
       </c>
       <c r="V24" s="7" t="inlineStr">
         <is>
-          <t>audio-the-midnight-sleeper-train-across-the-alps-en-v1-aac96</t>
+          <t>Slow, weightless drift</t>
         </is>
       </c>
       <c r="W24" s="7" t="inlineStr">
         <is>
+          <t>Deep, glowing, silent</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>You sink through the ocean's floors of light, from sunlit gold down through a deep cathedral blue into the midnight zone, where nine of ten creatures make their own cold light to say here I am. You drift past a lanternfish's blinking rows, an anglerfish's small warm lamp, and glass sponges that have filtered the same gentle current for ten thousand years. Marine snow falls without pause through halls holding an old ship and a whale fall's soft, fed city, all the way down to a trench floor where a small pink snailfish is entirely at home. The museum keeps everything for you until morning, softly, with its own lamps.</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-midnight-museum-beneath-the-sea-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X24" s="7" t="inlineStr">
+      <c r="AA24" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y24" s="7" t="inlineStr">
+      <c r="AB24" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z24" s="9" t="inlineStr">
+      <c r="AC24" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA24" s="9" t="inlineStr">
+      <c r="AD24" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE24" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5535,14 +5637,29 @@
       </c>
       <c r="AT24" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-midnight-sleeper-train-across-the-alps/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-midnight-museum-beneath-the-sea/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>the-moons-of-jupiter-europa-s-ice-and-ocean</t>
+          <t>the-midnight-sleeper-train-across-the-alps</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr"/>
@@ -5563,22 +5680,22 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>The Moons of Jupiter: Europa's Ice and Ocean</t>
+          <t>The Midnight Sleeper Train Across the Alps</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>A small cracked moon of ice, and the dark ocean turning over beneath it</t>
+          <t>A warm berth, a folder of sleeping passports, and mountains passing in the dark</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Read by Niamh from Kinsale</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr"/>
@@ -5599,87 +5716,75 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>0E1A2B</t>
+          <t>151A2E</t>
         </is>
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>9FC8DA</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>2369</v>
-      </c>
-      <c r="Q25" s="7" t="inlineStr">
-        <is>
-          <t>There is no light down there and there never has been. The water simply turns over in the dark, as it has for a very long time, and none of it needs watching tonight.</t>
-        </is>
-      </c>
-      <c r="R25" s="7" t="inlineStr">
-        <is>
-          <t>Sinking into sleep</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>Quiet and downward</t>
-        </is>
+          <t>D9B36C</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr"/>
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="8" t="n">
+        <v>2404</v>
       </c>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>Cold, white, deep, quiet</t>
+          <t>The signals are turning green all the way to the lake, and the attendant is awake so you need not be. The train knows the rest, and none of it is your business tonight.</t>
         </is>
       </c>
       <c r="U25" s="7" t="inlineStr">
         <is>
-          <t>You travel out past Mars to a banded planet eleven times the width of the Earth, and find four small worlds standing beside it in a line. The second one is white, smooth as a billiard ball, and cracked all over like a glazed bowl. You learn why it has almost no craters, how a tiny wobble in its orbit keeps an ocean liquid where nothing should be, and how that ocean was found from the outside without anyone touching it. Then you sink through the ice into water that has never once seen light.</t>
+          <t>Being gently carried</t>
         </is>
       </c>
       <c r="V25" s="7" t="inlineStr">
         <is>
-          <t>audio-the-moons-of-jupiter-europa-s-ice-and-ocean-en-v1-aac96</t>
+          <t>Rocking and westward</t>
         </is>
       </c>
       <c r="W25" s="7" t="inlineStr">
         <is>
+          <t>Warm, amber, moonlit, moving</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>Board the midnight-blue sleeper in Vienna, hand your passport to the attendant, and let the train do the rest. Cross the Alps in a rocking berth while borders pass over you like weather, carriages are quietly sorted toward separate mornings, and a freight train washes past in the dark. Along the way, why the clickety-clack disappeared when the rails were welded into seamless miles, the 1884 tunnel bored from both ends to meet like a handshake, and the whole quiet profession of people who stay awake so that everyone else can sleep at seventy miles an hour.</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-midnight-sleeper-train-across-the-alps-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X25" s="7" t="inlineStr">
+      <c r="AA25" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y25" s="7" t="inlineStr">
+      <c r="AB25" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z25" s="9" t="inlineStr">
+      <c r="AC25" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA25" s="9" t="inlineStr">
+      <c r="AD25" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB25" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC25" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD25" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE25" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5757,14 +5862,29 @@
       </c>
       <c r="AT25" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-moons-of-jupiter-europa-s-ice-and-ocean/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-midnight-sleeper-train-across-the-alps/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>the-observatory-on-ben-nevis</t>
+          <t>the-moons-of-jupiter-europa-s-ice-and-ocean</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr"/>
@@ -5785,22 +5905,22 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>The Observatory on Ben Nevis</t>
+          <t>The Moons of Jupiter: Europa's Ice and Ocean</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Twenty-one years of hourly weather readings, taken by lamplight inside a cloud</t>
+          <t>A small cracked moon of ice, and the dark ocean turning over beneath it</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Lullable</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>cozy-tales</t>
+          <t>cosmic-journeys</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr"/>
@@ -5821,87 +5941,75 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>1F2A2E</t>
+          <t>0E1A2B</t>
         </is>
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>B9C9CE</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>2418</v>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>Somebody is awake on a mountain, taking a reading on the hour, whether or not you are. The next one is not yours, and it will be taken anyway.</t>
-        </is>
-      </c>
-      <c r="R26" s="7" t="inlineStr">
-        <is>
-          <t>Letting go of the day</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>Hourly and unhurried</t>
-        </is>
+          <t>9FC8DA</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr"/>
+      <c r="Q26" s="7" t="inlineStr"/>
+      <c r="R26" s="7" t="inlineStr"/>
+      <c r="S26" s="8" t="n">
+        <v>2369</v>
       </c>
       <c r="T26" s="7" t="inlineStr">
         <is>
-          <t>Cold, lamplit, patient</t>
+          <t>There is no light down there and there never has been. The water simply turns over in the dark, as it has for a very long time, and none of it needs watching tonight.</t>
         </is>
       </c>
       <c r="U26" s="7" t="inlineStr">
         <is>
-          <t>You climb into the cloud that sits on the highest ground in Britain, and step through a low stone door into lamplight, a warm stove, and a kettle that is always on. For twenty-one years, somebody here walked out into the weather every hour of every night and wrote down what it was doing. You learn how a wet sleeve of muslin measures the dryness of the air, why the thermometer boxes had to be lifted as the snow came up to meet them, and how ice grows sideways into the wind. Then the lamp is turned low, a wet coat goes on the hook, and the mountain carries on without you.</t>
+          <t>Sinking into sleep</t>
         </is>
       </c>
       <c r="V26" s="7" t="inlineStr">
         <is>
-          <t>audio-the-observatory-on-ben-nevis-en-v1-aac96</t>
+          <t>Quiet and downward</t>
         </is>
       </c>
       <c r="W26" s="7" t="inlineStr">
         <is>
+          <t>Cold, white, deep, quiet</t>
+        </is>
+      </c>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>You travel out past Mars to a banded planet eleven times the width of the Earth, and find four small worlds standing beside it in a line. The second one is white, smooth as a billiard ball, and cracked all over like a glazed bowl. You learn why it has almost no craters, how a tiny wobble in its orbit keeps an ocean liquid where nothing should be, and how that ocean was found from the outside without anyone touching it. Then you sink through the ice into water that has never once seen light.</t>
+        </is>
+      </c>
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-moons-of-jupiter-europa-s-ice-and-ocean-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z26" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X26" s="7" t="inlineStr">
+      <c r="AA26" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y26" s="7" t="inlineStr">
+      <c r="AB26" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z26" s="9" t="inlineStr">
+      <c r="AC26" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA26" s="9" t="inlineStr">
+      <c r="AD26" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB26" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC26" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD26" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE26" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5979,14 +6087,29 @@
       </c>
       <c r="AT26" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-observatory-on-ben-nevis/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-moons-of-jupiter-europa-s-ice-and-ocean/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>the-quiet-observatory-questions-about-time</t>
+          <t>the-observatory-on-ben-nevis</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr"/>
@@ -6007,22 +6130,22 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>The Quiet Observatory: Questions About Time</t>
+          <t>The Observatory on Ben Nevis</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>A gentle night among telescopes, old clocks, and the soft, bending nature of time itself</t>
+          <t>Twenty-one years of hourly weather readings, taken by lamplight inside a cloud</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Read by Emma from Oxford</t>
+          <t>Lullable</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>cozy-tales</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr"/>
@@ -6043,87 +6166,75 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>141B2E</t>
+          <t>1F2A2E</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>C9D6E8</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>2115</v>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
-        <is>
-          <t>Time only flows, never hurries, never waits. Tonight it is only asking you to lie still while it carries you, the way it has carried every sleeper before you.</t>
-        </is>
-      </c>
-      <c r="R27" s="7" t="inlineStr">
-        <is>
-          <t>Quieting a busy mind</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>Slow and thoughtful</t>
-        </is>
+          <t>B9C9CE</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr"/>
+      <c r="Q27" s="7" t="inlineStr"/>
+      <c r="R27" s="7" t="inlineStr"/>
+      <c r="S27" s="8" t="n">
+        <v>2418</v>
       </c>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>Starlit, hushed, timeless</t>
+          <t>Somebody is awake on a mountain, taking a reading on the hour, whether or not you are. The next one is not yours, and it will be taken anyway.</t>
         </is>
       </c>
       <c r="U27" s="7" t="inlineStr">
         <is>
-          <t>You climb a small hill to a small observatory to spend the night with the gentlest big question there is: what is time. A telescope shows that starlight is an old patient archive, arriving from a hundred different pasts all at once, and that there is no single now shared by the whole universe. Pendulum clocks, water clocks, and candle clocks each try to hang a bucket in a stream that never pools. A carpenter's son builds four clocks to solve longitude at sea, a hill at Greenwich becomes the world's meridian, and modern clocks now count the hum inside an atom. At the end, the astronomer closes the logbook with one word, closed, and so can you.</t>
+          <t>Letting go of the day</t>
         </is>
       </c>
       <c r="V27" s="7" t="inlineStr">
         <is>
-          <t>audio-the-quiet-observatory-questions-about-time-en-v1-aac96</t>
+          <t>Hourly and unhurried</t>
         </is>
       </c>
       <c r="W27" s="7" t="inlineStr">
         <is>
+          <t>Cold, lamplit, patient</t>
+        </is>
+      </c>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>You climb into the cloud that sits on the highest ground in Britain, and step through a low stone door into lamplight, a warm stove, and a kettle that is always on. For twenty-one years, somebody here walked out into the weather every hour of every night and wrote down what it was doing. You learn how a wet sleeve of muslin measures the dryness of the air, why the thermometer boxes had to be lifted as the snow came up to meet them, and how ice grows sideways into the wind. Then the lamp is turned low, a wet coat goes on the hook, and the mountain carries on without you.</t>
+        </is>
+      </c>
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-observatory-on-ben-nevis-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X27" s="7" t="inlineStr">
+      <c r="AA27" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y27" s="7" t="inlineStr">
+      <c r="AB27" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z27" s="9" t="inlineStr">
+      <c r="AC27" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA27" s="9" t="inlineStr">
+      <c r="AD27" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB27" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC27" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD27" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE27" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6201,14 +6312,29 @@
       </c>
       <c r="AT27" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-quiet-observatory-questions-about-time/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-observatory-on-ben-nevis/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>the-rings-of-saturn</t>
+          <t>the-quiet-observatory-questions-about-time</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr"/>
@@ -6219,27 +6345,27 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>The Rings of Saturn</t>
+          <t>The Quiet Observatory: Questions About Time</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Ten metres of ice, two hundred thousand kilometres wide, turning in silence</t>
+          <t>A gentle night among telescopes, old clocks, and the soft, bending nature of time itself</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Read by Emma from Oxford</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -6260,92 +6386,80 @@
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14T17:53:16Z</t>
+          <t>2026-08-20T19:30:00Z</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>1B2436</t>
+          <t>141B2E</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>E8C89A</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>2298</v>
-      </c>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>A long way from anything that has ever asked something of you. Nothing out here is in a hurry, and none of it needs watching.</t>
-        </is>
-      </c>
-      <c r="R28" s="7" t="inlineStr">
-        <is>
-          <t>Drifting off slowly</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>Slow and weightless</t>
-        </is>
+          <t>C9D6E8</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr"/>
+      <c r="Q28" s="7" t="inlineStr"/>
+      <c r="R28" s="7" t="inlineStr"/>
+      <c r="S28" s="8" t="n">
+        <v>2115</v>
       </c>
       <c r="T28" s="7" t="inlineStr">
         <is>
-          <t>Cold, vast, silent</t>
+          <t>Time only flows, never hurries, never waits. Tonight it is only asking you to lie still while it carries you, the way it has carried every sleeper before you.</t>
         </is>
       </c>
       <c r="U28" s="7" t="inlineStr">
         <is>
-          <t>You rise gently from your own roof and travel outward, past the Moon and Jupiter, until a tilted gold shape appears in the dark. Up close the rings resolve into thousands of fine bright lines, and then into ice: billions of frozen pieces, some finer than dust and some the size of mountains, all drifting the same way at once. You watch small moons carve clean lanes and raise slow waves behind them, hear a gentle unfinished argument about how old it all is, and then settle into the ring plane and stay.</t>
+          <t>Quieting a busy mind</t>
         </is>
       </c>
       <c r="V28" s="7" t="inlineStr">
         <is>
-          <t>audio-the-rings-of-saturn-en-v3-aac96</t>
+          <t>Slow and thoughtful</t>
         </is>
       </c>
       <c r="W28" s="7" t="inlineStr">
         <is>
+          <t>Starlit, hushed, timeless</t>
+        </is>
+      </c>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>You climb a small hill to a small observatory to spend the night with the gentlest big question there is: what is time. A telescope shows that starlight is an old patient archive, arriving from a hundred different pasts all at once, and that there is no single now shared by the whole universe. Pendulum clocks, water clocks, and candle clocks each try to hang a bucket in a stream that never pools. A carpenter's son builds four clocks to solve longitude at sea, a hill at Greenwich becomes the world's meridian, and modern clocks now count the hum inside an atom. At the end, the astronomer closes the logbook with one word, closed, and so can you.</t>
+        </is>
+      </c>
+      <c r="Y28" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-quiet-observatory-questions-about-time-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z28" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X28" s="7" t="inlineStr">
+      <c r="AA28" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y28" s="7" t="inlineStr">
+      <c r="AB28" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z28" s="9" t="inlineStr">
+      <c r="AC28" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA28" s="9" t="inlineStr">
+      <c r="AD28" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB28" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC28" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD28" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE28" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6423,14 +6537,29 @@
       </c>
       <c r="AT28" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-rings-of-saturn/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-quiet-observatory-questions-about-time/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>the-slow-life-of-a-redwood</t>
+          <t>the-rings-of-saturn</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr"/>
@@ -6441,32 +6570,32 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>free</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>The Slow Life of a Redwood</t>
+          <t>The Rings of Saturn</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>A night in the fog with the tallest living things there have ever been</t>
+          <t>Ten metres of ice, two hundred thousand kilometres wide, turning in silence</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Read by Patrick, Block Island</t>
+          <t>Read by Amy from Greenwich</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>gentle-nature</t>
+          <t>cosmic-journeys</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr"/>
@@ -6482,92 +6611,92 @@
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20T19:30:00Z</t>
+          <t>2026-08-14T17:53:16Z</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>14201A</t>
+          <t>1B2436</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>A8C3A0</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="n">
-        <v>2431</v>
+          <t>E8C89A</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>saturn-rings</t>
+        </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>The grove waters itself with fog while everyone sleeps, and has done for two thousand summers. Nothing in it moves faster than a slug, and nothing needs watching tonight.</t>
+          <t>38506E</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>Quieting a full mind</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>Soft, green, ancient</t>
-        </is>
+          <t>1B2231</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>2298</v>
       </c>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>Foggy, hushed, deep green</t>
+          <t>A long way from anything that has ever asked something of you. Nothing out here is in a hurry, and none of it needs watching.</t>
         </is>
       </c>
       <c r="U29" s="7" t="inlineStr">
         <is>
-          <t>Walk into a coastal grove at dusk and stand at the foot of a tree over three hundred feet tall, wrapped in a foot of soft bark, older than the cathedrals. Follow one unbroken thread of water from the roots to the highest needle, and wait for the summer fog to roll in off the cold Pacific so the forest can water itself in the dark. Along the way, roots that graft into their neighbours and hold each other up, rings of trees standing where their elders stood, a ghost-white redwood fed by its family, and a garden of ferns and huckleberries growing a metre deep in the crown.</t>
+          <t>Drifting off slowly</t>
         </is>
       </c>
       <c r="V29" s="7" t="inlineStr">
         <is>
-          <t>audio-the-slow-life-of-a-redwood-en-v1-aac96</t>
+          <t>Slow and weightless</t>
         </is>
       </c>
       <c r="W29" s="7" t="inlineStr">
         <is>
+          <t>Cold, vast, silent</t>
+        </is>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>You rise gently from your own roof and travel outward, past the Moon and Jupiter, until a tilted gold shape appears in the dark. Up close the rings resolve into thousands of fine bright lines, and then into ice: billions of frozen pieces, some finer than dust and some the size of mountains, all drifting the same way at once. You watch small moons carve clean lanes and raise slow waves behind them, hear a gentle unfinished argument about how old it all is, and then settle into the ring plane and stay.</t>
+        </is>
+      </c>
+      <c r="Y29" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-rings-of-saturn-en-v3-aac96</t>
+        </is>
+      </c>
+      <c r="Z29" s="7" t="inlineStr">
+        <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X29" s="7" t="inlineStr">
+      <c r="AA29" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y29" s="7" t="inlineStr">
+      <c r="AB29" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z29" s="9" t="inlineStr">
+      <c r="AC29" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA29" s="9" t="inlineStr">
+      <c r="AD29" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB29" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC29" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD29" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="AE29" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6645,14 +6774,29 @@
       </c>
       <c r="AT29" s="9" t="inlineStr">
         <is>
-          <t>Stories/the-slow-life-of-a-redwood/story.yaml</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW29" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-rings-of-saturn/story.yaml</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>voyager-1-a-journey-to-interstellar-space</t>
+          <t>the-slow-life-of-a-redwood</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr"/>
@@ -6673,22 +6817,22 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Voyager 1: A Journey to Interstellar Space</t>
+          <t>The Slow Life of a Redwood</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>A small gold machine, forty-nine years out, still quietly drifting away from us</t>
+          <t>A night in the fog with the tallest living things there have ever been</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Read by Amy from Greenwich</t>
+          <t>Read by Patrick, Block Island</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>cosmic-journeys</t>
+          <t>gentle-nature</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr"/>
@@ -6709,179 +6853,407 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
+          <t>14201A</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>A8C3A0</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr"/>
+      <c r="Q30" s="7" t="inlineStr"/>
+      <c r="R30" s="7" t="inlineStr"/>
+      <c r="S30" s="8" t="n">
+        <v>2431</v>
+      </c>
+      <c r="T30" s="7" t="inlineStr">
+        <is>
+          <t>The grove waters itself with fog while everyone sleeps, and has done for two thousand summers. Nothing in it moves faster than a slug, and nothing needs watching tonight.</t>
+        </is>
+      </c>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>Quieting a full mind</t>
+        </is>
+      </c>
+      <c r="V30" s="7" t="inlineStr">
+        <is>
+          <t>Soft, green, ancient</t>
+        </is>
+      </c>
+      <c r="W30" s="7" t="inlineStr">
+        <is>
+          <t>Foggy, hushed, deep green</t>
+        </is>
+      </c>
+      <c r="X30" s="7" t="inlineStr">
+        <is>
+          <t>Walk into a coastal grove at dusk and stand at the foot of a tree over three hundred feet tall, wrapped in a foot of soft bark, older than the cathedrals. Follow one unbroken thread of water from the roots to the highest needle, and wait for the summer fog to roll in off the cold Pacific so the forest can water itself in the dark. Along the way, roots that graft into their neighbours and hold each other up, rings of trees standing where their elders stood, a ghost-white redwood fed by its family, and a garden of ferns and huckleberries growing a metre deep in the crown.</t>
+        </is>
+      </c>
+      <c r="Y30" s="7" t="inlineStr">
+        <is>
+          <t>audio-the-slow-life-of-a-redwood-en-v1-aac96</t>
+        </is>
+      </c>
+      <c r="Z30" s="7" t="inlineStr">
+        <is>
+          <t>master.wav</t>
+        </is>
+      </c>
+      <c r="AA30" s="7" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="AB30" s="7" t="inlineStr">
+        <is>
+          <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
+        </is>
+      </c>
+      <c r="AC30" s="9" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="AD30" s="9" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="AE30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AH30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AI30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AO30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AP30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>Stories/the-slow-life-of-a-redwood/story.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>voyager-1-a-journey-to-interstellar-space</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr"/>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Voyager 1: A Journey to Interstellar Space</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>A small gold machine, forty-nine years out, still quietly drifting away from us</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Read by Amy from Greenwich</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>cosmic-journeys</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20T19:30:00Z</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
           <t>0A0F1C</t>
         </is>
       </c>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>C7B27A</t>
         </is>
       </c>
-      <c r="P30" s="8" t="n">
+      <c r="P31" s="7" t="inlineStr"/>
+      <c r="Q31" s="7" t="inlineStr"/>
+      <c r="R31" s="7" t="inlineStr"/>
+      <c r="S31" s="8" t="n">
         <v>2290</v>
       </c>
-      <c r="Q30" s="7" t="inlineStr">
+      <c r="T31" s="7" t="inlineStr">
         <is>
           <t>It left in 1977 and it is not going anywhere in particular. It is simply still going, steadily, and none of it needs watching tonight.</t>
         </is>
       </c>
-      <c r="R30" s="7" t="inlineStr">
+      <c r="U31" s="7" t="inlineStr">
         <is>
           <t>Settling into the quiet</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="V31" s="7" t="inlineStr">
         <is>
           <t>Steady and outward</t>
         </is>
       </c>
-      <c r="T30" s="7" t="inlineStr">
+      <c r="W31" s="7" t="inlineStr">
         <is>
           <t>Dark, distant, gold, calm</t>
         </is>
       </c>
-      <c r="U30" s="7" t="inlineStr">
+      <c r="X31" s="7" t="inlineStr">
         <is>
           <t>Follow the most distant object people have ever made, out past Jupiter and Saturn and into the space between the stars. A gold record bolted to its side, a transmitter no brighter than a refrigerator bulb, and a whisper of radio that takes almost a full day to reach a dish in the Australian grass. Along the way, the gentle theft of a gravity assist, the choice to look at Titan, and the faint steady hum the gas out there turns out to make. Nothing about it is urgent. Nothing about it ever was.</t>
         </is>
       </c>
-      <c r="V30" s="7" t="inlineStr">
+      <c r="Y31" s="7" t="inlineStr">
         <is>
           <t>audio-voyager-1-a-journey-to-interstellar-space-en-v1-aac96</t>
         </is>
       </c>
-      <c r="W30" s="7" t="inlineStr">
+      <c r="Z31" s="7" t="inlineStr">
         <is>
           <t>master.wav</t>
         </is>
       </c>
-      <c r="X30" s="7" t="inlineStr">
+      <c r="AA31" s="7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="Y30" s="7" t="inlineStr">
+      <c r="AB31" s="7" t="inlineStr">
         <is>
           <t>AAC-LC M4A, 44.1 kHz, mono, 96 kbps</t>
         </is>
       </c>
-      <c r="Z30" s="9" t="inlineStr">
+      <c r="AC31" s="9" t="inlineStr">
         <is>
           <t>published</t>
         </is>
       </c>
-      <c r="AA30" s="9" t="inlineStr">
+      <c r="AD31" s="9" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="AB30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AC30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AD30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AE30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AF30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AG30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AH30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AI30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AJ30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AK30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AL30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AM30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AN30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AO30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AP30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AQ30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AR30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AS30" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AT30" s="9" t="inlineStr">
+      <c r="AE31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AH31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AI31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AO31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AP31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW31" s="9" t="inlineStr">
         <is>
           <t>Stories/voyager-1-a-journey-to-interstellar-space/story.yaml</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AT30"/>
+  <autoFilter ref="A3:AW31"/>
   <mergeCells count="6">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="AB2:AT2"/>
+    <mergeCell ref="A1:AW1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="F2:Y2"/>
-    <mergeCell ref="A1:AT1"/>
+    <mergeCell ref="AE2:AW2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="F2:AB2"/>
   </mergeCells>
-  <conditionalFormatting sqref="AB5:AT30">
+  <conditionalFormatting sqref="AE5:AW31">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"FAIL"</formula>
     </cfRule>
@@ -6889,7 +7261,7 @@
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA5:AA30">
+  <conditionalFormatting sqref="AD5:AD31">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"READY"</formula>
     </cfRule>
@@ -6897,31 +7269,31 @@
       <formula>"NOT READY"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D30">
+  <conditionalFormatting sqref="D5:D31">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"PENDING"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="C5:C70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="workflowStatus" prompt="Pipeline stage." type="list" errorStyle="stop">
+    <dataValidation sqref="C5:C71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="workflowStatus" prompt="Pipeline stage." type="list" errorStyle="stop">
       <formula1>"draft,rendered,qa-approved,staging,published"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="accessDecision" prompt="Free vs premium. Settle before staging." type="list" errorStyle="stop">
+    <dataValidation sqref="D5:D71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="accessDecision" prompt="Free vs premium. Settle before staging." type="list" errorStyle="stop">
       <formula1>"PENDING,free,premium"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_1" prompt="Existing genre IDs only." type="list" errorStyle="stop">
+    <dataValidation sqref="I5:I71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_1" prompt="Existing genre IDs only." type="list" errorStyle="stop">
       <formula1>"ancient-worlds,gentle-nature,cosmic-journeys,cozy-tales"</formula1>
     </dataValidation>
-    <dataValidation sqref="J5:J70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_2" prompt="Existing genre IDs only." type="list" errorStyle="stop">
+    <dataValidation sqref="J5:J71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="genreID_2" prompt="Existing genre IDs only." type="list" errorStyle="stop">
       <formula1>"ancient-worlds,gentle-nature,cosmic-journeys,cozy-tales"</formula1>
     </dataValidation>
-    <dataValidation sqref="X5:X70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="commercialRightsStatus" prompt="Must be verified to publish." type="list" errorStyle="stop">
+    <dataValidation sqref="AA5:AA71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="commercialRightsStatus" prompt="Must be verified to publish." type="list" errorStyle="stop">
       <formula1>"pending-verification,verified,restricted"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="trialPreviewEligible" prompt="true or false." type="list" errorStyle="stop">
+    <dataValidation sqref="K5:K71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="trialPreviewEligible" prompt="true or false." type="list" errorStyle="stop">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="isFeatured" prompt="true or false." type="list" errorStyle="stop">
+    <dataValidation sqref="L5:L71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Rejected" error="Not an allowed value. Pick from the list." promptTitle="isFeatured" prompt="true or false." type="list" errorStyle="stop">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
